--- a/2026 - 2027 FEE.xlsx
+++ b/2026 - 2027 FEE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB1001F-A16E-49DD-B2A1-F42FB38F518D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC92B81-C2C9-4DC4-9883-CF2DA9C8F58A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1789,7 +1789,7 @@
         <v>4500</v>
       </c>
       <c r="O5" s="24">
-        <v>19560</v>
+        <v>19500</v>
       </c>
       <c r="P5" s="24">
         <v>14330</v>
@@ -1823,14 +1823,14 @@
       </c>
       <c r="Z5" s="24">
         <f t="shared" si="5"/>
-        <v>78390</v>
+        <v>78330</v>
       </c>
       <c r="AA5" s="24">
         <v>0</v>
       </c>
       <c r="AB5" s="20">
         <f t="shared" si="6"/>
-        <v>78390</v>
+        <v>78330</v>
       </c>
       <c r="AC5" s="24" t="str">
         <f t="shared" si="7"/>
@@ -1894,7 +1894,7 @@
         <v>4200</v>
       </c>
       <c r="O6" s="24">
-        <v>19560</v>
+        <v>19500</v>
       </c>
       <c r="P6" s="24">
         <v>14330</v>
@@ -1928,14 +1928,14 @@
       </c>
       <c r="Z6" s="24">
         <f t="shared" si="5"/>
-        <v>67590</v>
+        <v>67530</v>
       </c>
       <c r="AA6" s="24">
         <v>0</v>
       </c>
       <c r="AB6" s="20">
         <f t="shared" si="6"/>
-        <v>67590</v>
+        <v>67530</v>
       </c>
       <c r="AC6" s="24" t="str">
         <f t="shared" si="7"/>
@@ -1999,7 +1999,7 @@
         <v>6000</v>
       </c>
       <c r="O7" s="24">
-        <v>19560</v>
+        <v>19500</v>
       </c>
       <c r="P7" s="24">
         <v>14330</v>
@@ -2033,14 +2033,14 @@
       </c>
       <c r="Z7" s="24">
         <f t="shared" si="5"/>
-        <v>79890</v>
+        <v>79830</v>
       </c>
       <c r="AA7" s="24">
         <v>0</v>
       </c>
       <c r="AB7" s="20">
         <f t="shared" si="6"/>
-        <v>79890</v>
+        <v>79830</v>
       </c>
       <c r="AC7" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2104,7 +2104,7 @@
         <v>6000</v>
       </c>
       <c r="O8" s="24">
-        <v>19560</v>
+        <v>19500</v>
       </c>
       <c r="P8" s="24">
         <v>14330</v>
@@ -2138,14 +2138,14 @@
       </c>
       <c r="Z8" s="24">
         <f t="shared" si="5"/>
-        <v>79890</v>
+        <v>79830</v>
       </c>
       <c r="AA8" s="24">
         <v>0</v>
       </c>
       <c r="AB8" s="20">
         <f t="shared" si="6"/>
-        <v>79890</v>
+        <v>79830</v>
       </c>
       <c r="AC8" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2209,7 +2209,7 @@
         <v>4200</v>
       </c>
       <c r="O9" s="24">
-        <v>19560</v>
+        <v>19500</v>
       </c>
       <c r="P9" s="24">
         <v>14330</v>
@@ -2243,14 +2243,14 @@
       </c>
       <c r="Z9" s="24">
         <f t="shared" si="5"/>
-        <v>67590</v>
+        <v>67530</v>
       </c>
       <c r="AA9" s="24">
         <v>0</v>
       </c>
       <c r="AB9" s="20">
         <f t="shared" si="6"/>
-        <v>67590</v>
+        <v>67530</v>
       </c>
       <c r="AC9" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2314,7 +2314,7 @@
         <v>3000</v>
       </c>
       <c r="O10" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P10" s="24">
         <v>14330</v>
@@ -2348,14 +2348,14 @@
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="5"/>
-        <v>62410</v>
+        <v>62230</v>
       </c>
       <c r="AA10" s="24">
         <v>0</v>
       </c>
       <c r="AB10" s="20">
         <f t="shared" si="6"/>
-        <v>62410</v>
+        <v>62230</v>
       </c>
       <c r="AC10" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2419,7 +2419,7 @@
         <v>3000</v>
       </c>
       <c r="O11" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P11" s="24">
         <v>14330</v>
@@ -2453,14 +2453,14 @@
       </c>
       <c r="Z11" s="24">
         <f t="shared" si="5"/>
-        <v>62410</v>
+        <v>62230</v>
       </c>
       <c r="AA11" s="24">
         <v>0</v>
       </c>
       <c r="AB11" s="20">
         <f t="shared" si="6"/>
-        <v>62410</v>
+        <v>62230</v>
       </c>
       <c r="AC11" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2524,7 +2524,7 @@
         <v>3000</v>
       </c>
       <c r="O12" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P12" s="24">
         <v>14330</v>
@@ -2558,14 +2558,14 @@
       </c>
       <c r="Z12" s="24">
         <f t="shared" si="5"/>
-        <v>70380</v>
+        <v>70200</v>
       </c>
       <c r="AA12" s="24">
         <v>0</v>
       </c>
       <c r="AB12" s="20">
         <f t="shared" si="6"/>
-        <v>70380</v>
+        <v>70200</v>
       </c>
       <c r="AC12" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2629,7 +2629,7 @@
         <v>6000</v>
       </c>
       <c r="O13" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P13" s="24">
         <v>14330</v>
@@ -2663,14 +2663,14 @@
       </c>
       <c r="Z13" s="24">
         <f t="shared" si="5"/>
-        <v>73940</v>
+        <v>73760</v>
       </c>
       <c r="AA13" s="24">
         <v>0</v>
       </c>
       <c r="AB13" s="20">
         <f t="shared" si="6"/>
-        <v>73940</v>
+        <v>73760</v>
       </c>
       <c r="AC13" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2734,7 +2734,7 @@
         <v>3000</v>
       </c>
       <c r="O14" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P14" s="24">
         <v>14330</v>
@@ -2768,14 +2768,14 @@
       </c>
       <c r="Z14" s="24">
         <f t="shared" si="5"/>
-        <v>62890</v>
+        <v>62710</v>
       </c>
       <c r="AA14" s="24">
         <v>0</v>
       </c>
       <c r="AB14" s="20">
         <f t="shared" si="6"/>
-        <v>62890</v>
+        <v>62710</v>
       </c>
       <c r="AC14" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2839,7 +2839,7 @@
         <v>4500</v>
       </c>
       <c r="O15" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P15" s="24">
         <v>14330</v>
@@ -2873,14 +2873,14 @@
       </c>
       <c r="Z15" s="24">
         <f t="shared" si="5"/>
-        <v>72660</v>
+        <v>72480</v>
       </c>
       <c r="AA15" s="24">
         <v>0</v>
       </c>
       <c r="AB15" s="20">
         <f t="shared" si="6"/>
-        <v>72660</v>
+        <v>72480</v>
       </c>
       <c r="AC15" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2944,7 +2944,7 @@
         <v>3000</v>
       </c>
       <c r="O16" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P16" s="24">
         <v>14330</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="Z16" s="24">
         <f t="shared" si="5"/>
-        <v>62910</v>
+        <v>62730</v>
       </c>
       <c r="AA16" s="24">
         <v>0</v>
       </c>
       <c r="AB16" s="20">
         <f t="shared" si="6"/>
-        <v>62910</v>
+        <v>62730</v>
       </c>
       <c r="AC16" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3049,7 +3049,7 @@
         <v>3000</v>
       </c>
       <c r="O17" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P17" s="24">
         <v>14330</v>
@@ -3083,14 +3083,14 @@
       </c>
       <c r="Z17" s="24">
         <f t="shared" si="5"/>
-        <v>62410</v>
+        <v>62230</v>
       </c>
       <c r="AA17" s="24">
         <v>0</v>
       </c>
       <c r="AB17" s="20">
         <f t="shared" si="6"/>
-        <v>62410</v>
+        <v>62230</v>
       </c>
       <c r="AC17" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3154,7 +3154,7 @@
         <v>4200</v>
       </c>
       <c r="O18" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P18" s="24">
         <v>14330</v>
@@ -3188,14 +3188,14 @@
       </c>
       <c r="Z18" s="24">
         <f t="shared" si="5"/>
-        <v>70610</v>
+        <v>70430</v>
       </c>
       <c r="AA18" s="24">
         <v>0</v>
       </c>
       <c r="AB18" s="20">
         <f t="shared" si="6"/>
-        <v>70610</v>
+        <v>70430</v>
       </c>
       <c r="AC18" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3259,7 +3259,7 @@
         <v>3000</v>
       </c>
       <c r="O19" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P19" s="24">
         <v>14330</v>
@@ -3293,14 +3293,14 @@
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="5"/>
-        <v>67265</v>
+        <v>67085</v>
       </c>
       <c r="AA19" s="24">
         <v>0</v>
       </c>
       <c r="AB19" s="20">
         <f t="shared" si="6"/>
-        <v>67265</v>
+        <v>67085</v>
       </c>
       <c r="AC19" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3364,7 +3364,7 @@
         <v>4200</v>
       </c>
       <c r="O20" s="24">
-        <v>22580</v>
+        <v>22400</v>
       </c>
       <c r="P20" s="24">
         <v>14330</v>
@@ -3398,14 +3398,14 @@
       </c>
       <c r="Z20" s="24">
         <f t="shared" si="5"/>
-        <v>78610</v>
+        <v>78430</v>
       </c>
       <c r="AA20" s="24">
         <v>0</v>
       </c>
       <c r="AB20" s="20">
         <f t="shared" si="6"/>
-        <v>78610</v>
+        <v>78430</v>
       </c>
       <c r="AC20" s="24" t="str">
         <f t="shared" si="7"/>
@@ -11587,14 +11587,14 @@
         <v>0</v>
       </c>
       <c r="Z98" s="24">
-        <f t="shared" ref="Z98:Z129" si="35">SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z120" si="35">SUM(J98:Y98)</f>
         <v>77120</v>
       </c>
       <c r="AA98" s="24">
         <v>0</v>
       </c>
       <c r="AB98" s="20">
-        <f t="shared" ref="AB98:AB129" si="36">Z98-AA98</f>
+        <f t="shared" ref="AB98:AB120" si="36">Z98-AA98</f>
         <v>77120</v>
       </c>
       <c r="AC98" s="24" t="str">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="Z121" s="27">
         <f t="shared" si="40"/>
-        <v>7251495</v>
+        <v>7249215</v>
       </c>
       <c r="AA121" s="27">
         <f t="shared" si="40"/>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="AB121" s="27">
         <f t="shared" si="40"/>
-        <v>7160495</v>
+        <v>7158215</v>
       </c>
       <c r="AC121" s="27">
         <f t="shared" si="40"/>

--- a/2026 - 2027 FEE.xlsx
+++ b/2026 - 2027 FEE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B6D6AD-C843-43BA-B1C8-0C59B36561F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62977A2E-3E9F-409E-81F8-E82B394EEF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="266">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -830,6 +830,12 @@
   <si>
     <t>AKANDE FAMILY</t>
   </si>
+  <si>
+    <t>NIP:paul onyezuoke udenson</t>
+  </si>
+  <si>
+    <t>UDENSON FAMILY</t>
+  </si>
 </sst>
 </file>
 
@@ -13846,11 +13852,11 @@
         <v>36390</v>
       </c>
       <c r="AA118" s="24">
-        <v>0</v>
+        <v>7070</v>
       </c>
       <c r="AB118" s="20">
         <f t="shared" si="36"/>
-        <v>36390</v>
+        <v>29320</v>
       </c>
       <c r="AC118" s="24" t="str">
         <f t="shared" si="37"/>
@@ -13877,7 +13883,7 @@
         <v>30</v>
       </c>
       <c r="D119" s="23">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E119" s="24">
         <v>0</v>
@@ -13900,7 +13906,7 @@
       </c>
       <c r="K119" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
+        <v>18200</v>
       </c>
       <c r="L119" s="24">
         <f t="shared" si="32"/>
@@ -13908,7 +13914,7 @@
       </c>
       <c r="M119" s="24">
         <f t="shared" si="33"/>
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="N119" s="24">
         <f t="shared" si="34"/>
@@ -13949,14 +13955,14 @@
       </c>
       <c r="Z119" s="24">
         <f t="shared" si="35"/>
-        <v>44280</v>
+        <v>42930</v>
       </c>
       <c r="AA119" s="24">
-        <v>0</v>
+        <v>42930</v>
       </c>
       <c r="AB119" s="20">
         <f t="shared" si="36"/>
-        <v>44280</v>
+        <v>0</v>
       </c>
       <c r="AC119" s="24" t="str">
         <f t="shared" si="37"/>
@@ -13970,7 +13976,9 @@
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="AF119" s="25"/>
+      <c r="AF119" s="25" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" s="22" t="s">
@@ -14139,15 +14147,15 @@
       </c>
       <c r="Z121" s="28">
         <f t="shared" si="40"/>
-        <v>7235925</v>
+        <v>7234575</v>
       </c>
       <c r="AA121" s="28">
         <f t="shared" si="40"/>
-        <v>304975</v>
+        <v>354975</v>
       </c>
       <c r="AB121" s="28">
         <f t="shared" si="40"/>
-        <v>6930950</v>
+        <v>6879600</v>
       </c>
       <c r="AC121" s="28">
         <f t="shared" si="40"/>
@@ -22554,6 +22562,23 @@
         <v>263</v>
       </c>
     </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D10" s="9">
+        <v>50000</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
     <row r="13" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>

--- a/2026 - 2027 FEE.xlsx
+++ b/2026 - 2027 FEE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62977A2E-3E9F-409E-81F8-E82B394EEF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83457E3A-BDF4-4CB9-AC26-808051A1DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="267">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -816,9 +816,6 @@
     <t>COMMENT</t>
   </si>
   <si>
-    <t>BONUS</t>
-  </si>
-  <si>
     <t>NIP:ABIMBOLA ADENIKE ALABI</t>
   </si>
   <si>
@@ -835,6 +832,12 @@
   </si>
   <si>
     <t>UDENSON FAMILY</t>
+  </si>
+  <si>
+    <t>NIP:SUKURA DASOLA MUKAILA</t>
+  </si>
+  <si>
+    <t>ADEDAMOLA IREMIDE</t>
   </si>
 </sst>
 </file>
@@ -1555,18 +1558,21 @@
         <v>51180</v>
       </c>
       <c r="AC2" s="24" t="str">
-        <f t="shared" ref="AC2:AC33" si="7">IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
+        <f>IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
         <v/>
       </c>
       <c r="AD2" s="24" t="str">
-        <f t="shared" ref="AD2:AD33" si="8">IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
+        <f>IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
         <v/>
       </c>
       <c r="AE2" s="24" t="str">
-        <f t="shared" ref="AE2:AE33" si="9">IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
-        <v/>
-      </c>
-      <c r="AF2" s="25"/>
+        <f>IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
+        <v/>
+      </c>
+      <c r="AF2" s="25" t="str">
+        <f>IF(AB2&lt;=0,"BONUS","")</f>
+        <v/>
+      </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -1617,7 +1623,7 @@
         <v>3750</v>
       </c>
       <c r="O3" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P3" s="24">
         <v>11330</v>
@@ -1651,28 +1657,31 @@
       </c>
       <c r="Z3" s="24">
         <f t="shared" si="5"/>
-        <v>71875</v>
+        <v>72355</v>
       </c>
       <c r="AA3" s="24">
         <v>0</v>
       </c>
       <c r="AB3" s="20">
         <f t="shared" si="6"/>
-        <v>71875</v>
+        <v>72355</v>
       </c>
       <c r="AC3" s="24" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AC3:AC66" si="7">IF(AND($T3=6000, ($T3+$W3-$AB3)&gt;=6000),T3,"")</f>
         <v/>
       </c>
       <c r="AD3" s="24" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="AD3:AD66" si="8">IF(AND($T3=8000, ($T3+$W3-$AB3)&gt;=8000),T3,"")</f>
         <v/>
       </c>
       <c r="AE3" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="AF3" s="25"/>
+        <f t="shared" ref="AE3:AE66" si="9">IF(($T3+$W3-$AB3)&gt;=$T3+8000,W3,"")</f>
+        <v/>
+      </c>
+      <c r="AF3" s="25" t="str">
+        <f t="shared" ref="AF3:AF66" si="10">IF(AB3&lt;=0,"BONUS","")</f>
+        <v/>
+      </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
@@ -1778,7 +1787,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF4" s="25"/>
+      <c r="AF4" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
@@ -1829,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P5" s="24">
         <v>10730</v>
@@ -1863,14 +1875,14 @@
       </c>
       <c r="Z5" s="24">
         <f t="shared" si="5"/>
-        <v>58680</v>
+        <v>59160</v>
       </c>
       <c r="AA5" s="24">
         <v>0</v>
       </c>
       <c r="AB5" s="20">
         <f t="shared" si="6"/>
-        <v>58680</v>
+        <v>59160</v>
       </c>
       <c r="AC5" s="24" t="str">
         <f t="shared" si="7"/>
@@ -1884,7 +1896,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF5" s="25"/>
+      <c r="AF5" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
@@ -1990,7 +2005,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF6" s="25"/>
+      <c r="AF6" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
@@ -2096,8 +2114,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF7" s="25" t="s">
-        <v>259</v>
+      <c r="AF7" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -2204,7 +2223,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF8" s="25"/>
+      <c r="AF8" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
@@ -2310,7 +2332,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF9" s="25"/>
+      <c r="AF9" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
@@ -2361,7 +2386,7 @@
         <v>3750</v>
       </c>
       <c r="O10" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P10" s="24">
         <v>13230</v>
@@ -2395,14 +2420,14 @@
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="5"/>
-        <v>68810</v>
+        <v>69290</v>
       </c>
       <c r="AA10" s="24">
         <v>0</v>
       </c>
       <c r="AB10" s="20">
         <f t="shared" si="6"/>
-        <v>68810</v>
+        <v>69290</v>
       </c>
       <c r="AC10" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2416,7 +2441,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF10" s="25"/>
+      <c r="AF10" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
@@ -2522,7 +2550,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF11" s="25"/>
+      <c r="AF11" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
@@ -2628,7 +2659,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF12" s="25"/>
+      <c r="AF12" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
@@ -2679,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P13" s="24">
         <v>10730</v>
@@ -2713,14 +2747,14 @@
       </c>
       <c r="Z13" s="24">
         <f t="shared" si="5"/>
-        <v>52180</v>
+        <v>52660</v>
       </c>
       <c r="AA13" s="24">
         <v>0</v>
       </c>
       <c r="AB13" s="20">
         <f t="shared" si="6"/>
-        <v>52180</v>
+        <v>52660</v>
       </c>
       <c r="AC13" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2734,7 +2768,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF13" s="25"/>
+      <c r="AF13" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
@@ -2785,7 +2822,7 @@
         <v>2500</v>
       </c>
       <c r="O14" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P14" s="24">
         <v>13230</v>
@@ -2819,14 +2856,14 @@
       </c>
       <c r="Z14" s="24">
         <f t="shared" si="5"/>
-        <v>60030</v>
+        <v>60510</v>
       </c>
       <c r="AA14" s="24">
         <v>0</v>
       </c>
       <c r="AB14" s="20">
         <f t="shared" si="6"/>
-        <v>60030</v>
+        <v>60510</v>
       </c>
       <c r="AC14" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2840,7 +2877,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF14" s="25"/>
+      <c r="AF14" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
@@ -2853,7 +2893,7 @@
         <v>49</v>
       </c>
       <c r="D15" s="23">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E15" s="24">
         <v>0</v>
@@ -2876,7 +2916,7 @@
       </c>
       <c r="K15" s="24">
         <f t="shared" si="1"/>
-        <v>26000</v>
+        <v>24700</v>
       </c>
       <c r="L15" s="24">
         <f t="shared" si="2"/>
@@ -2884,7 +2924,7 @@
       </c>
       <c r="M15" s="24">
         <f t="shared" si="3"/>
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="N15" s="24">
         <f t="shared" si="4"/>
@@ -2925,14 +2965,14 @@
       </c>
       <c r="Z15" s="24">
         <f t="shared" si="5"/>
+        <v>40790</v>
+      </c>
+      <c r="AA15" s="24">
         <v>42140</v>
-      </c>
-      <c r="AA15" s="24">
-        <v>0</v>
       </c>
       <c r="AB15" s="20">
         <f t="shared" si="6"/>
-        <v>42140</v>
+        <v>-1350</v>
       </c>
       <c r="AC15" s="24" t="str">
         <f t="shared" si="7"/>
@@ -2946,7 +2986,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF15" s="25"/>
+      <c r="AF15" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>BONUS</v>
+      </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
@@ -2997,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P16" s="24">
         <v>10730</v>
@@ -3031,14 +3074,14 @@
       </c>
       <c r="Z16" s="24">
         <f t="shared" si="5"/>
-        <v>58680</v>
+        <v>59160</v>
       </c>
       <c r="AA16" s="24">
         <v>0</v>
       </c>
       <c r="AB16" s="20">
         <f t="shared" si="6"/>
-        <v>58680</v>
+        <v>59160</v>
       </c>
       <c r="AC16" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3052,7 +3095,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF16" s="25"/>
+      <c r="AF16" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
@@ -3103,7 +3149,7 @@
         <v>3750</v>
       </c>
       <c r="O17" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P17" s="24">
         <v>13230</v>
@@ -3137,14 +3183,14 @@
       </c>
       <c r="Z17" s="24">
         <f t="shared" si="5"/>
-        <v>68810</v>
+        <v>69290</v>
       </c>
       <c r="AA17" s="24">
         <v>0</v>
       </c>
       <c r="AB17" s="20">
         <f t="shared" si="6"/>
-        <v>68810</v>
+        <v>69290</v>
       </c>
       <c r="AC17" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3158,7 +3204,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF17" s="25"/>
+      <c r="AF17" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
@@ -3264,8 +3313,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF18" s="25" t="s">
-        <v>259</v>
+      <c r="AF18" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -3317,7 +3367,7 @@
         <v>3750</v>
       </c>
       <c r="O19" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P19" s="24">
         <v>11330</v>
@@ -3351,14 +3401,14 @@
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="5"/>
-        <v>73445</v>
+        <v>73925</v>
       </c>
       <c r="AA19" s="24">
         <v>51685</v>
       </c>
       <c r="AB19" s="20">
         <f t="shared" si="6"/>
-        <v>21760</v>
+        <v>22240</v>
       </c>
       <c r="AC19" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3372,7 +3422,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF19" s="25"/>
+      <c r="AF19" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
@@ -3478,7 +3531,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF20" s="25"/>
+      <c r="AF20" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
@@ -3584,7 +3640,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF21" s="25"/>
+      <c r="AF21" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="22" t="s">
@@ -3690,7 +3749,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF22" s="25"/>
+      <c r="AF22" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
@@ -3741,7 +3803,7 @@
         <v>3750</v>
       </c>
       <c r="O23" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P23" s="24">
         <v>11330</v>
@@ -3775,14 +3837,14 @@
       </c>
       <c r="Z23" s="24">
         <f t="shared" si="5"/>
-        <v>65750</v>
+        <v>66230</v>
       </c>
       <c r="AA23" s="24">
         <v>0</v>
       </c>
       <c r="AB23" s="20">
         <f t="shared" si="6"/>
-        <v>65750</v>
+        <v>66230</v>
       </c>
       <c r="AC23" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3796,7 +3858,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF23" s="25"/>
+      <c r="AF23" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
@@ -3847,7 +3912,7 @@
         <v>3750</v>
       </c>
       <c r="O24" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P24" s="24">
         <v>11330</v>
@@ -3881,14 +3946,14 @@
       </c>
       <c r="Z24" s="24">
         <f t="shared" si="5"/>
-        <v>65750</v>
+        <v>66230</v>
       </c>
       <c r="AA24" s="24">
         <v>0</v>
       </c>
       <c r="AB24" s="20">
         <f t="shared" si="6"/>
-        <v>65750</v>
+        <v>66230</v>
       </c>
       <c r="AC24" s="24" t="str">
         <f t="shared" si="7"/>
@@ -3902,7 +3967,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF24" s="25"/>
+      <c r="AF24" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
@@ -4008,7 +4076,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF25" s="25"/>
+      <c r="AF25" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
@@ -4114,7 +4185,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF26" s="25"/>
+      <c r="AF26" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
@@ -4220,7 +4294,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF27" s="25"/>
+      <c r="AF27" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
@@ -4326,7 +4403,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF28" s="25"/>
+      <c r="AF28" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
@@ -4432,7 +4512,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF29" s="25"/>
+      <c r="AF29" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="22" t="s">
@@ -4538,7 +4621,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF30" s="25"/>
+      <c r="AF30" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
@@ -4644,7 +4730,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF31" s="25"/>
+      <c r="AF31" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="22" t="s">
@@ -4750,7 +4839,10 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF32" s="25"/>
+      <c r="AF32" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
@@ -4856,8 +4948,9 @@
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AF33" s="25" t="s">
-        <v>259</v>
+      <c r="AF33" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
@@ -4889,27 +4982,27 @@
         <v>0</v>
       </c>
       <c r="J34" s="24">
-        <f t="shared" ref="J34:J65" si="10">(1-$D34)*E34</f>
+        <f t="shared" ref="J34:J65" si="11">(1-$D34)*E34</f>
         <v>0</v>
       </c>
       <c r="K34" s="24">
-        <f t="shared" ref="K34:K65" si="11">(1-$D34)*F34</f>
+        <f t="shared" ref="K34:K65" si="12">(1-$D34)*F34</f>
         <v>19500</v>
       </c>
       <c r="L34" s="24">
-        <f t="shared" ref="L34:L65" si="12">G34</f>
+        <f t="shared" ref="L34:L65" si="13">G34</f>
         <v>4000</v>
       </c>
       <c r="M34" s="24">
-        <f t="shared" ref="M34:M65" si="13">(1-$D34)*H34</f>
+        <f t="shared" ref="M34:M65" si="14">(1-$D34)*H34</f>
         <v>0</v>
       </c>
       <c r="N34" s="24">
-        <f t="shared" ref="N34:N65" si="14">(1-$D34)*I34</f>
+        <f t="shared" ref="N34:N65" si="15">(1-$D34)*I34</f>
         <v>0</v>
       </c>
       <c r="O34" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P34" s="24">
         <v>10730</v>
@@ -4942,29 +5035,32 @@
         <v>0</v>
       </c>
       <c r="Z34" s="24">
-        <f t="shared" ref="Z34:Z65" si="15">SUM(J34:Y34)</f>
-        <v>64680</v>
+        <f t="shared" ref="Z34:Z65" si="16">SUM(J34:Y34)</f>
+        <v>65160</v>
       </c>
       <c r="AA34" s="24">
         <v>0</v>
       </c>
       <c r="AB34" s="20">
-        <f t="shared" ref="AB34:AB65" si="16">Z34-AA34</f>
-        <v>64680</v>
+        <f t="shared" ref="AB34:AB65" si="17">Z34-AA34</f>
+        <v>65160</v>
       </c>
       <c r="AC34" s="24" t="str">
-        <f t="shared" ref="AC34:AC65" si="17">IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD34" s="24" t="str">
-        <f t="shared" ref="AD34:AD65" si="18">IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE34" s="24" t="str">
-        <f t="shared" ref="AE34:AE65" si="19">IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
-        <v/>
-      </c>
-      <c r="AF34" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF34" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
@@ -4995,27 +5091,27 @@
         <v>5000</v>
       </c>
       <c r="J35" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K35" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L35" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M35" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N35" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O35" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P35" s="24">
         <v>11330</v>
@@ -5048,29 +5144,32 @@
         <v>250</v>
       </c>
       <c r="Z35" s="24">
-        <f t="shared" si="15"/>
-        <v>72000</v>
+        <f t="shared" si="16"/>
+        <v>72480</v>
       </c>
       <c r="AA35" s="24">
         <v>0</v>
       </c>
       <c r="AB35" s="20">
-        <f t="shared" si="16"/>
-        <v>72000</v>
+        <f t="shared" si="17"/>
+        <v>72480</v>
       </c>
       <c r="AC35" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD35" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE35" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF35" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF35" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="22" t="s">
@@ -5101,23 +5200,23 @@
         <v>0</v>
       </c>
       <c r="J36" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K36" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L36" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M36" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N36" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O36" s="24">
@@ -5154,29 +5253,32 @@
         <v>0</v>
       </c>
       <c r="Z36" s="24">
-        <f t="shared" si="15"/>
-        <v>43140</v>
-      </c>
-      <c r="AA36" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="20">
         <f t="shared" si="16"/>
         <v>43140</v>
       </c>
+      <c r="AA36" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="20">
+        <f t="shared" si="17"/>
+        <v>43140</v>
+      </c>
       <c r="AC36" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD36" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE36" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF36" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF36" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="22" t="s">
@@ -5207,23 +5309,23 @@
         <v>0</v>
       </c>
       <c r="J37" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K37" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L37" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M37" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N37" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O37" s="24">
@@ -5260,29 +5362,32 @@
         <v>0</v>
       </c>
       <c r="Z37" s="24">
-        <f t="shared" si="15"/>
-        <v>56930</v>
-      </c>
-      <c r="AA37" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="20">
         <f t="shared" si="16"/>
         <v>56930</v>
       </c>
+      <c r="AA37" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="20">
+        <f t="shared" si="17"/>
+        <v>56930</v>
+      </c>
       <c r="AC37" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD37" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE37" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF37" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF37" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="22" t="s">
@@ -5313,23 +5418,23 @@
         <v>0</v>
       </c>
       <c r="J38" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K38" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L38" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2000</v>
       </c>
       <c r="M38" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N38" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O38" s="24">
@@ -5366,29 +5471,32 @@
         <v>0</v>
       </c>
       <c r="Z38" s="24">
-        <f t="shared" si="15"/>
-        <v>31050</v>
-      </c>
-      <c r="AA38" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="20">
         <f t="shared" si="16"/>
         <v>31050</v>
       </c>
+      <c r="AA38" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="20">
+        <f t="shared" si="17"/>
+        <v>31050</v>
+      </c>
       <c r="AC38" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD38" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE38" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF38" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF38" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
@@ -5419,23 +5527,23 @@
         <v>0</v>
       </c>
       <c r="J39" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K39" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L39" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M39" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N39" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O39" s="24">
@@ -5472,29 +5580,32 @@
         <v>0</v>
       </c>
       <c r="Z39" s="24">
-        <f t="shared" si="15"/>
-        <v>43140</v>
-      </c>
-      <c r="AA39" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="20">
         <f t="shared" si="16"/>
         <v>43140</v>
       </c>
+      <c r="AA39" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="20">
+        <f t="shared" si="17"/>
+        <v>43140</v>
+      </c>
       <c r="AC39" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD39" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE39" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF39" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF39" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
@@ -5525,23 +5636,23 @@
         <v>6000</v>
       </c>
       <c r="J40" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K40" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L40" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M40" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N40" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O40" s="24">
@@ -5578,29 +5689,32 @@
         <v>-30</v>
       </c>
       <c r="Z40" s="24">
-        <f t="shared" si="15"/>
-        <v>70200</v>
-      </c>
-      <c r="AA40" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="20">
         <f t="shared" si="16"/>
         <v>70200</v>
       </c>
+      <c r="AA40" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="20">
+        <f t="shared" si="17"/>
+        <v>70200</v>
+      </c>
       <c r="AC40" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD40" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE40" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF40" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF40" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="22" t="s">
@@ -5631,23 +5745,23 @@
         <v>6000</v>
       </c>
       <c r="J41" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K41" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>33000</v>
       </c>
       <c r="L41" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M41" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N41" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O41" s="24">
@@ -5684,29 +5798,32 @@
         <v>-8970</v>
       </c>
       <c r="Z41" s="24">
-        <f t="shared" si="15"/>
-        <v>73760</v>
-      </c>
-      <c r="AA41" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="20">
         <f t="shared" si="16"/>
         <v>73760</v>
       </c>
+      <c r="AA41" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="20">
+        <f t="shared" si="17"/>
+        <v>73760</v>
+      </c>
       <c r="AC41" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD41" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE41" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF41" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF41" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="22" t="s">
@@ -5737,23 +5854,23 @@
         <v>8000</v>
       </c>
       <c r="J42" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K42" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>40000</v>
       </c>
       <c r="L42" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M42" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N42" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8000</v>
       </c>
       <c r="O42" s="24">
@@ -5790,29 +5907,32 @@
         <v>120</v>
       </c>
       <c r="Z42" s="24">
-        <f t="shared" si="15"/>
-        <v>81330</v>
-      </c>
-      <c r="AA42" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="20">
         <f t="shared" si="16"/>
         <v>81330</v>
       </c>
+      <c r="AA42" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="20">
+        <f t="shared" si="17"/>
+        <v>81330</v>
+      </c>
       <c r="AC42" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD42" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE42" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF42" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF42" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="22" t="s">
@@ -5843,23 +5963,23 @@
         <v>6000</v>
       </c>
       <c r="J43" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K43" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L43" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M43" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N43" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O43" s="24">
@@ -5896,29 +6016,32 @@
         <v>480</v>
       </c>
       <c r="Z43" s="24">
-        <f t="shared" si="15"/>
-        <v>62710</v>
-      </c>
-      <c r="AA43" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="20">
         <f t="shared" si="16"/>
         <v>62710</v>
       </c>
+      <c r="AA43" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="20">
+        <f t="shared" si="17"/>
+        <v>62710</v>
+      </c>
       <c r="AC43" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD43" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE43" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF43" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF43" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
@@ -5949,23 +6072,23 @@
         <v>6000</v>
       </c>
       <c r="J44" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K44" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24750</v>
       </c>
       <c r="L44" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M44" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N44" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4500</v>
       </c>
       <c r="O44" s="24">
@@ -6002,29 +6125,32 @@
         <v>0</v>
       </c>
       <c r="Z44" s="24">
-        <f t="shared" si="15"/>
-        <v>72480</v>
-      </c>
-      <c r="AA44" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="20">
         <f t="shared" si="16"/>
         <v>72480</v>
       </c>
+      <c r="AA44" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="20">
+        <f t="shared" si="17"/>
+        <v>72480</v>
+      </c>
       <c r="AC44" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD44" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE44" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF44" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF44" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
@@ -6055,23 +6181,23 @@
         <v>8000</v>
       </c>
       <c r="J45" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K45" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>30000</v>
       </c>
       <c r="L45" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M45" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N45" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O45" s="24">
@@ -6108,29 +6234,32 @@
         <v>0</v>
       </c>
       <c r="Z45" s="24">
-        <f t="shared" si="15"/>
-        <v>68710</v>
-      </c>
-      <c r="AA45" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="20">
         <f t="shared" si="16"/>
         <v>68710</v>
       </c>
+      <c r="AA45" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="20">
+        <f t="shared" si="17"/>
+        <v>68710</v>
+      </c>
       <c r="AC45" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD45" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE45" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF45" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF45" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
@@ -6161,23 +6290,23 @@
         <v>0</v>
       </c>
       <c r="J46" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K46" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L46" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M46" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N46" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O46" s="24">
@@ -6214,29 +6343,32 @@
         <v>0</v>
       </c>
       <c r="Z46" s="24">
-        <f t="shared" si="15"/>
-        <v>43140</v>
-      </c>
-      <c r="AA46" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="20">
         <f t="shared" si="16"/>
         <v>43140</v>
       </c>
+      <c r="AA46" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="20">
+        <f t="shared" si="17"/>
+        <v>43140</v>
+      </c>
       <c r="AC46" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD46" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE46" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF46" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF46" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="22" t="s">
@@ -6267,27 +6399,27 @@
         <v>0</v>
       </c>
       <c r="J47" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K47" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19500</v>
       </c>
       <c r="L47" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M47" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N47" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O47" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P47" s="24">
         <v>10730</v>
@@ -6320,29 +6452,32 @@
         <v>18500</v>
       </c>
       <c r="Z47" s="24">
-        <f t="shared" si="15"/>
-        <v>83180</v>
+        <f t="shared" si="16"/>
+        <v>83660</v>
       </c>
       <c r="AA47" s="24">
         <v>48000</v>
       </c>
       <c r="AB47" s="20">
-        <f t="shared" si="16"/>
-        <v>35180</v>
+        <f t="shared" si="17"/>
+        <v>35660</v>
       </c>
       <c r="AC47" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD47" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE47" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF47" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF47" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="22" t="s">
@@ -6373,23 +6508,23 @@
         <v>5000</v>
       </c>
       <c r="J48" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K48" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L48" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M48" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N48" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O48" s="24">
@@ -6426,29 +6561,32 @@
         <v>0</v>
       </c>
       <c r="Z48" s="24">
-        <f t="shared" si="15"/>
-        <v>79020</v>
-      </c>
-      <c r="AA48" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="20">
         <f t="shared" si="16"/>
         <v>79020</v>
       </c>
+      <c r="AA48" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="20">
+        <f t="shared" si="17"/>
+        <v>79020</v>
+      </c>
       <c r="AC48" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD48" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE48" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF48" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF48" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
@@ -6479,27 +6617,27 @@
         <v>5000</v>
       </c>
       <c r="J49" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K49" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L49" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M49" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N49" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O49" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P49" s="24">
         <v>11330</v>
@@ -6532,29 +6670,32 @@
         <v>0</v>
       </c>
       <c r="Z49" s="24">
-        <f t="shared" si="15"/>
-        <v>82320</v>
+        <f t="shared" si="16"/>
+        <v>82800</v>
       </c>
       <c r="AA49" s="24">
         <v>0</v>
       </c>
       <c r="AB49" s="20">
-        <f t="shared" si="16"/>
-        <v>82320</v>
+        <f t="shared" si="17"/>
+        <v>82800</v>
       </c>
       <c r="AC49" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD49" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE49" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF49" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF49" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="22" t="s">
@@ -6585,23 +6726,23 @@
         <v>6000</v>
       </c>
       <c r="J50" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K50" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L50" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M50" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N50" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O50" s="24">
@@ -6638,29 +6779,32 @@
         <v>500</v>
       </c>
       <c r="Z50" s="24">
-        <f t="shared" si="15"/>
-        <v>62730</v>
-      </c>
-      <c r="AA50" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="20">
         <f t="shared" si="16"/>
         <v>62730</v>
       </c>
+      <c r="AA50" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="20">
+        <f t="shared" si="17"/>
+        <v>62730</v>
+      </c>
       <c r="AC50" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD50" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE50" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF50" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF50" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
@@ -6691,27 +6835,27 @@
         <v>5000</v>
       </c>
       <c r="J51" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K51" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L51" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M51" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N51" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O51" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P51" s="24">
         <v>11330</v>
@@ -6744,29 +6888,32 @@
         <v>22105</v>
       </c>
       <c r="Z51" s="24">
-        <f t="shared" si="15"/>
-        <v>93855</v>
+        <f t="shared" si="16"/>
+        <v>94335</v>
       </c>
       <c r="AA51" s="24">
         <v>0</v>
       </c>
       <c r="AB51" s="20">
-        <f t="shared" si="16"/>
-        <v>93855</v>
+        <f t="shared" si="17"/>
+        <v>94335</v>
       </c>
       <c r="AC51" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD51" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE51" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF51" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF51" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
@@ -6797,23 +6944,23 @@
         <v>5000</v>
       </c>
       <c r="J52" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K52" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L52" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M52" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N52" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O52" s="24">
@@ -6850,29 +6997,32 @@
         <v>24395</v>
       </c>
       <c r="Z52" s="24">
-        <f t="shared" si="15"/>
-        <v>101165</v>
-      </c>
-      <c r="AA52" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="20">
         <f t="shared" si="16"/>
         <v>101165</v>
       </c>
+      <c r="AA52" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="20">
+        <f t="shared" si="17"/>
+        <v>101165</v>
+      </c>
       <c r="AC52" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD52" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE52" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF52" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF52" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="22" t="s">
@@ -6903,23 +7053,23 @@
         <v>0</v>
       </c>
       <c r="J53" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K53" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L53" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M53" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N53" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O53" s="24">
@@ -6956,29 +7106,32 @@
         <v>0</v>
       </c>
       <c r="Z53" s="24">
-        <f t="shared" si="15"/>
-        <v>51030</v>
-      </c>
-      <c r="AA53" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="20">
         <f t="shared" si="16"/>
         <v>51030</v>
       </c>
+      <c r="AA53" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="20">
+        <f t="shared" si="17"/>
+        <v>51030</v>
+      </c>
       <c r="AC53" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD53" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE53" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF53" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF53" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="22" t="s">
@@ -7009,23 +7162,23 @@
         <v>0</v>
       </c>
       <c r="J54" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K54" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L54" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M54" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N54" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O54" s="24">
@@ -7062,29 +7215,32 @@
         <v>2000</v>
       </c>
       <c r="Z54" s="24">
-        <f t="shared" si="15"/>
-        <v>45140</v>
-      </c>
-      <c r="AA54" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="20">
         <f t="shared" si="16"/>
         <v>45140</v>
       </c>
+      <c r="AA54" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="20">
+        <f t="shared" si="17"/>
+        <v>45140</v>
+      </c>
       <c r="AC54" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD54" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE54" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF54" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF54" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
@@ -7115,23 +7271,23 @@
         <v>0</v>
       </c>
       <c r="J55" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K55" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L55" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M55" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N55" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O55" s="24">
@@ -7168,29 +7324,32 @@
         <v>0</v>
       </c>
       <c r="Z55" s="24">
-        <f t="shared" si="15"/>
-        <v>56930</v>
-      </c>
-      <c r="AA55" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB55" s="20">
         <f t="shared" si="16"/>
         <v>56930</v>
       </c>
+      <c r="AA55" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="20">
+        <f t="shared" si="17"/>
+        <v>56930</v>
+      </c>
       <c r="AC55" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD55" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE55" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF55" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF55" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="22" t="s">
@@ -7221,27 +7380,27 @@
         <v>5000</v>
       </c>
       <c r="J56" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K56" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L56" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M56" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N56" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O56" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P56" s="24">
         <v>11330</v>
@@ -7274,29 +7433,32 @@
         <v>0</v>
       </c>
       <c r="Z56" s="24">
-        <f t="shared" si="15"/>
-        <v>76320</v>
+        <f t="shared" si="16"/>
+        <v>76800</v>
       </c>
       <c r="AA56" s="24">
         <v>0</v>
       </c>
       <c r="AB56" s="20">
-        <f t="shared" si="16"/>
-        <v>76320</v>
+        <f t="shared" si="17"/>
+        <v>76800</v>
       </c>
       <c r="AC56" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD56" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE56" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF56" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF56" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="22" t="s">
@@ -7327,23 +7489,23 @@
         <v>0</v>
       </c>
       <c r="J57" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K57" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19500</v>
       </c>
       <c r="L57" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M57" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N57" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O57" s="24">
@@ -7380,29 +7542,32 @@
         <v>0</v>
       </c>
       <c r="Z57" s="24">
-        <f t="shared" si="15"/>
-        <v>44430</v>
-      </c>
-      <c r="AA57" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="20">
         <f t="shared" si="16"/>
         <v>44430</v>
       </c>
+      <c r="AA57" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="20">
+        <f t="shared" si="17"/>
+        <v>44430</v>
+      </c>
       <c r="AC57" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD57" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE57" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF57" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF57" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="22" t="s">
@@ -7433,23 +7598,23 @@
         <v>0</v>
       </c>
       <c r="J58" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K58" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>24700</v>
       </c>
       <c r="L58" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M58" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N58" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O58" s="24">
@@ -7486,30 +7651,31 @@
         <v>1000</v>
       </c>
       <c r="Z58" s="24">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>50630</v>
       </c>
       <c r="AA58" s="24">
         <v>51930</v>
       </c>
       <c r="AB58" s="20">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1300</v>
       </c>
       <c r="AC58" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD58" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE58" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF58" s="25" t="s">
-        <v>259</v>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF58" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
@@ -7541,27 +7707,27 @@
         <v>5000</v>
       </c>
       <c r="J59" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K59" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L59" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M59" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N59" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O59" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P59" s="24">
         <v>11330</v>
@@ -7594,29 +7760,32 @@
         <v>550</v>
       </c>
       <c r="Z59" s="24">
-        <f t="shared" si="15"/>
-        <v>76870</v>
+        <f t="shared" si="16"/>
+        <v>77350</v>
       </c>
       <c r="AA59" s="24">
         <v>0</v>
       </c>
       <c r="AB59" s="20">
-        <f t="shared" si="16"/>
-        <v>76870</v>
+        <f t="shared" si="17"/>
+        <v>77350</v>
       </c>
       <c r="AC59" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD59" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE59" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF59" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF59" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="22" t="s">
@@ -7647,27 +7816,27 @@
         <v>5000</v>
       </c>
       <c r="J60" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K60" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L60" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M60" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N60" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O60" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P60" s="24">
         <v>13230</v>
@@ -7700,29 +7869,32 @@
         <v>0</v>
       </c>
       <c r="Z60" s="24">
-        <f t="shared" si="15"/>
-        <v>77060</v>
+        <f t="shared" si="16"/>
+        <v>77540</v>
       </c>
       <c r="AA60" s="24">
         <v>0</v>
       </c>
       <c r="AB60" s="20">
-        <f t="shared" si="16"/>
-        <v>77060</v>
+        <f t="shared" si="17"/>
+        <v>77540</v>
       </c>
       <c r="AC60" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD60" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE60" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF60" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF60" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="22" t="s">
@@ -7753,23 +7925,23 @@
         <v>6000</v>
       </c>
       <c r="J61" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K61" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L61" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M61" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N61" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O61" s="24">
@@ -7806,29 +7978,32 @@
         <v>0</v>
       </c>
       <c r="Z61" s="24">
-        <f t="shared" si="15"/>
-        <v>62230</v>
-      </c>
-      <c r="AA61" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="20">
         <f t="shared" si="16"/>
         <v>62230</v>
       </c>
+      <c r="AA61" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="20">
+        <f t="shared" si="17"/>
+        <v>62230</v>
+      </c>
       <c r="AC61" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD61" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE61" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF61" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF61" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" s="22" t="s">
@@ -7859,27 +8034,27 @@
         <v>5000</v>
       </c>
       <c r="J62" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K62" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L62" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M62" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N62" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O62" s="24">
-        <v>26850</v>
+        <v>27330</v>
       </c>
       <c r="P62" s="24">
         <v>13230</v>
@@ -7912,29 +8087,32 @@
         <v>0</v>
       </c>
       <c r="Z62" s="24">
-        <f t="shared" si="15"/>
-        <v>68830</v>
+        <f t="shared" si="16"/>
+        <v>69310</v>
       </c>
       <c r="AA62" s="24">
         <v>0</v>
       </c>
       <c r="AB62" s="20">
-        <f t="shared" si="16"/>
-        <v>68830</v>
+        <f t="shared" si="17"/>
+        <v>69310</v>
       </c>
       <c r="AC62" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD62" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE62" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF62" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF62" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="22" t="s">
@@ -7965,23 +8143,23 @@
         <v>6000</v>
       </c>
       <c r="J63" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K63" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>33000</v>
       </c>
       <c r="L63" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M63" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N63" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O63" s="24">
@@ -8018,29 +8196,32 @@
         <v>0</v>
       </c>
       <c r="Z63" s="24">
-        <f t="shared" si="15"/>
-        <v>79830</v>
-      </c>
-      <c r="AA63" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="20">
         <f t="shared" si="16"/>
         <v>79830</v>
       </c>
+      <c r="AA63" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="20">
+        <f t="shared" si="17"/>
+        <v>79830</v>
+      </c>
       <c r="AC63" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD63" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE63" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF63" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF63" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="22" t="s">
@@ -8071,23 +8252,23 @@
         <v>0</v>
       </c>
       <c r="J64" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K64" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13000</v>
       </c>
       <c r="L64" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M64" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>500</v>
       </c>
       <c r="N64" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O64" s="24">
@@ -8124,29 +8305,32 @@
         <v>0</v>
       </c>
       <c r="Z64" s="24">
-        <f t="shared" si="15"/>
-        <v>29640</v>
-      </c>
-      <c r="AA64" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB64" s="20">
         <f t="shared" si="16"/>
         <v>29640</v>
       </c>
+      <c r="AA64" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="20">
+        <f t="shared" si="17"/>
+        <v>29640</v>
+      </c>
       <c r="AC64" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD64" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE64" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF64" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF64" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="22" t="s">
@@ -8177,23 +8361,23 @@
         <v>0</v>
       </c>
       <c r="J65" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K65" s="24">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>13000</v>
       </c>
       <c r="L65" s="24">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M65" s="24">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N65" s="24">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O65" s="24">
@@ -8230,29 +8414,32 @@
         <v>8000</v>
       </c>
       <c r="Z65" s="24">
-        <f t="shared" si="15"/>
-        <v>45930</v>
-      </c>
-      <c r="AA65" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB65" s="20">
         <f t="shared" si="16"/>
         <v>45930</v>
       </c>
+      <c r="AA65" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="20">
+        <f t="shared" si="17"/>
+        <v>45930</v>
+      </c>
       <c r="AC65" s="24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD65" s="24" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE65" s="24" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AF65" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF65" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="22" t="s">
@@ -8283,23 +8470,23 @@
         <v>0</v>
       </c>
       <c r="J66" s="24">
-        <f t="shared" ref="J66:J97" si="20">(1-$D66)*E66</f>
+        <f t="shared" ref="J66:J97" si="18">(1-$D66)*E66</f>
         <v>0</v>
       </c>
       <c r="K66" s="24">
-        <f t="shared" ref="K66:K97" si="21">(1-$D66)*F66</f>
+        <f t="shared" ref="K66:K97" si="19">(1-$D66)*F66</f>
         <v>13000</v>
       </c>
       <c r="L66" s="24">
-        <f t="shared" ref="L66:L97" si="22">G66</f>
+        <f t="shared" ref="L66:L97" si="20">G66</f>
         <v>4000</v>
       </c>
       <c r="M66" s="24">
-        <f t="shared" ref="M66:M97" si="23">(1-$D66)*H66</f>
+        <f t="shared" ref="M66:M97" si="21">(1-$D66)*H66</f>
         <v>0</v>
       </c>
       <c r="N66" s="24">
-        <f t="shared" ref="N66:N97" si="24">(1-$D66)*I66</f>
+        <f t="shared" ref="N66:N97" si="22">(1-$D66)*I66</f>
         <v>0</v>
       </c>
       <c r="O66" s="24">
@@ -8336,29 +8523,32 @@
         <v>8000</v>
       </c>
       <c r="Z66" s="24">
-        <f t="shared" ref="Z66:Z97" si="25">SUM(J66:Y66)</f>
+        <f t="shared" ref="Z66:Z97" si="23">SUM(J66:Y66)</f>
         <v>45930</v>
       </c>
       <c r="AA66" s="24">
         <v>0</v>
       </c>
       <c r="AB66" s="20">
-        <f t="shared" ref="AB66:AB97" si="26">Z66-AA66</f>
+        <f t="shared" ref="AB66:AB97" si="24">Z66-AA66</f>
         <v>45930</v>
       </c>
       <c r="AC66" s="24" t="str">
-        <f t="shared" ref="AC66:AC97" si="27">IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD66" s="24" t="str">
-        <f t="shared" ref="AD66:AD97" si="28">IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE66" s="24" t="str">
-        <f t="shared" ref="AE66:AE97" si="29">IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
-        <v/>
-      </c>
-      <c r="AF66" s="25"/>
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AF66" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="22" t="s">
@@ -8389,27 +8579,27 @@
         <v>5000</v>
       </c>
       <c r="J67" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K67" s="24">
+        <f t="shared" si="19"/>
+        <v>14000</v>
+      </c>
+      <c r="L67" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K67" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M67" s="24">
         <f t="shared" si="21"/>
-        <v>14000</v>
-      </c>
-      <c r="L67" s="24">
+        <v>0</v>
+      </c>
+      <c r="N67" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M67" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N67" s="24">
-        <f t="shared" si="24"/>
         <v>2500</v>
       </c>
       <c r="O67" s="24">
-        <v>26850</v>
+        <v>27330</v>
       </c>
       <c r="P67" s="24">
         <v>13230</v>
@@ -8442,29 +8632,32 @@
         <v>8080</v>
       </c>
       <c r="Z67" s="24">
-        <f t="shared" si="25"/>
-        <v>68660</v>
+        <f t="shared" si="23"/>
+        <v>69140</v>
       </c>
       <c r="AA67" s="24">
         <v>0</v>
       </c>
       <c r="AB67" s="20">
-        <f t="shared" si="26"/>
-        <v>68660</v>
+        <f t="shared" si="24"/>
+        <v>69140</v>
       </c>
       <c r="AC67" s="24" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="AC67:AC120" si="25">IF(AND($T67=6000, ($T67+$W67-$AB67)&gt;=6000),T67,"")</f>
         <v/>
       </c>
       <c r="AD67" s="24" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="AD67:AD120" si="26">IF(AND($T67=8000, ($T67+$W67-$AB67)&gt;=8000),T67,"")</f>
         <v/>
       </c>
       <c r="AE67" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF67" s="25"/>
+        <f t="shared" ref="AE67:AE120" si="27">IF(($T67+$W67-$AB67)&gt;=$T67+8000,W67,"")</f>
+        <v/>
+      </c>
+      <c r="AF67" s="25" t="str">
+        <f t="shared" ref="AF67:AF120" si="28">IF(AB67&lt;=0,"BONUS","")</f>
+        <v/>
+      </c>
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="22" t="s">
@@ -8495,23 +8688,23 @@
         <v>0</v>
       </c>
       <c r="J68" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="24">
+        <f t="shared" si="19"/>
+        <v>26000</v>
+      </c>
+      <c r="L68" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K68" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M68" s="24">
         <f t="shared" si="21"/>
-        <v>26000</v>
-      </c>
-      <c r="L68" s="24">
+        <v>1000</v>
+      </c>
+      <c r="N68" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M68" s="24">
-        <f t="shared" si="23"/>
-        <v>1000</v>
-      </c>
-      <c r="N68" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O68" s="24">
@@ -8548,29 +8741,32 @@
         <v>0</v>
       </c>
       <c r="Z68" s="24">
+        <f t="shared" si="23"/>
+        <v>43140</v>
+      </c>
+      <c r="AA68" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="20">
+        <f t="shared" si="24"/>
+        <v>43140</v>
+      </c>
+      <c r="AC68" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>43140</v>
-      </c>
-      <c r="AA68" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB68" s="20">
+        <v/>
+      </c>
+      <c r="AD68" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>43140</v>
-      </c>
-      <c r="AC68" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE68" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD68" s="24" t="str">
+      <c r="AF68" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE68" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF68" s="25"/>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
@@ -8601,27 +8797,27 @@
         <v>0</v>
       </c>
       <c r="J69" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L69" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K69" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M69" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L69" s="24">
+        <v>0</v>
+      </c>
+      <c r="N69" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M69" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N69" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O69" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P69" s="24">
         <v>10730</v>
@@ -8654,29 +8850,32 @@
         <v>0</v>
       </c>
       <c r="Z69" s="24">
+        <f t="shared" si="23"/>
+        <v>65160</v>
+      </c>
+      <c r="AA69" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="20">
+        <f t="shared" si="24"/>
+        <v>65160</v>
+      </c>
+      <c r="AC69" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>64680</v>
-      </c>
-      <c r="AA69" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB69" s="20">
+        <v/>
+      </c>
+      <c r="AD69" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>64680</v>
-      </c>
-      <c r="AC69" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE69" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD69" s="24" t="str">
+      <c r="AF69" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE69" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF69" s="25"/>
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
@@ -8707,23 +8906,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L70" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K70" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M70" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L70" s="24">
+        <v>750</v>
+      </c>
+      <c r="N70" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M70" s="24">
-        <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="N70" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O70" s="24">
@@ -8760,29 +8959,32 @@
         <v>-500</v>
       </c>
       <c r="Z70" s="24">
+        <f t="shared" si="23"/>
+        <v>35890</v>
+      </c>
+      <c r="AA70" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="20">
+        <f t="shared" si="24"/>
+        <v>35890</v>
+      </c>
+      <c r="AC70" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>35890</v>
-      </c>
-      <c r="AA70" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="20">
+        <v/>
+      </c>
+      <c r="AD70" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>35890</v>
-      </c>
-      <c r="AC70" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE70" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD70" s="24" t="str">
+      <c r="AF70" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE70" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF70" s="25"/>
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
@@ -8813,23 +9015,23 @@
         <v>0</v>
       </c>
       <c r="J71" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K71" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L71" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K71" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M71" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L71" s="24">
+        <v>0</v>
+      </c>
+      <c r="N71" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M71" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N71" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O71" s="24">
@@ -8866,29 +9068,32 @@
         <v>0</v>
       </c>
       <c r="Z71" s="24">
+        <f t="shared" si="23"/>
+        <v>50430</v>
+      </c>
+      <c r="AA71" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="20">
+        <f t="shared" si="24"/>
+        <v>50430</v>
+      </c>
+      <c r="AC71" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>50430</v>
-      </c>
-      <c r="AA71" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB71" s="20">
+        <v/>
+      </c>
+      <c r="AD71" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>50430</v>
-      </c>
-      <c r="AC71" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE71" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD71" s="24" t="str">
+      <c r="AF71" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE71" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF71" s="25"/>
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
@@ -8919,23 +9124,23 @@
         <v>0</v>
       </c>
       <c r="J72" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L72" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K72" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M72" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L72" s="24">
+        <v>750</v>
+      </c>
+      <c r="N72" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M72" s="24">
-        <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="N72" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O72" s="24">
@@ -8972,29 +9177,32 @@
         <v>0</v>
       </c>
       <c r="Z72" s="24">
+        <f t="shared" si="23"/>
+        <v>36390</v>
+      </c>
+      <c r="AA72" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="20">
+        <f t="shared" si="24"/>
+        <v>36390</v>
+      </c>
+      <c r="AC72" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>36390</v>
-      </c>
-      <c r="AA72" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="20">
+        <v/>
+      </c>
+      <c r="AD72" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>36390</v>
-      </c>
-      <c r="AC72" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE72" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD72" s="24" t="str">
+      <c r="AF72" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE72" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF72" s="25"/>
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
@@ -9025,23 +9233,23 @@
         <v>0</v>
       </c>
       <c r="J73" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L73" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K73" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M73" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L73" s="24">
+        <v>0</v>
+      </c>
+      <c r="N73" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M73" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N73" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O73" s="24">
@@ -9078,29 +9286,32 @@
         <v>0</v>
       </c>
       <c r="Z73" s="24">
+        <f t="shared" si="23"/>
+        <v>50430</v>
+      </c>
+      <c r="AA73" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="20">
+        <f t="shared" si="24"/>
+        <v>50430</v>
+      </c>
+      <c r="AC73" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>50430</v>
-      </c>
-      <c r="AA73" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="20">
+        <v/>
+      </c>
+      <c r="AD73" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>50430</v>
-      </c>
-      <c r="AC73" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE73" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD73" s="24" t="str">
+      <c r="AF73" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE73" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF73" s="25"/>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
@@ -9131,27 +9342,27 @@
         <v>5000</v>
       </c>
       <c r="J74" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K74" s="24">
+        <f t="shared" si="19"/>
+        <v>21000</v>
+      </c>
+      <c r="L74" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K74" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M74" s="24">
         <f t="shared" si="21"/>
-        <v>21000</v>
-      </c>
-      <c r="L74" s="24">
+        <v>0</v>
+      </c>
+      <c r="N74" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M74" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N74" s="24">
-        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O74" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P74" s="24">
         <v>13230</v>
@@ -9184,29 +9395,32 @@
         <v>-695</v>
       </c>
       <c r="Z74" s="24">
+        <f t="shared" si="23"/>
+        <v>74595</v>
+      </c>
+      <c r="AA74" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="20">
+        <f t="shared" si="24"/>
+        <v>74595</v>
+      </c>
+      <c r="AC74" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>74115</v>
-      </c>
-      <c r="AA74" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB74" s="20">
+        <v/>
+      </c>
+      <c r="AD74" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>74115</v>
-      </c>
-      <c r="AC74" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE74" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD74" s="24" t="str">
+      <c r="AF74" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE74" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF74" s="25"/>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
@@ -9237,23 +9451,23 @@
         <v>0</v>
       </c>
       <c r="J75" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K75" s="24">
+        <f t="shared" si="19"/>
+        <v>26000</v>
+      </c>
+      <c r="L75" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K75" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M75" s="24">
         <f t="shared" si="21"/>
-        <v>26000</v>
-      </c>
-      <c r="L75" s="24">
+        <v>0</v>
+      </c>
+      <c r="N75" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M75" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N75" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O75" s="24">
@@ -9290,29 +9504,32 @@
         <v>14000</v>
       </c>
       <c r="Z75" s="24">
+        <f t="shared" si="23"/>
+        <v>64930</v>
+      </c>
+      <c r="AA75" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="20">
+        <f t="shared" si="24"/>
+        <v>64930</v>
+      </c>
+      <c r="AC75" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>64930</v>
-      </c>
-      <c r="AA75" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="20">
+        <v/>
+      </c>
+      <c r="AD75" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>64930</v>
-      </c>
-      <c r="AC75" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE75" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD75" s="24" t="str">
+      <c r="AF75" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE75" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF75" s="25"/>
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
@@ -9343,23 +9560,23 @@
         <v>6000</v>
       </c>
       <c r="J76" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K76" s="24">
+        <f t="shared" si="19"/>
+        <v>23100</v>
+      </c>
+      <c r="L76" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K76" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M76" s="24">
         <f t="shared" si="21"/>
-        <v>23100</v>
-      </c>
-      <c r="L76" s="24">
+        <v>1400</v>
+      </c>
+      <c r="N76" s="24">
         <f t="shared" si="22"/>
-        <v>5000</v>
-      </c>
-      <c r="M76" s="24">
-        <f t="shared" si="23"/>
-        <v>1400</v>
-      </c>
-      <c r="N76" s="24">
-        <f t="shared" si="24"/>
         <v>4200</v>
       </c>
       <c r="O76" s="24">
@@ -9396,29 +9613,32 @@
         <v>0</v>
       </c>
       <c r="Z76" s="24">
+        <f t="shared" si="23"/>
+        <v>67530</v>
+      </c>
+      <c r="AA76" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="20">
+        <f t="shared" si="24"/>
+        <v>67530</v>
+      </c>
+      <c r="AC76" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>67530</v>
-      </c>
-      <c r="AA76" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="20">
+        <v/>
+      </c>
+      <c r="AD76" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>67530</v>
-      </c>
-      <c r="AC76" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE76" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD76" s="24" t="str">
+      <c r="AF76" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE76" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF76" s="25"/>
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
@@ -9449,27 +9669,27 @@
         <v>5000</v>
       </c>
       <c r="J77" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="24">
+        <f t="shared" si="19"/>
+        <v>21000</v>
+      </c>
+      <c r="L77" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M77" s="24">
         <f t="shared" si="21"/>
-        <v>21000</v>
-      </c>
-      <c r="L77" s="24">
+        <v>0</v>
+      </c>
+      <c r="N77" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M77" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N77" s="24">
-        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O77" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P77" s="24">
         <v>13230</v>
@@ -9502,29 +9722,32 @@
         <v>450</v>
       </c>
       <c r="Z77" s="24">
+        <f t="shared" si="23"/>
+        <v>69740</v>
+      </c>
+      <c r="AA77" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="20">
+        <f t="shared" si="24"/>
+        <v>69740</v>
+      </c>
+      <c r="AC77" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>69260</v>
-      </c>
-      <c r="AA77" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="20">
+        <v/>
+      </c>
+      <c r="AD77" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>69260</v>
-      </c>
-      <c r="AC77" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE77" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD77" s="24" t="str">
+      <c r="AF77" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE77" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF77" s="25"/>
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
@@ -9555,23 +9778,23 @@
         <v>8000</v>
       </c>
       <c r="J78" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K78" s="24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L78" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K78" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M78" s="24">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="L78" s="24">
+      <c r="N78" s="24">
         <f t="shared" si="22"/>
-        <v>5000</v>
-      </c>
-      <c r="M78" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N78" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O78" s="24">
@@ -9608,29 +9831,32 @@
         <v>0</v>
       </c>
       <c r="Z78" s="24">
+        <f t="shared" si="23"/>
+        <v>31210</v>
+      </c>
+      <c r="AA78" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="20">
+        <f t="shared" si="24"/>
+        <v>31210</v>
+      </c>
+      <c r="AC78" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>31210</v>
-      </c>
-      <c r="AA78" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="20">
+        <v/>
+      </c>
+      <c r="AD78" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>31210</v>
-      </c>
-      <c r="AC78" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE78" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD78" s="24" t="str">
+      <c r="AF78" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE78" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF78" s="25"/>
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
@@ -9661,23 +9887,23 @@
         <v>0</v>
       </c>
       <c r="J79" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K79" s="24">
+        <f t="shared" si="19"/>
+        <v>26000</v>
+      </c>
+      <c r="L79" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K79" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M79" s="24">
         <f t="shared" si="21"/>
-        <v>26000</v>
-      </c>
-      <c r="L79" s="24">
+        <v>0</v>
+      </c>
+      <c r="N79" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M79" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N79" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O79" s="24">
@@ -9687,7 +9913,7 @@
         <v>7550</v>
       </c>
       <c r="Q79" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="R79" s="24">
         <v>0</v>
@@ -9714,29 +9940,32 @@
         <v>7000</v>
       </c>
       <c r="Z79" s="24">
+        <f t="shared" si="23"/>
+        <v>65930</v>
+      </c>
+      <c r="AA79" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="20">
+        <f t="shared" si="24"/>
+        <v>65930</v>
+      </c>
+      <c r="AC79" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>57930</v>
-      </c>
-      <c r="AA79" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="20">
+        <v/>
+      </c>
+      <c r="AD79" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>57930</v>
-      </c>
-      <c r="AC79" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE79" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD79" s="24" t="str">
+      <c r="AF79" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE79" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF79" s="25"/>
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
@@ -9767,23 +9996,23 @@
         <v>0</v>
       </c>
       <c r="J80" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K80" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L80" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K80" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M80" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L80" s="24">
+        <v>750</v>
+      </c>
+      <c r="N80" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M80" s="24">
-        <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="N80" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O80" s="24">
@@ -9820,29 +10049,32 @@
         <v>19200</v>
       </c>
       <c r="Z80" s="24">
+        <f t="shared" si="23"/>
+        <v>55590</v>
+      </c>
+      <c r="AA80" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="20">
+        <f t="shared" si="24"/>
+        <v>55590</v>
+      </c>
+      <c r="AC80" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>55590</v>
-      </c>
-      <c r="AA80" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="20">
+        <v/>
+      </c>
+      <c r="AD80" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>55590</v>
-      </c>
-      <c r="AC80" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE80" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD80" s="24" t="str">
+      <c r="AF80" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE80" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF80" s="25"/>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
@@ -9873,23 +10105,23 @@
         <v>0</v>
       </c>
       <c r="J81" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K81" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L81" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K81" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M81" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L81" s="24">
+        <v>750</v>
+      </c>
+      <c r="N81" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M81" s="24">
-        <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="N81" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O81" s="24">
@@ -9926,29 +10158,32 @@
         <v>19200</v>
       </c>
       <c r="Z81" s="24">
+        <f t="shared" si="23"/>
+        <v>55590</v>
+      </c>
+      <c r="AA81" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="20">
+        <f t="shared" si="24"/>
+        <v>55590</v>
+      </c>
+      <c r="AC81" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>55590</v>
-      </c>
-      <c r="AA81" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="20">
+        <v/>
+      </c>
+      <c r="AD81" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>55590</v>
-      </c>
-      <c r="AC81" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE81" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD81" s="24" t="str">
+      <c r="AF81" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE81" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF81" s="25"/>
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
@@ -9979,23 +10214,23 @@
         <v>8000</v>
       </c>
       <c r="J82" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K82" s="24">
+        <f t="shared" si="19"/>
+        <v>40000</v>
+      </c>
+      <c r="L82" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K82" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M82" s="24">
         <f t="shared" si="21"/>
-        <v>40000</v>
-      </c>
-      <c r="L82" s="24">
+        <v>2000</v>
+      </c>
+      <c r="N82" s="24">
         <f t="shared" si="22"/>
-        <v>5000</v>
-      </c>
-      <c r="M82" s="24">
-        <f t="shared" si="23"/>
-        <v>2000</v>
-      </c>
-      <c r="N82" s="24">
-        <f t="shared" si="24"/>
         <v>8000</v>
       </c>
       <c r="O82" s="24">
@@ -10032,29 +10267,32 @@
         <v>5830</v>
       </c>
       <c r="Z82" s="24">
+        <f t="shared" si="23"/>
+        <v>87040</v>
+      </c>
+      <c r="AA82" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="20">
+        <f t="shared" si="24"/>
+        <v>87040</v>
+      </c>
+      <c r="AC82" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>87040</v>
-      </c>
-      <c r="AA82" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB82" s="20">
+        <v/>
+      </c>
+      <c r="AD82" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>87040</v>
-      </c>
-      <c r="AC82" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE82" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD82" s="24" t="str">
+      <c r="AF82" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE82" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF82" s="25"/>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
@@ -10085,23 +10323,23 @@
         <v>0</v>
       </c>
       <c r="J83" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K83" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L83" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M83" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L83" s="24">
+        <v>750</v>
+      </c>
+      <c r="N83" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M83" s="24">
-        <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="N83" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O83" s="24">
@@ -10138,29 +10376,32 @@
         <v>0</v>
       </c>
       <c r="Z83" s="24">
+        <f t="shared" si="23"/>
+        <v>60390</v>
+      </c>
+      <c r="AA83" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="20">
+        <f t="shared" si="24"/>
+        <v>60390</v>
+      </c>
+      <c r="AC83" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>60390</v>
-      </c>
-      <c r="AA83" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="20">
+        <v/>
+      </c>
+      <c r="AD83" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>60390</v>
-      </c>
-      <c r="AC83" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE83" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD83" s="24" t="str">
+      <c r="AF83" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE83" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF83" s="25"/>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
@@ -10191,33 +10432,33 @@
         <v>5000</v>
       </c>
       <c r="J84" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K84" s="24">
+        <f t="shared" si="19"/>
+        <v>21000</v>
+      </c>
+      <c r="L84" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K84" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M84" s="24">
         <f t="shared" si="21"/>
-        <v>21000</v>
-      </c>
-      <c r="L84" s="24">
+        <v>1875</v>
+      </c>
+      <c r="N84" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M84" s="24">
-        <f t="shared" si="23"/>
-        <v>1875</v>
-      </c>
-      <c r="N84" s="24">
-        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O84" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P84" s="24">
         <v>11330</v>
       </c>
       <c r="Q84" s="24">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="R84" s="24">
         <v>0</v>
@@ -10244,29 +10485,32 @@
         <v>0</v>
       </c>
       <c r="Z84" s="24">
+        <f t="shared" si="23"/>
+        <v>83925</v>
+      </c>
+      <c r="AA84" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="20">
+        <f t="shared" si="24"/>
+        <v>83925</v>
+      </c>
+      <c r="AC84" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>67445</v>
-      </c>
-      <c r="AA84" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB84" s="20">
+        <v/>
+      </c>
+      <c r="AD84" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>67445</v>
-      </c>
-      <c r="AC84" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE84" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD84" s="24" t="str">
+      <c r="AF84" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE84" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF84" s="25"/>
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="22" t="s">
@@ -10297,23 +10541,23 @@
         <v>0</v>
       </c>
       <c r="J85" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="24">
+        <f t="shared" si="19"/>
+        <v>26000</v>
+      </c>
+      <c r="L85" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M85" s="24">
         <f t="shared" si="21"/>
-        <v>26000</v>
-      </c>
-      <c r="L85" s="24">
+        <v>0</v>
+      </c>
+      <c r="N85" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M85" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N85" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O85" s="24">
@@ -10350,29 +10594,32 @@
         <v>-3030</v>
       </c>
       <c r="Z85" s="24">
+        <f t="shared" si="23"/>
+        <v>47900</v>
+      </c>
+      <c r="AA85" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="20">
+        <f t="shared" si="24"/>
+        <v>47900</v>
+      </c>
+      <c r="AC85" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>47900</v>
-      </c>
-      <c r="AA85" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB85" s="20">
+        <v/>
+      </c>
+      <c r="AD85" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>47900</v>
-      </c>
-      <c r="AC85" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE85" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD85" s="24" t="str">
+      <c r="AF85" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE85" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF85" s="25"/>
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="22" t="s">
@@ -10403,23 +10650,23 @@
         <v>0</v>
       </c>
       <c r="J86" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K86" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L86" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K86" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M86" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L86" s="24">
+        <v>750</v>
+      </c>
+      <c r="N86" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M86" s="24">
-        <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="N86" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O86" s="24">
@@ -10456,29 +10703,32 @@
         <v>3500</v>
       </c>
       <c r="Z86" s="24">
+        <f t="shared" si="23"/>
+        <v>39890</v>
+      </c>
+      <c r="AA86" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="20">
+        <f t="shared" si="24"/>
+        <v>39890</v>
+      </c>
+      <c r="AC86" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>39890</v>
-      </c>
-      <c r="AA86" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB86" s="20">
+        <v/>
+      </c>
+      <c r="AD86" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>39890</v>
-      </c>
-      <c r="AC86" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE86" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD86" s="24" t="str">
+      <c r="AF86" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE86" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF86" s="25"/>
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="22" t="s">
@@ -10509,23 +10759,23 @@
         <v>0</v>
       </c>
       <c r="J87" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K87" s="24">
+        <f t="shared" si="19"/>
+        <v>26000</v>
+      </c>
+      <c r="L87" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K87" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M87" s="24">
         <f t="shared" si="21"/>
-        <v>26000</v>
-      </c>
-      <c r="L87" s="24">
+        <v>0</v>
+      </c>
+      <c r="N87" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M87" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N87" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O87" s="24">
@@ -10562,29 +10812,32 @@
         <v>0</v>
       </c>
       <c r="Z87" s="24">
+        <f t="shared" si="23"/>
+        <v>56930</v>
+      </c>
+      <c r="AA87" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="20">
+        <f t="shared" si="24"/>
+        <v>56930</v>
+      </c>
+      <c r="AC87" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>56930</v>
-      </c>
-      <c r="AA87" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB87" s="20">
+        <v/>
+      </c>
+      <c r="AD87" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>56930</v>
-      </c>
-      <c r="AC87" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE87" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD87" s="24" t="str">
+      <c r="AF87" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE87" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF87" s="25"/>
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="22" t="s">
@@ -10615,23 +10868,23 @@
         <v>0</v>
       </c>
       <c r="J88" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K88" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L88" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K88" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M88" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L88" s="24">
+        <v>0</v>
+      </c>
+      <c r="N88" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M88" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N88" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O88" s="24">
@@ -10668,29 +10921,32 @@
         <v>0</v>
       </c>
       <c r="Z88" s="24">
+        <f t="shared" si="23"/>
+        <v>50430</v>
+      </c>
+      <c r="AA88" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="20">
+        <f t="shared" si="24"/>
+        <v>50430</v>
+      </c>
+      <c r="AC88" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>50430</v>
-      </c>
-      <c r="AA88" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB88" s="20">
+        <v/>
+      </c>
+      <c r="AD88" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>50430</v>
-      </c>
-      <c r="AC88" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE88" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD88" s="24" t="str">
+      <c r="AF88" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE88" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF88" s="25"/>
     </row>
     <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="22" t="s">
@@ -10721,27 +10977,27 @@
         <v>5000</v>
       </c>
       <c r="J89" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K89" s="24">
+        <f t="shared" si="19"/>
+        <v>21000</v>
+      </c>
+      <c r="L89" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K89" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M89" s="24">
         <f t="shared" si="21"/>
-        <v>21000</v>
-      </c>
-      <c r="L89" s="24">
+        <v>1875</v>
+      </c>
+      <c r="N89" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M89" s="24">
-        <f t="shared" si="23"/>
-        <v>1875</v>
-      </c>
-      <c r="N89" s="24">
-        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O89" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P89" s="24">
         <v>11330</v>
@@ -10774,29 +11030,32 @@
         <v>0</v>
       </c>
       <c r="Z89" s="24">
+        <f t="shared" si="23"/>
+        <v>73925</v>
+      </c>
+      <c r="AA89" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="20">
+        <f t="shared" si="24"/>
+        <v>73925</v>
+      </c>
+      <c r="AC89" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>73445</v>
-      </c>
-      <c r="AA89" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="20">
+        <v/>
+      </c>
+      <c r="AD89" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>73445</v>
-      </c>
-      <c r="AC89" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE89" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD89" s="24" t="str">
+      <c r="AF89" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE89" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF89" s="25"/>
     </row>
     <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="22" t="s">
@@ -10827,27 +11086,27 @@
         <v>5000</v>
       </c>
       <c r="J90" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K90" s="24">
+        <f t="shared" si="19"/>
+        <v>21000</v>
+      </c>
+      <c r="L90" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K90" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M90" s="24">
         <f t="shared" si="21"/>
-        <v>21000</v>
-      </c>
-      <c r="L90" s="24">
+        <v>0</v>
+      </c>
+      <c r="N90" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M90" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N90" s="24">
-        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O90" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P90" s="24">
         <v>13230</v>
@@ -10880,29 +11139,32 @@
         <v>0</v>
       </c>
       <c r="Z90" s="24">
+        <f t="shared" si="23"/>
+        <v>75290</v>
+      </c>
+      <c r="AA90" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="20">
+        <f t="shared" si="24"/>
+        <v>75290</v>
+      </c>
+      <c r="AC90" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>74810</v>
-      </c>
-      <c r="AA90" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB90" s="20">
+        <v/>
+      </c>
+      <c r="AD90" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>74810</v>
-      </c>
-      <c r="AC90" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE90" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD90" s="24" t="str">
+      <c r="AF90" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE90" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF90" s="25"/>
     </row>
     <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="22" t="s">
@@ -10933,27 +11195,27 @@
         <v>5000</v>
       </c>
       <c r="J91" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K91" s="24">
+        <f t="shared" si="19"/>
+        <v>28000</v>
+      </c>
+      <c r="L91" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K91" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M91" s="24">
         <f t="shared" si="21"/>
-        <v>28000</v>
-      </c>
-      <c r="L91" s="24">
+        <v>2500</v>
+      </c>
+      <c r="N91" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M91" s="24">
-        <f t="shared" si="23"/>
-        <v>2500</v>
-      </c>
-      <c r="N91" s="24">
-        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="O91" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P91" s="24">
         <v>11330</v>
@@ -10986,29 +11248,32 @@
         <v>0</v>
       </c>
       <c r="Z91" s="24">
+        <f t="shared" si="23"/>
+        <v>76800</v>
+      </c>
+      <c r="AA91" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="20">
+        <f t="shared" si="24"/>
+        <v>76800</v>
+      </c>
+      <c r="AC91" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>76320</v>
-      </c>
-      <c r="AA91" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="20">
+        <v/>
+      </c>
+      <c r="AD91" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>76320</v>
-      </c>
-      <c r="AC91" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE91" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD91" s="24" t="str">
+      <c r="AF91" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE91" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF91" s="25"/>
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="22" t="s">
@@ -11039,27 +11304,27 @@
         <v>5000</v>
       </c>
       <c r="J92" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K92" s="24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L92" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M92" s="24">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="L92" s="24">
+      <c r="N92" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M92" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N92" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O92" s="24">
-        <v>26850</v>
+        <v>27330</v>
       </c>
       <c r="P92" s="24">
         <v>13230</v>
@@ -11092,29 +11357,32 @@
         <v>0</v>
       </c>
       <c r="Z92" s="24">
+        <f t="shared" si="23"/>
+        <v>50560</v>
+      </c>
+      <c r="AA92" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="20">
+        <f t="shared" si="24"/>
+        <v>50560</v>
+      </c>
+      <c r="AC92" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>50080</v>
-      </c>
-      <c r="AA92" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB92" s="20">
+        <v/>
+      </c>
+      <c r="AD92" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>50080</v>
-      </c>
-      <c r="AC92" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE92" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD92" s="24" t="str">
+      <c r="AF92" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE92" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF92" s="25"/>
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="22" t="s">
@@ -11145,23 +11413,23 @@
         <v>0</v>
       </c>
       <c r="J93" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K93" s="24">
+        <f t="shared" si="19"/>
+        <v>19500</v>
+      </c>
+      <c r="L93" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K93" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M93" s="24">
         <f t="shared" si="21"/>
-        <v>19500</v>
-      </c>
-      <c r="L93" s="24">
+        <v>750</v>
+      </c>
+      <c r="N93" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M93" s="24">
-        <f t="shared" si="23"/>
-        <v>750</v>
-      </c>
-      <c r="N93" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O93" s="24">
@@ -11198,29 +11466,32 @@
         <v>65</v>
       </c>
       <c r="Z93" s="24">
+        <f t="shared" si="23"/>
+        <v>50345</v>
+      </c>
+      <c r="AA93" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="20">
+        <f t="shared" si="24"/>
+        <v>50345</v>
+      </c>
+      <c r="AC93" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>50345</v>
-      </c>
-      <c r="AA93" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="20">
+        <v/>
+      </c>
+      <c r="AD93" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>50345</v>
-      </c>
-      <c r="AC93" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE93" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD93" s="24" t="str">
+      <c r="AF93" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE93" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF93" s="25"/>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="22" t="s">
@@ -11251,27 +11522,27 @@
         <v>5000</v>
       </c>
       <c r="J94" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K94" s="24">
+        <f t="shared" si="19"/>
+        <v>21000</v>
+      </c>
+      <c r="L94" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K94" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M94" s="24">
         <f t="shared" si="21"/>
-        <v>21000</v>
-      </c>
-      <c r="L94" s="24">
+        <v>1875</v>
+      </c>
+      <c r="N94" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M94" s="24">
-        <f t="shared" si="23"/>
-        <v>1875</v>
-      </c>
-      <c r="N94" s="24">
-        <f t="shared" si="24"/>
         <v>3750</v>
       </c>
       <c r="O94" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P94" s="24">
         <v>11330</v>
@@ -11304,29 +11575,32 @@
         <v>0</v>
       </c>
       <c r="Z94" s="24">
+        <f t="shared" si="23"/>
+        <v>73925</v>
+      </c>
+      <c r="AA94" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="20">
+        <f t="shared" si="24"/>
+        <v>73925</v>
+      </c>
+      <c r="AC94" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>73445</v>
-      </c>
-      <c r="AA94" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="20">
+        <v/>
+      </c>
+      <c r="AD94" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>73445</v>
-      </c>
-      <c r="AC94" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE94" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD94" s="24" t="str">
+      <c r="AF94" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE94" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF94" s="25"/>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="22" t="s">
@@ -11357,23 +11631,23 @@
         <v>6000</v>
       </c>
       <c r="J95" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K95" s="24">
+        <f t="shared" si="19"/>
+        <v>23100</v>
+      </c>
+      <c r="L95" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K95" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M95" s="24">
         <f t="shared" si="21"/>
-        <v>23100</v>
-      </c>
-      <c r="L95" s="24">
+        <v>1400</v>
+      </c>
+      <c r="N95" s="24">
         <f t="shared" si="22"/>
-        <v>5000</v>
-      </c>
-      <c r="M95" s="24">
-        <f t="shared" si="23"/>
-        <v>1400</v>
-      </c>
-      <c r="N95" s="24">
-        <f t="shared" si="24"/>
         <v>4200</v>
       </c>
       <c r="O95" s="24">
@@ -11410,29 +11684,32 @@
         <v>0</v>
       </c>
       <c r="Z95" s="24">
+        <f t="shared" si="23"/>
+        <v>70430</v>
+      </c>
+      <c r="AA95" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="20">
+        <f t="shared" si="24"/>
+        <v>70430</v>
+      </c>
+      <c r="AC95" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>70430</v>
-      </c>
-      <c r="AA95" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB95" s="20">
+        <v/>
+      </c>
+      <c r="AD95" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>70430</v>
-      </c>
-      <c r="AC95" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE95" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD95" s="24" t="str">
+      <c r="AF95" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE95" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF95" s="25"/>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="22" t="s">
@@ -11463,23 +11740,23 @@
         <v>0</v>
       </c>
       <c r="J96" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K96" s="24">
+        <f t="shared" si="19"/>
+        <v>26000</v>
+      </c>
+      <c r="L96" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K96" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M96" s="24">
         <f t="shared" si="21"/>
-        <v>26000</v>
-      </c>
-      <c r="L96" s="24">
+        <v>1000</v>
+      </c>
+      <c r="N96" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M96" s="24">
-        <f t="shared" si="23"/>
-        <v>1000</v>
-      </c>
-      <c r="N96" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O96" s="24">
@@ -11516,29 +11793,32 @@
         <v>-10000</v>
       </c>
       <c r="Z96" s="24">
+        <f t="shared" si="23"/>
+        <v>33140</v>
+      </c>
+      <c r="AA96" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="20">
+        <f t="shared" si="24"/>
+        <v>33140</v>
+      </c>
+      <c r="AC96" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>33140</v>
-      </c>
-      <c r="AA96" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="20">
+        <v/>
+      </c>
+      <c r="AD96" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>33140</v>
-      </c>
-      <c r="AC96" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE96" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD96" s="24" t="str">
+      <c r="AF96" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE96" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF96" s="25"/>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="22" t="s">
@@ -11569,23 +11849,23 @@
         <v>0</v>
       </c>
       <c r="J97" s="24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="K97" s="24">
+        <f t="shared" si="19"/>
+        <v>13000</v>
+      </c>
+      <c r="L97" s="24">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K97" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M97" s="24">
         <f t="shared" si="21"/>
-        <v>13000</v>
-      </c>
-      <c r="L97" s="24">
+        <v>0</v>
+      </c>
+      <c r="N97" s="24">
         <f t="shared" si="22"/>
-        <v>4000</v>
-      </c>
-      <c r="M97" s="24">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="N97" s="24">
-        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O97" s="24">
@@ -11622,29 +11902,32 @@
         <v>8000</v>
       </c>
       <c r="Z97" s="24">
+        <f t="shared" si="23"/>
+        <v>45930</v>
+      </c>
+      <c r="AA97" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="20">
+        <f t="shared" si="24"/>
+        <v>45930</v>
+      </c>
+      <c r="AC97" s="24" t="str">
         <f t="shared" si="25"/>
-        <v>45930</v>
-      </c>
-      <c r="AA97" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB97" s="20">
+        <v/>
+      </c>
+      <c r="AD97" s="24" t="str">
         <f t="shared" si="26"/>
-        <v>45930</v>
-      </c>
-      <c r="AC97" s="24" t="str">
+        <v/>
+      </c>
+      <c r="AE97" s="24" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="AD97" s="24" t="str">
+      <c r="AF97" s="25" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="AE97" s="24" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AF97" s="25"/>
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="s">
@@ -11675,27 +11958,27 @@
         <v>5000</v>
       </c>
       <c r="J98" s="24">
-        <f t="shared" ref="J98:J120" si="30">(1-$D98)*E98</f>
+        <f t="shared" ref="J98:J120" si="29">(1-$D98)*E98</f>
         <v>0</v>
       </c>
       <c r="K98" s="24">
-        <f t="shared" ref="K98:K120" si="31">(1-$D98)*F98</f>
+        <f t="shared" ref="K98:K120" si="30">(1-$D98)*F98</f>
         <v>14000</v>
       </c>
       <c r="L98" s="24">
-        <f t="shared" ref="L98:L120" si="32">G98</f>
+        <f t="shared" ref="L98:L120" si="31">G98</f>
         <v>4000</v>
       </c>
       <c r="M98" s="24">
-        <f t="shared" ref="M98:M120" si="33">(1-$D98)*H98</f>
+        <f t="shared" ref="M98:M120" si="32">(1-$D98)*H98</f>
         <v>0</v>
       </c>
       <c r="N98" s="24">
-        <f t="shared" ref="N98:N120" si="34">(1-$D98)*I98</f>
+        <f t="shared" ref="N98:N120" si="33">(1-$D98)*I98</f>
         <v>2500</v>
       </c>
       <c r="O98" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P98" s="24">
         <v>11330</v>
@@ -11728,29 +12011,32 @@
         <v>0</v>
       </c>
       <c r="Z98" s="24">
-        <f t="shared" ref="Z98:Z120" si="35">SUM(J98:Y98)</f>
-        <v>57500</v>
+        <f t="shared" ref="Z98:Z129" si="34">SUM(J98:Y98)</f>
+        <v>57980</v>
       </c>
       <c r="AA98" s="24">
         <v>0</v>
       </c>
       <c r="AB98" s="20">
-        <f t="shared" ref="AB98:AB120" si="36">Z98-AA98</f>
-        <v>57500</v>
+        <f t="shared" ref="AB98:AB129" si="35">Z98-AA98</f>
+        <v>57980</v>
       </c>
       <c r="AC98" s="24" t="str">
-        <f t="shared" ref="AC98:AC120" si="37">IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD98" s="24" t="str">
-        <f t="shared" ref="AD98:AD120" si="38">IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE98" s="24" t="str">
-        <f t="shared" ref="AE98:AE120" si="39">IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
-        <v/>
-      </c>
-      <c r="AF98" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF98" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="22" t="s">
@@ -11781,23 +12067,23 @@
         <v>6000</v>
       </c>
       <c r="J99" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K99" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K99" s="24">
+        <v>16500</v>
+      </c>
+      <c r="L99" s="24">
         <f t="shared" si="31"/>
-        <v>16500</v>
-      </c>
-      <c r="L99" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M99" s="24">
         <f t="shared" si="32"/>
-        <v>5000</v>
-      </c>
-      <c r="M99" s="24">
+        <v>1000</v>
+      </c>
+      <c r="N99" s="24">
         <f t="shared" si="33"/>
-        <v>1000</v>
-      </c>
-      <c r="N99" s="24">
-        <f t="shared" si="34"/>
         <v>3000</v>
       </c>
       <c r="O99" s="24">
@@ -11834,29 +12120,32 @@
         <v>-3145</v>
       </c>
       <c r="Z99" s="24">
+        <f t="shared" si="34"/>
+        <v>67085</v>
+      </c>
+      <c r="AA99" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="20">
         <f t="shared" si="35"/>
         <v>67085</v>
       </c>
-      <c r="AA99" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB99" s="20">
-        <f t="shared" si="36"/>
-        <v>67085</v>
-      </c>
       <c r="AC99" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD99" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE99" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF99" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF99" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="22" t="s">
@@ -11887,23 +12176,23 @@
         <v>0</v>
       </c>
       <c r="J100" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K100" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K100" s="24">
+        <v>19500</v>
+      </c>
+      <c r="L100" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
-      </c>
-      <c r="L100" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M100" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M100" s="24">
+        <v>0</v>
+      </c>
+      <c r="N100" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N100" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O100" s="24">
@@ -11913,7 +12202,7 @@
         <v>7550</v>
       </c>
       <c r="Q100" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="R100" s="24">
         <v>0</v>
@@ -11940,29 +12229,32 @@
         <v>0</v>
       </c>
       <c r="Z100" s="24">
+        <f t="shared" si="34"/>
+        <v>52430</v>
+      </c>
+      <c r="AA100" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="20">
         <f t="shared" si="35"/>
-        <v>44430</v>
-      </c>
-      <c r="AA100" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="20">
-        <f t="shared" si="36"/>
-        <v>44430</v>
+        <v>52430</v>
       </c>
       <c r="AC100" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD100" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE100" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF100" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF100" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" s="22" t="s">
@@ -11993,33 +12285,33 @@
         <v>5000</v>
       </c>
       <c r="J101" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K101" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K101" s="24">
+        <v>21000</v>
+      </c>
+      <c r="L101" s="24">
         <f t="shared" si="31"/>
-        <v>21000</v>
-      </c>
-      <c r="L101" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M101" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M101" s="24">
+        <v>0</v>
+      </c>
+      <c r="N101" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N101" s="24">
-        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O101" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P101" s="24">
         <v>13230</v>
       </c>
       <c r="Q101" s="24">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="R101" s="24">
         <v>0</v>
@@ -12046,29 +12338,32 @@
         <v>0</v>
       </c>
       <c r="Z101" s="24">
+        <f t="shared" si="34"/>
+        <v>77290</v>
+      </c>
+      <c r="AA101" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="20">
         <f t="shared" si="35"/>
-        <v>68810</v>
-      </c>
-      <c r="AA101" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="20">
-        <f t="shared" si="36"/>
-        <v>68810</v>
+        <v>77290</v>
       </c>
       <c r="AC101" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD101" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE101" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF101" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF101" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" s="22" t="s">
@@ -12099,27 +12394,27 @@
         <v>0</v>
       </c>
       <c r="J102" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K102" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K102" s="24">
+        <v>19500</v>
+      </c>
+      <c r="L102" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
-      </c>
-      <c r="L102" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M102" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M102" s="24">
+        <v>0</v>
+      </c>
+      <c r="N102" s="24">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="N102" s="24">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
       <c r="O102" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P102" s="24">
         <v>10730</v>
@@ -12152,29 +12447,32 @@
         <v>0</v>
       </c>
       <c r="Z102" s="24">
+        <f t="shared" si="34"/>
+        <v>65160</v>
+      </c>
+      <c r="AA102" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="20">
         <f t="shared" si="35"/>
-        <v>64680</v>
-      </c>
-      <c r="AA102" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="20">
-        <f t="shared" si="36"/>
-        <v>64680</v>
+        <v>65160</v>
       </c>
       <c r="AC102" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD102" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE102" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF102" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF102" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" s="22" t="s">
@@ -12205,27 +12503,27 @@
         <v>5000</v>
       </c>
       <c r="J103" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K103" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="24">
+        <v>21000</v>
+      </c>
+      <c r="L103" s="24">
         <f t="shared" si="31"/>
-        <v>21000</v>
-      </c>
-      <c r="L103" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M103" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M103" s="24">
+        <v>0</v>
+      </c>
+      <c r="N103" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N103" s="24">
-        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O103" s="24">
-        <v>26830</v>
+        <v>27310</v>
       </c>
       <c r="P103" s="24">
         <v>13230</v>
@@ -12258,29 +12556,32 @@
         <v>0</v>
       </c>
       <c r="Z103" s="24">
+        <f t="shared" si="34"/>
+        <v>75290</v>
+      </c>
+      <c r="AA103" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="20">
         <f t="shared" si="35"/>
-        <v>74810</v>
-      </c>
-      <c r="AA103" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB103" s="20">
-        <f t="shared" si="36"/>
-        <v>74810</v>
+        <v>75290</v>
       </c>
       <c r="AC103" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD103" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE103" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF103" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF103" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="s">
@@ -12311,23 +12612,23 @@
         <v>0</v>
       </c>
       <c r="J104" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K104" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K104" s="24">
+        <v>19500</v>
+      </c>
+      <c r="L104" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
-      </c>
-      <c r="L104" s="24">
+        <v>2000</v>
+      </c>
+      <c r="M104" s="24">
         <f t="shared" si="32"/>
-        <v>2000</v>
-      </c>
-      <c r="M104" s="24">
+        <v>0</v>
+      </c>
+      <c r="N104" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N104" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O104" s="24">
@@ -12364,29 +12665,32 @@
         <v>0</v>
       </c>
       <c r="Z104" s="24">
+        <f t="shared" si="34"/>
+        <v>24550</v>
+      </c>
+      <c r="AA104" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="20">
         <f t="shared" si="35"/>
         <v>24550</v>
       </c>
-      <c r="AA104" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB104" s="20">
-        <f t="shared" si="36"/>
-        <v>24550</v>
-      </c>
       <c r="AC104" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD104" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE104" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF104" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF104" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" s="22" t="s">
@@ -12417,27 +12721,27 @@
         <v>0</v>
       </c>
       <c r="J105" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K105" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K105" s="24">
+        <v>19500</v>
+      </c>
+      <c r="L105" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
-      </c>
-      <c r="L105" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M105" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M105" s="24">
+        <v>0</v>
+      </c>
+      <c r="N105" s="24">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="N105" s="24">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
       <c r="O105" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P105" s="24">
         <v>10730</v>
@@ -12470,29 +12774,32 @@
         <v>0</v>
       </c>
       <c r="Z105" s="24">
+        <f t="shared" si="34"/>
+        <v>65160</v>
+      </c>
+      <c r="AA105" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="20">
         <f t="shared" si="35"/>
-        <v>64680</v>
-      </c>
-      <c r="AA105" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB105" s="20">
-        <f t="shared" si="36"/>
-        <v>64680</v>
+        <v>65160</v>
       </c>
       <c r="AC105" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD105" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE105" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF105" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF105" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" s="22" t="s">
@@ -12523,27 +12830,27 @@
         <v>0</v>
       </c>
       <c r="J106" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K106" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K106" s="24">
+        <v>26000</v>
+      </c>
+      <c r="L106" s="24">
         <f t="shared" si="31"/>
-        <v>26000</v>
-      </c>
-      <c r="L106" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M106" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M106" s="24">
+        <v>0</v>
+      </c>
+      <c r="N106" s="24">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="N106" s="24">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
       <c r="O106" s="24">
-        <v>24450</v>
+        <v>24930</v>
       </c>
       <c r="P106" s="24">
         <v>10730</v>
@@ -12576,29 +12883,32 @@
         <v>14240</v>
       </c>
       <c r="Z106" s="24">
+        <f t="shared" si="34"/>
+        <v>85900</v>
+      </c>
+      <c r="AA106" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="20">
         <f t="shared" si="35"/>
-        <v>85420</v>
-      </c>
-      <c r="AA106" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB106" s="20">
-        <f t="shared" si="36"/>
-        <v>85420</v>
+        <v>85900</v>
       </c>
       <c r="AC106" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD106" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE106" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF106" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF106" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" s="22" t="s">
@@ -12629,23 +12939,23 @@
         <v>0</v>
       </c>
       <c r="J107" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K107" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K107" s="24">
+        <v>19500</v>
+      </c>
+      <c r="L107" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
-      </c>
-      <c r="L107" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M107" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M107" s="24">
+        <v>0</v>
+      </c>
+      <c r="N107" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N107" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O107" s="24">
@@ -12682,29 +12992,32 @@
         <v>0</v>
       </c>
       <c r="Z107" s="24">
+        <f t="shared" si="34"/>
+        <v>44430</v>
+      </c>
+      <c r="AA107" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="20">
         <f t="shared" si="35"/>
         <v>44430</v>
       </c>
-      <c r="AA107" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB107" s="20">
-        <f t="shared" si="36"/>
-        <v>44430</v>
-      </c>
       <c r="AC107" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD107" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE107" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF107" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF107" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" s="22" t="s">
@@ -12735,27 +13048,27 @@
         <v>5000</v>
       </c>
       <c r="J108" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K108" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K108" s="24">
+        <v>21000</v>
+      </c>
+      <c r="L108" s="24">
         <f t="shared" si="31"/>
-        <v>21000</v>
-      </c>
-      <c r="L108" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M108" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M108" s="24">
+        <v>0</v>
+      </c>
+      <c r="N108" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="24">
-        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O108" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P108" s="24">
         <v>11330</v>
@@ -12788,29 +13101,32 @@
         <v>0</v>
       </c>
       <c r="Z108" s="24">
+        <f t="shared" si="34"/>
+        <v>66230</v>
+      </c>
+      <c r="AA108" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="20">
         <f t="shared" si="35"/>
-        <v>65750</v>
-      </c>
-      <c r="AA108" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB108" s="20">
-        <f t="shared" si="36"/>
-        <v>65750</v>
+        <v>66230</v>
       </c>
       <c r="AC108" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD108" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE108" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF108" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF108" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" s="22" t="s">
@@ -12841,23 +13157,23 @@
         <v>5000</v>
       </c>
       <c r="J109" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K109" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="24">
+        <v>21000</v>
+      </c>
+      <c r="L109" s="24">
         <f t="shared" si="31"/>
-        <v>21000</v>
-      </c>
-      <c r="L109" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M109" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M109" s="24">
+        <v>0</v>
+      </c>
+      <c r="N109" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N109" s="24">
-        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O109" s="24">
@@ -12894,29 +13210,32 @@
         <v>0</v>
       </c>
       <c r="Z109" s="24">
+        <f t="shared" si="34"/>
+        <v>76770</v>
+      </c>
+      <c r="AA109" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="20">
         <f t="shared" si="35"/>
         <v>76770</v>
       </c>
-      <c r="AA109" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB109" s="20">
-        <f t="shared" si="36"/>
-        <v>76770</v>
-      </c>
       <c r="AC109" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD109" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE109" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF109" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF109" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" s="22" t="s">
@@ -12947,23 +13266,23 @@
         <v>8000</v>
       </c>
       <c r="J110" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K110" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K110" s="24">
+        <v>30000</v>
+      </c>
+      <c r="L110" s="24">
         <f t="shared" si="31"/>
-        <v>30000</v>
-      </c>
-      <c r="L110" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M110" s="24">
         <f t="shared" si="32"/>
-        <v>5000</v>
-      </c>
-      <c r="M110" s="24">
+        <v>1500</v>
+      </c>
+      <c r="N110" s="24">
         <f t="shared" si="33"/>
-        <v>1500</v>
-      </c>
-      <c r="N110" s="24">
-        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O110" s="24">
@@ -13000,29 +13319,32 @@
         <v>2660</v>
       </c>
       <c r="Z110" s="24">
+        <f t="shared" si="34"/>
+        <v>79370</v>
+      </c>
+      <c r="AA110" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB110" s="20">
         <f t="shared" si="35"/>
         <v>79370</v>
       </c>
-      <c r="AA110" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB110" s="20">
-        <f t="shared" si="36"/>
-        <v>79370</v>
-      </c>
       <c r="AC110" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD110" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE110" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF110" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF110" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" s="22" t="s">
@@ -13053,23 +13375,23 @@
         <v>0</v>
       </c>
       <c r="J111" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K111" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K111" s="24">
+        <v>19500</v>
+      </c>
+      <c r="L111" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
-      </c>
-      <c r="L111" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M111" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M111" s="24">
+        <v>750</v>
+      </c>
+      <c r="N111" s="24">
         <f t="shared" si="33"/>
-        <v>750</v>
-      </c>
-      <c r="N111" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O111" s="24">
@@ -13106,29 +13428,32 @@
         <v>1250</v>
       </c>
       <c r="Z111" s="24">
+        <f t="shared" si="34"/>
+        <v>51530</v>
+      </c>
+      <c r="AA111" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="20">
         <f t="shared" si="35"/>
         <v>51530</v>
       </c>
-      <c r="AA111" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB111" s="20">
-        <f t="shared" si="36"/>
-        <v>51530</v>
-      </c>
       <c r="AC111" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD111" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE111" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF111" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF111" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" s="22" t="s">
@@ -13159,27 +13484,27 @@
         <v>5000</v>
       </c>
       <c r="J112" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K112" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K112" s="24">
+        <v>21000</v>
+      </c>
+      <c r="L112" s="24">
         <f t="shared" si="31"/>
-        <v>21000</v>
-      </c>
-      <c r="L112" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M112" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M112" s="24">
+        <v>1875</v>
+      </c>
+      <c r="N112" s="24">
         <f t="shared" si="33"/>
-        <v>1875</v>
-      </c>
-      <c r="N112" s="24">
-        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O112" s="24">
-        <v>25490</v>
+        <v>25970</v>
       </c>
       <c r="P112" s="24">
         <v>11330</v>
@@ -13212,29 +13537,32 @@
         <v>9500</v>
       </c>
       <c r="Z112" s="24">
+        <f t="shared" si="34"/>
+        <v>83425</v>
+      </c>
+      <c r="AA112" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB112" s="20">
         <f t="shared" si="35"/>
-        <v>82945</v>
-      </c>
-      <c r="AA112" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB112" s="20">
-        <f t="shared" si="36"/>
-        <v>82945</v>
+        <v>83425</v>
       </c>
       <c r="AC112" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD112" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE112" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF112" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF112" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" s="22" t="s">
@@ -13265,27 +13593,27 @@
         <v>5000</v>
       </c>
       <c r="J113" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K113" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K113" s="24">
+        <v>21000</v>
+      </c>
+      <c r="L113" s="24">
         <f t="shared" si="31"/>
-        <v>21000</v>
-      </c>
-      <c r="L113" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M113" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M113" s="24">
+        <v>0</v>
+      </c>
+      <c r="N113" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N113" s="24">
-        <f t="shared" si="34"/>
         <v>3750</v>
       </c>
       <c r="O113" s="24">
-        <v>26850</v>
+        <v>27330</v>
       </c>
       <c r="P113" s="24">
         <v>13230</v>
@@ -13318,29 +13646,32 @@
         <v>0</v>
       </c>
       <c r="Z113" s="24">
+        <f t="shared" si="34"/>
+        <v>75310</v>
+      </c>
+      <c r="AA113" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB113" s="20">
         <f t="shared" si="35"/>
-        <v>74830</v>
-      </c>
-      <c r="AA113" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB113" s="20">
-        <f t="shared" si="36"/>
-        <v>74830</v>
+        <v>75310</v>
       </c>
       <c r="AC113" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD113" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE113" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF113" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF113" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" s="22" t="s">
@@ -13371,23 +13702,23 @@
         <v>0</v>
       </c>
       <c r="J114" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K114" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K114" s="24">
+        <v>26000</v>
+      </c>
+      <c r="L114" s="24">
         <f t="shared" si="31"/>
-        <v>26000</v>
-      </c>
-      <c r="L114" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M114" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M114" s="24">
+        <v>1000</v>
+      </c>
+      <c r="N114" s="24">
         <f t="shared" si="33"/>
-        <v>1000</v>
-      </c>
-      <c r="N114" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O114" s="24">
@@ -13424,29 +13755,32 @@
         <v>1000</v>
       </c>
       <c r="Z114" s="24">
+        <f t="shared" si="34"/>
+        <v>44140</v>
+      </c>
+      <c r="AA114" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB114" s="20">
         <f t="shared" si="35"/>
         <v>44140</v>
       </c>
-      <c r="AA114" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB114" s="20">
-        <f t="shared" si="36"/>
-        <v>44140</v>
-      </c>
       <c r="AC114" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD114" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE114" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF114" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF114" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" s="22" t="s">
@@ -13477,23 +13811,23 @@
         <v>6000</v>
       </c>
       <c r="J115" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K115" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K115" s="24">
+        <v>23100</v>
+      </c>
+      <c r="L115" s="24">
         <f t="shared" si="31"/>
-        <v>23100</v>
-      </c>
-      <c r="L115" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M115" s="24">
         <f t="shared" si="32"/>
-        <v>5000</v>
-      </c>
-      <c r="M115" s="24">
+        <v>1400</v>
+      </c>
+      <c r="N115" s="24">
         <f t="shared" si="33"/>
-        <v>1400</v>
-      </c>
-      <c r="N115" s="24">
-        <f t="shared" si="34"/>
         <v>4200</v>
       </c>
       <c r="O115" s="24">
@@ -13530,29 +13864,32 @@
         <v>0</v>
       </c>
       <c r="Z115" s="24">
+        <f t="shared" si="34"/>
+        <v>78430</v>
+      </c>
+      <c r="AA115" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB115" s="20">
         <f t="shared" si="35"/>
         <v>78430</v>
       </c>
-      <c r="AA115" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB115" s="20">
-        <f t="shared" si="36"/>
-        <v>78430</v>
-      </c>
       <c r="AC115" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD115" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE115" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF115" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF115" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" s="22" t="s">
@@ -13583,23 +13920,23 @@
         <v>8000</v>
       </c>
       <c r="J116" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K116" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K116" s="24">
+        <v>30000</v>
+      </c>
+      <c r="L116" s="24">
         <f t="shared" si="31"/>
-        <v>30000</v>
-      </c>
-      <c r="L116" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M116" s="24">
         <f t="shared" si="32"/>
-        <v>5000</v>
-      </c>
-      <c r="M116" s="24">
+        <v>1500</v>
+      </c>
+      <c r="N116" s="24">
         <f t="shared" si="33"/>
-        <v>1500</v>
-      </c>
-      <c r="N116" s="24">
-        <f t="shared" si="34"/>
         <v>6000</v>
       </c>
       <c r="O116" s="24">
@@ -13636,29 +13973,32 @@
         <v>0</v>
       </c>
       <c r="Z116" s="24">
+        <f t="shared" si="34"/>
+        <v>68710</v>
+      </c>
+      <c r="AA116" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="20">
         <f t="shared" si="35"/>
         <v>68710</v>
       </c>
-      <c r="AA116" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB116" s="20">
-        <f t="shared" si="36"/>
-        <v>68710</v>
-      </c>
       <c r="AC116" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD116" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE116" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF116" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF116" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" s="22" t="s">
@@ -13689,27 +14029,27 @@
         <v>5000</v>
       </c>
       <c r="J117" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K117" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K117" s="24">
+        <v>28000</v>
+      </c>
+      <c r="L117" s="24">
         <f t="shared" si="31"/>
-        <v>28000</v>
-      </c>
-      <c r="L117" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M117" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M117" s="24">
+        <v>0</v>
+      </c>
+      <c r="N117" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N117" s="24">
-        <f t="shared" si="34"/>
         <v>5000</v>
       </c>
       <c r="O117" s="24">
-        <v>25670</v>
+        <v>26150</v>
       </c>
       <c r="P117" s="24">
         <v>11330</v>
@@ -13742,29 +14082,32 @@
         <v>4020</v>
       </c>
       <c r="Z117" s="24">
+        <f t="shared" si="34"/>
+        <v>78500</v>
+      </c>
+      <c r="AA117" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB117" s="20">
         <f t="shared" si="35"/>
-        <v>78020</v>
-      </c>
-      <c r="AA117" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB117" s="20">
-        <f t="shared" si="36"/>
-        <v>78020</v>
+        <v>78500</v>
       </c>
       <c r="AC117" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD117" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE117" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF117" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF117" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" s="22" t="s">
@@ -13795,23 +14138,23 @@
         <v>0</v>
       </c>
       <c r="J118" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K118" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K118" s="24">
+        <v>19500</v>
+      </c>
+      <c r="L118" s="24">
         <f t="shared" si="31"/>
-        <v>19500</v>
-      </c>
-      <c r="L118" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M118" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M118" s="24">
+        <v>750</v>
+      </c>
+      <c r="N118" s="24">
         <f t="shared" si="33"/>
-        <v>750</v>
-      </c>
-      <c r="N118" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O118" s="24">
@@ -13848,29 +14191,32 @@
         <v>0</v>
       </c>
       <c r="Z118" s="24">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>36390</v>
       </c>
       <c r="AA118" s="24">
         <v>7070</v>
       </c>
       <c r="AB118" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>29320</v>
       </c>
       <c r="AC118" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD118" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE118" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF118" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF118" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" s="22" t="s">
@@ -13901,23 +14247,23 @@
         <v>0</v>
       </c>
       <c r="J119" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K119" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K119" s="24">
+        <v>18200</v>
+      </c>
+      <c r="L119" s="24">
         <f t="shared" si="31"/>
-        <v>18200</v>
-      </c>
-      <c r="L119" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M119" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M119" s="24">
+        <v>700</v>
+      </c>
+      <c r="N119" s="24">
         <f t="shared" si="33"/>
-        <v>700</v>
-      </c>
-      <c r="N119" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O119" s="24">
@@ -13954,30 +14300,31 @@
         <v>0</v>
       </c>
       <c r="Z119" s="24">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>42930</v>
       </c>
       <c r="AA119" s="24">
         <v>42930</v>
       </c>
       <c r="AB119" s="20">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AC119" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD119" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE119" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF119" s="25" t="s">
-        <v>259</v>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF119" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="120" spans="1:32" x14ac:dyDescent="0.25">
@@ -14009,23 +14356,23 @@
         <v>0</v>
       </c>
       <c r="J120" s="24">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="K120" s="24">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="K120" s="24">
+        <v>26000</v>
+      </c>
+      <c r="L120" s="24">
         <f t="shared" si="31"/>
-        <v>26000</v>
-      </c>
-      <c r="L120" s="24">
+        <v>4000</v>
+      </c>
+      <c r="M120" s="24">
         <f t="shared" si="32"/>
-        <v>4000</v>
-      </c>
-      <c r="M120" s="24">
+        <v>0</v>
+      </c>
+      <c r="N120" s="24">
         <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="N120" s="24">
-        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="O120" s="24">
@@ -14062,29 +14409,32 @@
         <v>0</v>
       </c>
       <c r="Z120" s="24">
+        <f t="shared" si="34"/>
+        <v>50930</v>
+      </c>
+      <c r="AA120" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB120" s="20">
         <f t="shared" si="35"/>
         <v>50930</v>
       </c>
-      <c r="AA120" s="24">
-        <v>0</v>
-      </c>
-      <c r="AB120" s="20">
-        <f t="shared" si="36"/>
-        <v>50930</v>
-      </c>
       <c r="AC120" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="AD120" s="24" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AE120" s="24" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="AF120" s="25"/>
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AF120" s="25" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
     </row>
     <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" s="26"/>
@@ -14102,71 +14452,71 @@
       <c r="M121" s="28"/>
       <c r="N121" s="28"/>
       <c r="O121" s="28">
-        <f t="shared" ref="O121:AE121" si="40">SUM(O2:O120)</f>
-        <v>2085190</v>
+        <f t="shared" ref="O121:AE121" si="36">SUM(O2:O120)</f>
+        <v>2103910</v>
       </c>
       <c r="P121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>1203390</v>
       </c>
       <c r="Q121" s="28">
-        <f t="shared" si="40"/>
-        <v>36000</v>
+        <f t="shared" si="36"/>
+        <v>76000</v>
       </c>
       <c r="R121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>8000</v>
       </c>
       <c r="S121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="T121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>252000</v>
       </c>
       <c r="U121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="V121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="W121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="X121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Y121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>188670</v>
       </c>
       <c r="Z121" s="28">
-        <f t="shared" si="40"/>
-        <v>7234575</v>
+        <f t="shared" si="36"/>
+        <v>7291945</v>
       </c>
       <c r="AA121" s="28">
-        <f t="shared" si="40"/>
-        <v>354975</v>
+        <f t="shared" si="36"/>
+        <v>397115</v>
       </c>
       <c r="AB121" s="28">
-        <f t="shared" si="40"/>
-        <v>6879600</v>
+        <f t="shared" si="36"/>
+        <v>6894830</v>
       </c>
       <c r="AC121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>6000</v>
       </c>
       <c r="AD121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AE121" s="28">
-        <f t="shared" si="40"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AF121" s="25"/>
@@ -22349,7 +22699,7 @@
       <c r="AD979" s="33"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE121">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AF121">
     <sortCondition ref="A2:A121"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -22536,13 +22886,13 @@
         <v>250</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D8" s="9">
         <v>60000</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -22553,13 +22903,13 @@
         <v>250</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D9" s="9">
         <v>50430</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -22570,13 +22920,30 @@
         <v>250</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D10" s="9">
         <v>50000</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>265</v>
+      </c>
+      <c r="D11" s="9">
+        <v>42140</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">

--- a/2026 - 2027 FEE.xlsx
+++ b/2026 - 2027 FEE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83457E3A-BDF4-4CB9-AC26-808051A1DBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EF9B45-0C21-4664-9312-7EC81E0C373A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="276">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -839,6 +839,33 @@
   <si>
     <t>ADEDAMOLA IREMIDE</t>
   </si>
+  <si>
+    <t>NIP:SEYI OLOWE</t>
+  </si>
+  <si>
+    <t>ADENIYI SAMUEL</t>
+  </si>
+  <si>
+    <t>AKINWUMI DAVID</t>
+  </si>
+  <si>
+    <t>MONIEPOINT</t>
+  </si>
+  <si>
+    <t>OMOWUNMI AFOLASADE AWOITE</t>
+  </si>
+  <si>
+    <t>FRIDAY OGECHUKWU UKOH</t>
+  </si>
+  <si>
+    <t>PETER FAVOUR</t>
+  </si>
+  <si>
+    <t>EDEM ZENITH</t>
+  </si>
+  <si>
+    <t>DAVID JESUTOFUNMI DARA</t>
+  </si>
 </sst>
 </file>
 
@@ -4058,11 +4085,11 @@
         <v>79830</v>
       </c>
       <c r="AA25" s="24">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="AB25" s="20">
         <f t="shared" si="6"/>
-        <v>79830</v>
+        <v>19830</v>
       </c>
       <c r="AC25" s="24" t="str">
         <f t="shared" si="7"/>
@@ -6490,7 +6517,7 @@
         <v>248</v>
       </c>
       <c r="D48" s="23">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E48" s="24">
         <v>0</v>
@@ -6513,7 +6540,7 @@
       </c>
       <c r="K48" s="24">
         <f t="shared" si="12"/>
-        <v>28000</v>
+        <v>26600</v>
       </c>
       <c r="L48" s="24">
         <f t="shared" si="13"/>
@@ -6525,7 +6552,7 @@
       </c>
       <c r="N48" s="24">
         <f t="shared" si="15"/>
-        <v>5000</v>
+        <v>4750</v>
       </c>
       <c r="O48" s="24">
         <v>28790</v>
@@ -6562,14 +6589,14 @@
       </c>
       <c r="Z48" s="24">
         <f t="shared" si="16"/>
+        <v>77370</v>
+      </c>
+      <c r="AA48" s="24">
         <v>79020</v>
-      </c>
-      <c r="AA48" s="24">
-        <v>0</v>
       </c>
       <c r="AB48" s="20">
         <f t="shared" si="17"/>
-        <v>79020</v>
+        <v>-1650</v>
       </c>
       <c r="AC48" s="24" t="str">
         <f t="shared" si="7"/>
@@ -6585,7 +6612,7 @@
       </c>
       <c r="AF48" s="25" t="str">
         <f t="shared" si="10"/>
-        <v/>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
@@ -6674,11 +6701,11 @@
         <v>82800</v>
       </c>
       <c r="AA49" s="24">
-        <v>0</v>
+        <v>42350</v>
       </c>
       <c r="AB49" s="20">
         <f t="shared" si="17"/>
-        <v>82800</v>
+        <v>40450</v>
       </c>
       <c r="AC49" s="24" t="str">
         <f t="shared" si="7"/>
@@ -12011,14 +12038,14 @@
         <v>0</v>
       </c>
       <c r="Z98" s="24">
-        <f t="shared" ref="Z98:Z129" si="34">SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z120" si="34">SUM(J98:Y98)</f>
         <v>57980</v>
       </c>
       <c r="AA98" s="24">
         <v>0</v>
       </c>
       <c r="AB98" s="20">
-        <f t="shared" ref="AB98:AB129" si="35">Z98-AA98</f>
+        <f t="shared" ref="AB98:AB120" si="35">Z98-AA98</f>
         <v>57980</v>
       </c>
       <c r="AC98" s="24" t="str">
@@ -12887,11 +12914,11 @@
         <v>85900</v>
       </c>
       <c r="AA106" s="24">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AB106" s="20">
         <f t="shared" si="35"/>
-        <v>85900</v>
+        <v>35900</v>
       </c>
       <c r="AC106" s="24" t="str">
         <f t="shared" si="25"/>
@@ -14497,15 +14524,15 @@
       </c>
       <c r="Z121" s="28">
         <f t="shared" si="36"/>
-        <v>7291945</v>
+        <v>7290295</v>
       </c>
       <c r="AA121" s="28">
         <f t="shared" si="36"/>
-        <v>397115</v>
+        <v>628485</v>
       </c>
       <c r="AB121" s="28">
         <f t="shared" si="36"/>
-        <v>6894830</v>
+        <v>6661810</v>
       </c>
       <c r="AC121" s="28">
         <f t="shared" si="36"/>
@@ -22729,10 +22756,10 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" style="7" customWidth="1"/>
     <col min="7" max="7" width="4.85546875" style="7" customWidth="1"/>
     <col min="8" max="23" width="24.140625" style="7" customWidth="1"/>
@@ -22946,11 +22973,39 @@
         <v>266</v>
       </c>
     </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D12" s="9">
+        <v>60000</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
     <row r="13" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
+      <c r="A13" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="9">
+        <v>79020</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>275</v>
+      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -22972,10 +23027,21 @@
       <c r="X13" s="7"/>
     </row>
     <row r="14" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7"/>
+      <c r="A14" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D14" s="9">
+        <v>42350</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>274</v>
+      </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -22997,10 +23063,21 @@
       <c r="X14" s="7"/>
     </row>
     <row r="15" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7"/>
+      <c r="A15" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="9">
+        <v>50000</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>273</v>
+      </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>

--- a/2026 - 2027 FEE.xlsx
+++ b/2026 - 2027 FEE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAA72A3-2B35-43D4-B07B-DBA43C5D9237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B291D2-5646-4D7E-A0FC-35ACFAE817AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="286">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -890,6 +890,12 @@
   <si>
     <t>JAMIU FAIZAH</t>
   </si>
+  <si>
+    <t>IP:KAYODE MATHEW OLUWASEUN-ISRAEL 1ST TERM</t>
+  </si>
+  <si>
+    <t>OLUWASEUN ISRAEL</t>
+  </si>
 </sst>
 </file>
 
@@ -1545,23 +1551,23 @@
         <v>0</v>
       </c>
       <c r="J2" s="24">
-        <f>(1-$D2)*E2</f>
+        <f t="shared" ref="J2:J33" si="0">(1-$D2)*E2</f>
         <v>0</v>
       </c>
       <c r="K2" s="24">
-        <f>(1-$D2)*F2</f>
+        <f t="shared" ref="K2:K33" si="1">(1-$D2)*F2</f>
         <v>19500</v>
       </c>
       <c r="L2" s="24">
-        <f>G2</f>
+        <f t="shared" ref="L2:L33" si="2">G2</f>
         <v>4000</v>
       </c>
       <c r="M2" s="24">
-        <f>(1-$D2)*H2</f>
+        <f t="shared" ref="M2:M33" si="3">(1-$D2)*H2</f>
         <v>0</v>
       </c>
       <c r="N2" s="24">
-        <f>(1-$D2)*I2</f>
+        <f t="shared" ref="N2:N33" si="4">(1-$D2)*I2</f>
         <v>0</v>
       </c>
       <c r="O2" s="24">
@@ -1598,30 +1604,30 @@
         <v>750</v>
       </c>
       <c r="Z2" s="24">
-        <f>SUM(J2:Y2)</f>
+        <f t="shared" ref="Z2:Z33" si="5">SUM(J2:Y2)</f>
         <v>51180</v>
       </c>
       <c r="AA2" s="24">
         <v>0</v>
       </c>
       <c r="AB2" s="20">
-        <f>Z2-AA2</f>
+        <f t="shared" ref="AB2:AB33" si="6">Z2-AA2</f>
         <v>51180</v>
       </c>
       <c r="AC2" s="24" t="str">
-        <f>IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
+        <f t="shared" ref="AC2:AC33" si="7">IF(AND($T2=6000, ($T2+$W2-$AB2)&gt;=6000),T2,"")</f>
         <v/>
       </c>
       <c r="AD2" s="24" t="str">
-        <f>IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
+        <f t="shared" ref="AD2:AD33" si="8">IF(AND($T2=8000, ($T2+$W2-$AB2)&gt;=8000),T2,"")</f>
         <v/>
       </c>
       <c r="AE2" s="24" t="str">
-        <f>IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
+        <f t="shared" ref="AE2:AE33" si="9">IF(($T2+$W2-$AB2)&gt;=$T2+8000,W2,"")</f>
         <v/>
       </c>
       <c r="AF2" s="25" t="str">
-        <f>IF(AB2&lt;=0,"BONUS","")</f>
+        <f t="shared" ref="AF2:AF33" si="10">IF(AB2&lt;=0,"BONUS","")</f>
         <v/>
       </c>
     </row>
@@ -1654,23 +1660,23 @@
         <v>5000</v>
       </c>
       <c r="J3" s="24">
-        <f>(1-$D3)*E3</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K3" s="24">
-        <f>(1-$D3)*F3</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L3" s="24">
-        <f>G3</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M3" s="24">
-        <f>(1-$D3)*H3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N3" s="24">
-        <f>(1-$D3)*I3</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O3" s="24">
@@ -1707,30 +1713,30 @@
         <v>125</v>
       </c>
       <c r="Z3" s="24">
-        <f>SUM(J3:Y3)</f>
+        <f t="shared" si="5"/>
         <v>72355</v>
       </c>
       <c r="AA3" s="24">
         <v>0</v>
       </c>
       <c r="AB3" s="20">
-        <f>Z3-AA3</f>
+        <f t="shared" si="6"/>
         <v>72355</v>
       </c>
       <c r="AC3" s="24" t="str">
-        <f>IF(AND($T3=6000, ($T3+$W3-$AB3)&gt;=6000),T3,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD3" s="24" t="str">
-        <f>IF(AND($T3=8000, ($T3+$W3-$AB3)&gt;=8000),T3,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE3" s="24" t="str">
-        <f>IF(($T3+$W3-$AB3)&gt;=$T3+8000,W3,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF3" s="25" t="str">
-        <f>IF(AB3&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -1763,23 +1769,23 @@
         <v>8000</v>
       </c>
       <c r="J4" s="24">
-        <f>(1-$D4)*E4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K4" s="24">
-        <f>(1-$D4)*F4</f>
+        <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="L4" s="24">
-        <f>G4</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M4" s="24">
-        <f>(1-$D4)*H4</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N4" s="24">
-        <f>(1-$D4)*I4</f>
+        <f t="shared" si="4"/>
         <v>8000</v>
       </c>
       <c r="O4" s="24">
@@ -1816,30 +1822,30 @@
         <v>0</v>
       </c>
       <c r="Z4" s="24">
-        <f>SUM(J4:Y4)</f>
+        <f t="shared" si="5"/>
         <v>81210</v>
       </c>
       <c r="AA4" s="24">
         <v>0</v>
       </c>
       <c r="AB4" s="20">
-        <f>Z4-AA4</f>
+        <f t="shared" si="6"/>
         <v>81210</v>
       </c>
       <c r="AC4" s="24" t="str">
-        <f>IF(AND($T4=6000, ($T4+$W4-$AB4)&gt;=6000),T4,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD4" s="24" t="str">
-        <f>IF(AND($T4=8000, ($T4+$W4-$AB4)&gt;=8000),T4,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE4" s="24" t="str">
-        <f>IF(($T4+$W4-$AB4)&gt;=$T4+8000,W4,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF4" s="25" t="str">
-        <f>IF(AB4&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -1872,23 +1878,23 @@
         <v>0</v>
       </c>
       <c r="J5" s="24">
-        <f>(1-$D5)*E5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K5" s="24">
-        <f>(1-$D5)*F5</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L5" s="24">
-        <f>G5</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M5" s="24">
-        <f>(1-$D5)*H5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N5" s="24">
-        <f>(1-$D5)*I5</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O5" s="24">
@@ -1925,30 +1931,30 @@
         <v>0</v>
       </c>
       <c r="Z5" s="24">
-        <f>SUM(J5:Y5)</f>
+        <f t="shared" si="5"/>
         <v>59160</v>
       </c>
       <c r="AA5" s="24">
         <v>0</v>
       </c>
       <c r="AB5" s="20">
-        <f>Z5-AA5</f>
+        <f t="shared" si="6"/>
         <v>59160</v>
       </c>
       <c r="AC5" s="24" t="str">
-        <f>IF(AND($T5=6000, ($T5+$W5-$AB5)&gt;=6000),T5,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD5" s="24" t="str">
-        <f>IF(AND($T5=8000, ($T5+$W5-$AB5)&gt;=8000),T5,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE5" s="24" t="str">
-        <f>IF(($T5+$W5-$AB5)&gt;=$T5+8000,W5,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF5" s="25" t="str">
-        <f>IF(AB5&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -1981,23 +1987,23 @@
         <v>0</v>
       </c>
       <c r="J6" s="24">
-        <f>(1-$D6)*E6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6" s="24">
-        <f>(1-$D6)*F6</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L6" s="24">
-        <f>G6</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M6" s="24">
-        <f>(1-$D6)*H6</f>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="N6" s="24">
-        <f>(1-$D6)*I6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O6" s="24">
@@ -2034,30 +2040,30 @@
         <v>0</v>
       </c>
       <c r="Z6" s="24">
-        <f>SUM(J6:Y6)</f>
+        <f t="shared" si="5"/>
         <v>44280</v>
       </c>
       <c r="AA6" s="24">
         <v>0</v>
       </c>
       <c r="AB6" s="20">
-        <f>Z6-AA6</f>
+        <f t="shared" si="6"/>
         <v>44280</v>
       </c>
       <c r="AC6" s="24" t="str">
-        <f>IF(AND($T6=6000, ($T6+$W6-$AB6)&gt;=6000),T6,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD6" s="24" t="str">
-        <f>IF(AND($T6=8000, ($T6+$W6-$AB6)&gt;=8000),T6,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE6" s="24" t="str">
-        <f>IF(($T6+$W6-$AB6)&gt;=$T6+8000,W6,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF6" s="25" t="str">
-        <f>IF(AB6&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2090,23 +2096,23 @@
         <v>0</v>
       </c>
       <c r="J7" s="24">
-        <f>(1-$D7)*E7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K7" s="24">
-        <f>(1-$D7)*F7</f>
+        <f t="shared" si="1"/>
         <v>18200</v>
       </c>
       <c r="L7" s="24">
-        <f>G7</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M7" s="24">
-        <f>(1-$D7)*H7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N7" s="24">
-        <f>(1-$D7)*I7</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O7" s="24">
@@ -2143,30 +2149,30 @@
         <v>0</v>
       </c>
       <c r="Z7" s="24">
-        <f>SUM(J7:Y7)</f>
+        <f t="shared" si="5"/>
         <v>43130</v>
       </c>
       <c r="AA7" s="24">
         <v>43130</v>
       </c>
       <c r="AB7" s="20">
-        <f>Z7-AA7</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC7" s="24" t="str">
-        <f>IF(AND($T7=6000, ($T7+$W7-$AB7)&gt;=6000),T7,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD7" s="24" t="str">
-        <f>IF(AND($T7=8000, ($T7+$W7-$AB7)&gt;=8000),T7,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE7" s="24" t="str">
-        <f>IF(($T7+$W7-$AB7)&gt;=$T7+8000,W7,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF7" s="25" t="str">
-        <f>IF(AB7&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -2199,23 +2205,23 @@
         <v>0</v>
       </c>
       <c r="J8" s="24">
-        <f>(1-$D8)*E8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8" s="24">
-        <f>(1-$D8)*F8</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L8" s="24">
-        <f>G8</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M8" s="24">
-        <f>(1-$D8)*H8</f>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="N8" s="24">
-        <f>(1-$D8)*I8</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O8" s="24">
@@ -2252,30 +2258,30 @@
         <v>-90</v>
       </c>
       <c r="Z8" s="24">
-        <f>SUM(J8:Y8)</f>
+        <f t="shared" si="5"/>
         <v>50190</v>
       </c>
       <c r="AA8" s="24">
         <v>0</v>
       </c>
       <c r="AB8" s="20">
-        <f>Z8-AA8</f>
+        <f t="shared" si="6"/>
         <v>50190</v>
       </c>
       <c r="AC8" s="24" t="str">
-        <f>IF(AND($T8=6000, ($T8+$W8-$AB8)&gt;=6000),T8,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD8" s="24" t="str">
-        <f>IF(AND($T8=8000, ($T8+$W8-$AB8)&gt;=8000),T8,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE8" s="24" t="str">
-        <f>IF(($T8+$W8-$AB8)&gt;=$T8+8000,W8,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF8" s="25" t="str">
-        <f>IF(AB8&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2308,23 +2314,23 @@
         <v>0</v>
       </c>
       <c r="J9" s="24">
-        <f>(1-$D9)*E9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K9" s="24">
-        <f>(1-$D9)*F9</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L9" s="24">
-        <f>G9</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M9" s="24">
-        <f>(1-$D9)*H9</f>
+        <f t="shared" si="3"/>
         <v>750</v>
       </c>
       <c r="N9" s="24">
-        <f>(1-$D9)*I9</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O9" s="24">
@@ -2361,30 +2367,30 @@
         <v>0</v>
       </c>
       <c r="Z9" s="24">
-        <f>SUM(J9:Y9)</f>
+        <f t="shared" si="5"/>
         <v>44280</v>
       </c>
       <c r="AA9" s="24">
         <v>16870</v>
       </c>
       <c r="AB9" s="20">
-        <f>Z9-AA9</f>
+        <f t="shared" si="6"/>
         <v>27410</v>
       </c>
       <c r="AC9" s="24" t="str">
-        <f>IF(AND($T9=6000, ($T9+$W9-$AB9)&gt;=6000),T9,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD9" s="24" t="str">
-        <f>IF(AND($T9=8000, ($T9+$W9-$AB9)&gt;=8000),T9,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE9" s="24" t="str">
-        <f>IF(($T9+$W9-$AB9)&gt;=$T9+8000,W9,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF9" s="25" t="str">
-        <f>IF(AB9&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2417,23 +2423,23 @@
         <v>5000</v>
       </c>
       <c r="J10" s="24">
-        <f>(1-$D10)*E10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K10" s="24">
-        <f>(1-$D10)*F10</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L10" s="24">
-        <f>G10</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M10" s="24">
-        <f>(1-$D10)*H10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N10" s="24">
-        <f>(1-$D10)*I10</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O10" s="24">
@@ -2470,30 +2476,30 @@
         <v>0</v>
       </c>
       <c r="Z10" s="24">
-        <f>SUM(J10:Y10)</f>
+        <f t="shared" si="5"/>
         <v>69290</v>
       </c>
       <c r="AA10" s="24">
         <v>0</v>
       </c>
       <c r="AB10" s="20">
-        <f>Z10-AA10</f>
+        <f t="shared" si="6"/>
         <v>69290</v>
       </c>
       <c r="AC10" s="24" t="str">
-        <f>IF(AND($T10=6000, ($T10+$W10-$AB10)&gt;=6000),T10,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD10" s="24" t="str">
-        <f>IF(AND($T10=8000, ($T10+$W10-$AB10)&gt;=8000),T10,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE10" s="24" t="str">
-        <f>IF(($T10+$W10-$AB10)&gt;=$T10+8000,W10,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF10" s="25" t="str">
-        <f>IF(AB10&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2526,23 +2532,23 @@
         <v>6000</v>
       </c>
       <c r="J11" s="24">
-        <f>(1-$D11)*E11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="24">
-        <f>(1-$D11)*F11</f>
+        <f t="shared" si="1"/>
         <v>24750</v>
       </c>
       <c r="L11" s="24">
-        <f>G11</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M11" s="24">
-        <f>(1-$D11)*H11</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N11" s="24">
-        <f>(1-$D11)*I11</f>
+        <f t="shared" si="4"/>
         <v>4500</v>
       </c>
       <c r="O11" s="24">
@@ -2579,30 +2585,30 @@
         <v>750</v>
       </c>
       <c r="Z11" s="24">
-        <f>SUM(J11:Y11)</f>
+        <f t="shared" si="5"/>
         <v>78330</v>
       </c>
       <c r="AA11" s="24">
         <v>0</v>
       </c>
       <c r="AB11" s="20">
-        <f>Z11-AA11</f>
+        <f t="shared" si="6"/>
         <v>78330</v>
       </c>
       <c r="AC11" s="24" t="str">
-        <f>IF(AND($T11=6000, ($T11+$W11-$AB11)&gt;=6000),T11,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD11" s="24" t="str">
-        <f>IF(AND($T11=8000, ($T11+$W11-$AB11)&gt;=8000),T11,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE11" s="24" t="str">
-        <f>IF(($T11+$W11-$AB11)&gt;=$T11+8000,W11,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF11" s="25" t="str">
-        <f>IF(AB11&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2635,23 +2641,23 @@
         <v>8000</v>
       </c>
       <c r="J12" s="24">
-        <f>(1-$D12)*E12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K12" s="24">
-        <f>(1-$D12)*F12</f>
+        <f t="shared" si="1"/>
         <v>30000</v>
       </c>
       <c r="L12" s="24">
-        <f>G12</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M12" s="24">
-        <f>(1-$D12)*H12</f>
+        <f t="shared" si="3"/>
         <v>1500</v>
       </c>
       <c r="N12" s="24">
-        <f>(1-$D12)*I12</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O12" s="24">
@@ -2688,30 +2694,30 @@
         <v>540</v>
       </c>
       <c r="Z12" s="24">
-        <f>SUM(J12:Y12)</f>
+        <f t="shared" si="5"/>
         <v>97250</v>
       </c>
       <c r="AA12" s="24">
         <v>0</v>
       </c>
       <c r="AB12" s="20">
-        <f>Z12-AA12</f>
+        <f t="shared" si="6"/>
         <v>97250</v>
       </c>
       <c r="AC12" s="24" t="str">
-        <f>IF(AND($T12=6000, ($T12+$W12-$AB12)&gt;=6000),T12,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD12" s="24" t="str">
-        <f>IF(AND($T12=8000, ($T12+$W12-$AB12)&gt;=8000),T12,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE12" s="24" t="str">
-        <f>IF(($T12+$W12-$AB12)&gt;=$T12+8000,W12,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF12" s="25" t="str">
-        <f>IF(AB12&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2744,23 +2750,23 @@
         <v>0</v>
       </c>
       <c r="J13" s="24">
-        <f>(1-$D13)*E13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="24">
-        <f>(1-$D13)*F13</f>
+        <f t="shared" si="1"/>
         <v>13000</v>
       </c>
       <c r="L13" s="24">
-        <f>G13</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M13" s="24">
-        <f>(1-$D13)*H13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N13" s="24">
-        <f>(1-$D13)*I13</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O13" s="24">
@@ -2797,30 +2803,30 @@
         <v>0</v>
       </c>
       <c r="Z13" s="24">
-        <f>SUM(J13:Y13)</f>
+        <f t="shared" si="5"/>
         <v>52660</v>
       </c>
       <c r="AA13" s="24">
         <v>0</v>
       </c>
       <c r="AB13" s="20">
-        <f>Z13-AA13</f>
+        <f t="shared" si="6"/>
         <v>52660</v>
       </c>
       <c r="AC13" s="24" t="str">
-        <f>IF(AND($T13=6000, ($T13+$W13-$AB13)&gt;=6000),T13,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD13" s="24" t="str">
-        <f>IF(AND($T13=8000, ($T13+$W13-$AB13)&gt;=8000),T13,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE13" s="24" t="str">
-        <f>IF(($T13+$W13-$AB13)&gt;=$T13+8000,W13,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF13" s="25" t="str">
-        <f>IF(AB13&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2853,23 +2859,23 @@
         <v>5000</v>
       </c>
       <c r="J14" s="24">
-        <f>(1-$D14)*E14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14" s="24">
-        <f>(1-$D14)*F14</f>
+        <f t="shared" si="1"/>
         <v>14000</v>
       </c>
       <c r="L14" s="24">
-        <f>G14</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M14" s="24">
-        <f>(1-$D14)*H14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="24">
-        <f>(1-$D14)*I14</f>
+        <f t="shared" si="4"/>
         <v>2500</v>
       </c>
       <c r="O14" s="24">
@@ -2906,30 +2912,30 @@
         <v>-530</v>
       </c>
       <c r="Z14" s="24">
-        <f>SUM(J14:Y14)</f>
+        <f t="shared" si="5"/>
         <v>60510</v>
       </c>
       <c r="AA14" s="24">
         <v>0</v>
       </c>
       <c r="AB14" s="20">
-        <f>Z14-AA14</f>
+        <f t="shared" si="6"/>
         <v>60510</v>
       </c>
       <c r="AC14" s="24" t="str">
-        <f>IF(AND($T14=6000, ($T14+$W14-$AB14)&gt;=6000),T14,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD14" s="24" t="str">
-        <f>IF(AND($T14=8000, ($T14+$W14-$AB14)&gt;=8000),T14,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE14" s="24" t="str">
-        <f>IF(($T14+$W14-$AB14)&gt;=$T14+8000,W14,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF14" s="25" t="str">
-        <f>IF(AB14&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -2962,23 +2968,23 @@
         <v>0</v>
       </c>
       <c r="J15" s="24">
-        <f>(1-$D15)*E15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15" s="24">
-        <f>(1-$D15)*F15</f>
+        <f t="shared" si="1"/>
         <v>24700</v>
       </c>
       <c r="L15" s="24">
-        <f>G15</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M15" s="24">
-        <f>(1-$D15)*H15</f>
+        <f t="shared" si="3"/>
         <v>950</v>
       </c>
       <c r="N15" s="24">
-        <f>(1-$D15)*I15</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O15" s="24">
@@ -3015,30 +3021,30 @@
         <v>-1000</v>
       </c>
       <c r="Z15" s="24">
-        <f>SUM(J15:Y15)</f>
+        <f t="shared" si="5"/>
         <v>40790</v>
       </c>
       <c r="AA15" s="24">
         <v>42140</v>
       </c>
       <c r="AB15" s="20">
-        <f>Z15-AA15</f>
+        <f t="shared" si="6"/>
         <v>-1350</v>
       </c>
       <c r="AC15" s="24" t="str">
-        <f>IF(AND($T15=6000, ($T15+$W15-$AB15)&gt;=6000),T15,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD15" s="24" t="str">
-        <f>IF(AND($T15=8000, ($T15+$W15-$AB15)&gt;=8000),T15,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE15" s="24" t="str">
-        <f>IF(($T15+$W15-$AB15)&gt;=$T15+8000,W15,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF15" s="25" t="str">
-        <f>IF(AB15&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -3071,23 +3077,23 @@
         <v>0</v>
       </c>
       <c r="J16" s="24">
-        <f>(1-$D16)*E16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="24">
-        <f>(1-$D16)*F16</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L16" s="24">
-        <f>G16</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M16" s="24">
-        <f>(1-$D16)*H16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N16" s="24">
-        <f>(1-$D16)*I16</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O16" s="24">
@@ -3124,30 +3130,30 @@
         <v>0</v>
       </c>
       <c r="Z16" s="24">
-        <f>SUM(J16:Y16)</f>
+        <f t="shared" si="5"/>
         <v>59160</v>
       </c>
       <c r="AA16" s="24">
         <v>0</v>
       </c>
       <c r="AB16" s="20">
-        <f>Z16-AA16</f>
+        <f t="shared" si="6"/>
         <v>59160</v>
       </c>
       <c r="AC16" s="24" t="str">
-        <f>IF(AND($T16=6000, ($T16+$W16-$AB16)&gt;=6000),T16,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD16" s="24" t="str">
-        <f>IF(AND($T16=8000, ($T16+$W16-$AB16)&gt;=8000),T16,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE16" s="24" t="str">
-        <f>IF(($T16+$W16-$AB16)&gt;=$T16+8000,W16,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF16" s="25" t="str">
-        <f>IF(AB16&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3180,23 +3186,23 @@
         <v>5000</v>
       </c>
       <c r="J17" s="24">
-        <f>(1-$D17)*E17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K17" s="24">
-        <f>(1-$D17)*F17</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L17" s="24">
-        <f>G17</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M17" s="24">
-        <f>(1-$D17)*H17</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N17" s="24">
-        <f>(1-$D17)*I17</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O17" s="24">
@@ -3233,30 +3239,30 @@
         <v>0</v>
       </c>
       <c r="Z17" s="24">
-        <f>SUM(J17:Y17)</f>
+        <f t="shared" si="5"/>
         <v>69290</v>
       </c>
       <c r="AA17" s="24">
         <v>0</v>
       </c>
       <c r="AB17" s="20">
-        <f>Z17-AA17</f>
+        <f t="shared" si="6"/>
         <v>69290</v>
       </c>
       <c r="AC17" s="24" t="str">
-        <f>IF(AND($T17=6000, ($T17+$W17-$AB17)&gt;=6000),T17,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD17" s="24" t="str">
-        <f>IF(AND($T17=8000, ($T17+$W17-$AB17)&gt;=8000),T17,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE17" s="24" t="str">
-        <f>IF(($T17+$W17-$AB17)&gt;=$T17+8000,W17,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF17" s="25" t="str">
-        <f>IF(AB17&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3289,23 +3295,23 @@
         <v>0</v>
       </c>
       <c r="J18" s="24">
-        <f>(1-$D18)*E18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K18" s="24">
-        <f>(1-$D18)*F18</f>
+        <f t="shared" si="1"/>
         <v>18200</v>
       </c>
       <c r="L18" s="24">
-        <f>G18</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M18" s="24">
-        <f>(1-$D18)*H18</f>
+        <f t="shared" si="3"/>
         <v>700</v>
       </c>
       <c r="N18" s="24">
-        <f>(1-$D18)*I18</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O18" s="24">
@@ -3342,30 +3348,30 @@
         <v>0</v>
       </c>
       <c r="Z18" s="24">
-        <f>SUM(J18:Y18)</f>
+        <f t="shared" si="5"/>
         <v>42930</v>
       </c>
       <c r="AA18" s="24">
         <v>42930</v>
       </c>
       <c r="AB18" s="20">
-        <f>Z18-AA18</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC18" s="24" t="str">
-        <f>IF(AND($T18=6000, ($T18+$W18-$AB18)&gt;=6000),T18,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD18" s="24" t="str">
-        <f>IF(AND($T18=8000, ($T18+$W18-$AB18)&gt;=8000),T18,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE18" s="24" t="str">
-        <f>IF(($T18+$W18-$AB18)&gt;=$T18+8000,W18,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF18" s="25" t="str">
-        <f>IF(AB18&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -3398,23 +3404,23 @@
         <v>5000</v>
       </c>
       <c r="J19" s="24">
-        <f>(1-$D19)*E19</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K19" s="24">
-        <f>(1-$D19)*F19</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L19" s="24">
-        <f>G19</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M19" s="24">
-        <f>(1-$D19)*H19</f>
+        <f t="shared" si="3"/>
         <v>1875</v>
       </c>
       <c r="N19" s="24">
-        <f>(1-$D19)*I19</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O19" s="24">
@@ -3451,30 +3457,30 @@
         <v>0</v>
       </c>
       <c r="Z19" s="24">
-        <f>SUM(J19:Y19)</f>
+        <f t="shared" si="5"/>
         <v>73925</v>
       </c>
       <c r="AA19" s="24">
         <v>51685</v>
       </c>
       <c r="AB19" s="20">
-        <f>Z19-AA19</f>
+        <f t="shared" si="6"/>
         <v>22240</v>
       </c>
       <c r="AC19" s="24" t="str">
-        <f>IF(AND($T19=6000, ($T19+$W19-$AB19)&gt;=6000),T19,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD19" s="24" t="str">
-        <f>IF(AND($T19=8000, ($T19+$W19-$AB19)&gt;=8000),T19,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE19" s="24" t="str">
-        <f>IF(($T19+$W19-$AB19)&gt;=$T19+8000,W19,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF19" s="25" t="str">
-        <f>IF(AB19&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3507,23 +3513,23 @@
         <v>5000</v>
       </c>
       <c r="J20" s="24">
-        <f>(1-$D20)*E20</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K20" s="24">
-        <f>(1-$D20)*F20</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L20" s="24">
-        <f>G20</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M20" s="24">
-        <f>(1-$D20)*H20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N20" s="24">
-        <f>(1-$D20)*I20</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O20" s="24">
@@ -3560,30 +3566,30 @@
         <v>0</v>
       </c>
       <c r="Z20" s="24">
-        <f>SUM(J20:Y20)</f>
+        <f t="shared" si="5"/>
         <v>76770</v>
       </c>
       <c r="AA20" s="24">
         <v>0</v>
       </c>
       <c r="AB20" s="20">
-        <f>Z20-AA20</f>
+        <f t="shared" si="6"/>
         <v>76770</v>
       </c>
       <c r="AC20" s="24" t="str">
-        <f>IF(AND($T20=6000, ($T20+$W20-$AB20)&gt;=6000),T20,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD20" s="24" t="str">
-        <f>IF(AND($T20=8000, ($T20+$W20-$AB20)&gt;=8000),T20,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE20" s="24" t="str">
-        <f>IF(($T20+$W20-$AB20)&gt;=$T20+8000,W20,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF20" s="25" t="str">
-        <f>IF(AB20&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3616,23 +3622,23 @@
         <v>6000</v>
       </c>
       <c r="J21" s="24">
-        <f>(1-$D21)*E21</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K21" s="24">
-        <f>(1-$D21)*F21</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L21" s="24">
-        <f>G21</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M21" s="24">
-        <f>(1-$D21)*H21</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N21" s="24">
-        <f>(1-$D21)*I21</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O21" s="24">
@@ -3669,30 +3675,30 @@
         <v>0</v>
       </c>
       <c r="Z21" s="24">
-        <f>SUM(J21:Y21)</f>
+        <f t="shared" si="5"/>
         <v>62230</v>
       </c>
       <c r="AA21" s="24">
         <v>0</v>
       </c>
       <c r="AB21" s="20">
-        <f>Z21-AA21</f>
+        <f t="shared" si="6"/>
         <v>62230</v>
       </c>
       <c r="AC21" s="24" t="str">
-        <f>IF(AND($T21=6000, ($T21+$W21-$AB21)&gt;=6000),T21,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD21" s="24" t="str">
-        <f>IF(AND($T21=8000, ($T21+$W21-$AB21)&gt;=8000),T21,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE21" s="24" t="str">
-        <f>IF(($T21+$W21-$AB21)&gt;=$T21+8000,W21,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF21" s="25" t="str">
-        <f>IF(AB21&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3725,23 +3731,23 @@
         <v>6000</v>
       </c>
       <c r="J22" s="24">
-        <f>(1-$D22)*E22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K22" s="24">
-        <f>(1-$D22)*F22</f>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="L22" s="24">
-        <f>G22</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M22" s="24">
-        <f>(1-$D22)*H22</f>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="N22" s="24">
-        <f>(1-$D22)*I22</f>
+        <f t="shared" si="4"/>
         <v>4200</v>
       </c>
       <c r="O22" s="24">
@@ -3778,30 +3784,30 @@
         <v>0</v>
       </c>
       <c r="Z22" s="24">
-        <f>SUM(J22:Y22)</f>
+        <f t="shared" si="5"/>
         <v>67530</v>
       </c>
       <c r="AA22" s="24">
         <v>0</v>
       </c>
       <c r="AB22" s="20">
-        <f>Z22-AA22</f>
+        <f t="shared" si="6"/>
         <v>67530</v>
       </c>
       <c r="AC22" s="24" t="str">
-        <f>IF(AND($T22=6000, ($T22+$W22-$AB22)&gt;=6000),T22,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD22" s="24" t="str">
-        <f>IF(AND($T22=8000, ($T22+$W22-$AB22)&gt;=8000),T22,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE22" s="24" t="str">
-        <f>IF(($T22+$W22-$AB22)&gt;=$T22+8000,W22,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF22" s="25" t="str">
-        <f>IF(AB22&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3834,23 +3840,23 @@
         <v>5000</v>
       </c>
       <c r="J23" s="24">
-        <f>(1-$D23)*E23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K23" s="24">
-        <f>(1-$D23)*F23</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L23" s="24">
-        <f>G23</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M23" s="24">
-        <f>(1-$D23)*H23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N23" s="24">
-        <f>(1-$D23)*I23</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O23" s="24">
@@ -3887,30 +3893,30 @@
         <v>0</v>
       </c>
       <c r="Z23" s="24">
-        <f>SUM(J23:Y23)</f>
+        <f t="shared" si="5"/>
         <v>66230</v>
       </c>
       <c r="AA23" s="24">
         <v>0</v>
       </c>
       <c r="AB23" s="20">
-        <f>Z23-AA23</f>
+        <f t="shared" si="6"/>
         <v>66230</v>
       </c>
       <c r="AC23" s="24" t="str">
-        <f>IF(AND($T23=6000, ($T23+$W23-$AB23)&gt;=6000),T23,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD23" s="24" t="str">
-        <f>IF(AND($T23=8000, ($T23+$W23-$AB23)&gt;=8000),T23,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE23" s="24" t="str">
-        <f>IF(($T23+$W23-$AB23)&gt;=$T23+8000,W23,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF23" s="25" t="str">
-        <f>IF(AB23&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -3943,23 +3949,23 @@
         <v>5000</v>
       </c>
       <c r="J24" s="24">
-        <f>(1-$D24)*E24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K24" s="24">
-        <f>(1-$D24)*F24</f>
+        <f t="shared" si="1"/>
         <v>21000</v>
       </c>
       <c r="L24" s="24">
-        <f>G24</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M24" s="24">
-        <f>(1-$D24)*H24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N24" s="24">
-        <f>(1-$D24)*I24</f>
+        <f t="shared" si="4"/>
         <v>3750</v>
       </c>
       <c r="O24" s="24">
@@ -3996,30 +4002,30 @@
         <v>0</v>
       </c>
       <c r="Z24" s="24">
-        <f>SUM(J24:Y24)</f>
+        <f t="shared" si="5"/>
         <v>66230</v>
       </c>
       <c r="AA24" s="24">
         <v>0</v>
       </c>
       <c r="AB24" s="20">
-        <f>Z24-AA24</f>
+        <f t="shared" si="6"/>
         <v>66230</v>
       </c>
       <c r="AC24" s="24" t="str">
-        <f>IF(AND($T24=6000, ($T24+$W24-$AB24)&gt;=6000),T24,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD24" s="24" t="str">
-        <f>IF(AND($T24=8000, ($T24+$W24-$AB24)&gt;=8000),T24,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE24" s="24" t="str">
-        <f>IF(($T24+$W24-$AB24)&gt;=$T24+8000,W24,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF24" s="25" t="str">
-        <f>IF(AB24&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4052,23 +4058,23 @@
         <v>6000</v>
       </c>
       <c r="J25" s="24">
-        <f>(1-$D25)*E25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K25" s="24">
-        <f>(1-$D25)*F25</f>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="L25" s="24">
-        <f>G25</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M25" s="24">
-        <f>(1-$D25)*H25</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N25" s="24">
-        <f>(1-$D25)*I25</f>
+        <f t="shared" si="4"/>
         <v>6000</v>
       </c>
       <c r="O25" s="24">
@@ -4105,30 +4111,30 @@
         <v>0</v>
       </c>
       <c r="Z25" s="24">
-        <f>SUM(J25:Y25)</f>
+        <f t="shared" si="5"/>
         <v>79830</v>
       </c>
       <c r="AA25" s="24">
         <v>60000</v>
       </c>
       <c r="AB25" s="20">
-        <f>Z25-AA25</f>
+        <f t="shared" si="6"/>
         <v>19830</v>
       </c>
       <c r="AC25" s="24" t="str">
-        <f>IF(AND($T25=6000, ($T25+$W25-$AB25)&gt;=6000),T25,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD25" s="24" t="str">
-        <f>IF(AND($T25=8000, ($T25+$W25-$AB25)&gt;=8000),T25,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE25" s="24" t="str">
-        <f>IF(($T25+$W25-$AB25)&gt;=$T25+8000,W25,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF25" s="25" t="str">
-        <f>IF(AB25&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4161,23 +4167,23 @@
         <v>6000</v>
       </c>
       <c r="J26" s="24">
-        <f>(1-$D26)*E26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K26" s="24">
-        <f>(1-$D26)*F26</f>
+        <f t="shared" si="1"/>
         <v>16500</v>
       </c>
       <c r="L26" s="24">
-        <f>G26</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M26" s="24">
-        <f>(1-$D26)*H26</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N26" s="24">
-        <f>(1-$D26)*I26</f>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="O26" s="24">
@@ -4214,30 +4220,30 @@
         <v>0</v>
       </c>
       <c r="Z26" s="24">
-        <f>SUM(J26:Y26)</f>
+        <f t="shared" si="5"/>
         <v>62230</v>
       </c>
       <c r="AA26" s="24">
         <v>0</v>
       </c>
       <c r="AB26" s="20">
-        <f>Z26-AA26</f>
+        <f t="shared" si="6"/>
         <v>62230</v>
       </c>
       <c r="AC26" s="24" t="str">
-        <f>IF(AND($T26=6000, ($T26+$W26-$AB26)&gt;=6000),T26,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD26" s="24" t="str">
-        <f>IF(AND($T26=8000, ($T26+$W26-$AB26)&gt;=8000),T26,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE26" s="24" t="str">
-        <f>IF(($T26+$W26-$AB26)&gt;=$T26+8000,W26,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF26" s="25" t="str">
-        <f>IF(AB26&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4270,23 +4276,23 @@
         <v>0</v>
       </c>
       <c r="J27" s="24">
-        <f>(1-$D27)*E27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K27" s="24">
-        <f>(1-$D27)*F27</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L27" s="24">
-        <f>G27</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M27" s="24">
-        <f>(1-$D27)*H27</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N27" s="24">
-        <f>(1-$D27)*I27</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O27" s="24">
@@ -4323,30 +4329,30 @@
         <v>-400</v>
       </c>
       <c r="Z27" s="24">
-        <f>SUM(J27:Y27)</f>
+        <f t="shared" si="5"/>
         <v>56630</v>
       </c>
       <c r="AA27" s="24">
         <v>0</v>
       </c>
       <c r="AB27" s="20">
-        <f>Z27-AA27</f>
+        <f t="shared" si="6"/>
         <v>56630</v>
       </c>
       <c r="AC27" s="24" t="str">
-        <f>IF(AND($T27=6000, ($T27+$W27-$AB27)&gt;=6000),T27,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD27" s="24" t="str">
-        <f>IF(AND($T27=8000, ($T27+$W27-$AB27)&gt;=8000),T27,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE27" s="24" t="str">
-        <f>IF(($T27+$W27-$AB27)&gt;=$T27+8000,W27,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF27" s="25" t="str">
-        <f>IF(AB27&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4379,23 +4385,23 @@
         <v>0</v>
       </c>
       <c r="J28" s="24">
-        <f>(1-$D28)*E28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K28" s="24">
-        <f>(1-$D28)*F28</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L28" s="24">
-        <f>G28</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M28" s="24">
-        <f>(1-$D28)*H28</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N28" s="24">
-        <f>(1-$D28)*I28</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="24">
@@ -4432,30 +4438,30 @@
         <v>0</v>
       </c>
       <c r="Z28" s="24">
-        <f>SUM(J28:Y28)</f>
+        <f t="shared" si="5"/>
         <v>43140</v>
       </c>
       <c r="AA28" s="24">
         <v>0</v>
       </c>
       <c r="AB28" s="20">
-        <f>Z28-AA28</f>
+        <f t="shared" si="6"/>
         <v>43140</v>
       </c>
       <c r="AC28" s="24" t="str">
-        <f>IF(AND($T28=6000, ($T28+$W28-$AB28)&gt;=6000),T28,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD28" s="24" t="str">
-        <f>IF(AND($T28=8000, ($T28+$W28-$AB28)&gt;=8000),T28,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE28" s="24" t="str">
-        <f>IF(($T28+$W28-$AB28)&gt;=$T28+8000,W28,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF28" s="25" t="str">
-        <f>IF(AB28&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4488,23 +4494,23 @@
         <v>0</v>
       </c>
       <c r="J29" s="24">
-        <f>(1-$D29)*E29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K29" s="24">
-        <f>(1-$D29)*F29</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L29" s="24">
-        <f>G29</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M29" s="24">
-        <f>(1-$D29)*H29</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N29" s="24">
-        <f>(1-$D29)*I29</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="24">
@@ -4541,30 +4547,30 @@
         <v>11000</v>
       </c>
       <c r="Z29" s="24">
-        <f>SUM(J29:Y29)</f>
+        <f t="shared" si="5"/>
         <v>62030</v>
       </c>
       <c r="AA29" s="24">
         <v>0</v>
       </c>
       <c r="AB29" s="20">
-        <f>Z29-AA29</f>
+        <f t="shared" si="6"/>
         <v>62030</v>
       </c>
       <c r="AC29" s="24" t="str">
-        <f>IF(AND($T29=6000, ($T29+$W29-$AB29)&gt;=6000),T29,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD29" s="24" t="str">
-        <f>IF(AND($T29=8000, ($T29+$W29-$AB29)&gt;=8000),T29,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE29" s="24" t="str">
-        <f>IF(($T29+$W29-$AB29)&gt;=$T29+8000,W29,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF29" s="25" t="str">
-        <f>IF(AB29&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4597,23 +4603,23 @@
         <v>8000</v>
       </c>
       <c r="J30" s="24">
-        <f>(1-$D30)*E30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K30" s="24">
-        <f>(1-$D30)*F30</f>
+        <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="L30" s="24">
-        <f>G30</f>
+        <f t="shared" si="2"/>
         <v>5000</v>
       </c>
       <c r="M30" s="24">
-        <f>(1-$D30)*H30</f>
+        <f t="shared" si="3"/>
         <v>2000</v>
       </c>
       <c r="N30" s="24">
-        <f>(1-$D30)*I30</f>
+        <f t="shared" si="4"/>
         <v>8000</v>
       </c>
       <c r="O30" s="24">
@@ -4650,30 +4656,30 @@
         <v>0</v>
       </c>
       <c r="Z30" s="24">
-        <f>SUM(J30:Y30)</f>
+        <f t="shared" si="5"/>
         <v>81210</v>
       </c>
       <c r="AA30" s="24">
         <v>0</v>
       </c>
       <c r="AB30" s="20">
-        <f>Z30-AA30</f>
+        <f t="shared" si="6"/>
         <v>81210</v>
       </c>
       <c r="AC30" s="24" t="str">
-        <f>IF(AND($T30=6000, ($T30+$W30-$AB30)&gt;=6000),T30,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD30" s="24" t="str">
-        <f>IF(AND($T30=8000, ($T30+$W30-$AB30)&gt;=8000),T30,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE30" s="24" t="str">
-        <f>IF(($T30+$W30-$AB30)&gt;=$T30+8000,W30,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF30" s="25" t="str">
-        <f>IF(AB30&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4706,23 +4712,23 @@
         <v>0</v>
       </c>
       <c r="J31" s="24">
-        <f>(1-$D31)*E31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K31" s="24">
-        <f>(1-$D31)*F31</f>
+        <f t="shared" si="1"/>
         <v>26000</v>
       </c>
       <c r="L31" s="24">
-        <f>G31</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M31" s="24">
-        <f>(1-$D31)*H31</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N31" s="24">
-        <f>(1-$D31)*I31</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O31" s="24">
@@ -4759,30 +4765,30 @@
         <v>0</v>
       </c>
       <c r="Z31" s="24">
-        <f>SUM(J31:Y31)</f>
+        <f t="shared" si="5"/>
         <v>43140</v>
       </c>
       <c r="AA31" s="24">
         <v>0</v>
       </c>
       <c r="AB31" s="20">
-        <f>Z31-AA31</f>
+        <f t="shared" si="6"/>
         <v>43140</v>
       </c>
       <c r="AC31" s="24" t="str">
-        <f>IF(AND($T31=6000, ($T31+$W31-$AB31)&gt;=6000),T31,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD31" s="24" t="str">
-        <f>IF(AND($T31=8000, ($T31+$W31-$AB31)&gt;=8000),T31,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE31" s="24" t="str">
-        <f>IF(($T31+$W31-$AB31)&gt;=$T31+8000,W31,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF31" s="25" t="str">
-        <f>IF(AB31&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4815,23 +4821,23 @@
         <v>0</v>
       </c>
       <c r="J32" s="24">
-        <f>(1-$D32)*E32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K32" s="24">
-        <f>(1-$D32)*F32</f>
+        <f t="shared" si="1"/>
         <v>19500</v>
       </c>
       <c r="L32" s="24">
-        <f>G32</f>
+        <f t="shared" si="2"/>
         <v>2000</v>
       </c>
       <c r="M32" s="24">
-        <f>(1-$D32)*H32</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N32" s="24">
-        <f>(1-$D32)*I32</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O32" s="24">
@@ -4868,30 +4874,30 @@
         <v>0</v>
       </c>
       <c r="Z32" s="24">
-        <f>SUM(J32:Y32)</f>
+        <f t="shared" si="5"/>
         <v>24550</v>
       </c>
       <c r="AA32" s="24">
         <v>1300</v>
       </c>
       <c r="AB32" s="20">
-        <f>Z32-AA32</f>
+        <f t="shared" si="6"/>
         <v>23250</v>
       </c>
       <c r="AC32" s="24" t="str">
-        <f>IF(AND($T32=6000, ($T32+$W32-$AB32)&gt;=6000),T32,"")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="AD32" s="24" t="str">
-        <f>IF(AND($T32=8000, ($T32+$W32-$AB32)&gt;=8000),T32,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE32" s="24" t="str">
-        <f>IF(($T32+$W32-$AB32)&gt;=$T32+8000,W32,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF32" s="25" t="str">
-        <f>IF(AB32&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
@@ -4924,23 +4930,23 @@
         <v>0</v>
       </c>
       <c r="J33" s="24">
-        <f>(1-$D33)*E33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K33" s="24">
-        <f>(1-$D33)*F33</f>
+        <f t="shared" si="1"/>
         <v>18200</v>
       </c>
       <c r="L33" s="24">
-        <f>G33</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M33" s="24">
-        <f>(1-$D33)*H33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N33" s="24">
-        <f>(1-$D33)*I33</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O33" s="24">
@@ -4977,30 +4983,30 @@
         <v>0</v>
       </c>
       <c r="Z33" s="24">
-        <f>SUM(J33:Y33)</f>
+        <f t="shared" si="5"/>
         <v>49130</v>
       </c>
       <c r="AA33" s="24">
         <v>49130</v>
       </c>
       <c r="AB33" s="20">
-        <f>Z33-AA33</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC33" s="24">
-        <f>IF(AND($T33=6000, ($T33+$W33-$AB33)&gt;=6000),T33,"")</f>
+        <f t="shared" si="7"/>
         <v>6000</v>
       </c>
       <c r="AD33" s="24" t="str">
-        <f>IF(AND($T33=8000, ($T33+$W33-$AB33)&gt;=8000),T33,"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AE33" s="24" t="str">
-        <f>IF(($T33+$W33-$AB33)&gt;=$T33+8000,W33,"")</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AF33" s="25" t="str">
-        <f>IF(AB33&lt;=0,"BONUS","")</f>
+        <f t="shared" si="10"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -5033,23 +5039,23 @@
         <v>0</v>
       </c>
       <c r="J34" s="24">
-        <f>(1-$D34)*E34</f>
+        <f t="shared" ref="J34:J65" si="11">(1-$D34)*E34</f>
         <v>0</v>
       </c>
       <c r="K34" s="24">
-        <f>(1-$D34)*F34</f>
+        <f t="shared" ref="K34:K65" si="12">(1-$D34)*F34</f>
         <v>19500</v>
       </c>
       <c r="L34" s="24">
-        <f>G34</f>
+        <f t="shared" ref="L34:L65" si="13">G34</f>
         <v>4000</v>
       </c>
       <c r="M34" s="24">
-        <f>(1-$D34)*H34</f>
+        <f t="shared" ref="M34:M65" si="14">(1-$D34)*H34</f>
         <v>0</v>
       </c>
       <c r="N34" s="24">
-        <f>(1-$D34)*I34</f>
+        <f t="shared" ref="N34:N65" si="15">(1-$D34)*I34</f>
         <v>0</v>
       </c>
       <c r="O34" s="24">
@@ -5086,30 +5092,30 @@
         <v>0</v>
       </c>
       <c r="Z34" s="24">
-        <f>SUM(J34:Y34)</f>
+        <f t="shared" ref="Z34:Z65" si="16">SUM(J34:Y34)</f>
         <v>65160</v>
       </c>
       <c r="AA34" s="24">
         <v>0</v>
       </c>
       <c r="AB34" s="20">
-        <f>Z34-AA34</f>
+        <f t="shared" ref="AB34:AB65" si="17">Z34-AA34</f>
         <v>65160</v>
       </c>
       <c r="AC34" s="24" t="str">
-        <f>IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
+        <f t="shared" ref="AC34:AC65" si="18">IF(AND($T34=6000, ($T34+$W34-$AB34)&gt;=6000),T34,"")</f>
         <v/>
       </c>
       <c r="AD34" s="24" t="str">
-        <f>IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
+        <f t="shared" ref="AD34:AD65" si="19">IF(AND($T34=8000, ($T34+$W34-$AB34)&gt;=8000),T34,"")</f>
         <v/>
       </c>
       <c r="AE34" s="24" t="str">
-        <f>IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
+        <f t="shared" ref="AE34:AE65" si="20">IF(($T34+$W34-$AB34)&gt;=$T34+8000,W34,"")</f>
         <v/>
       </c>
       <c r="AF34" s="25" t="str">
-        <f>IF(AB34&lt;=0,"BONUS","")</f>
+        <f t="shared" ref="AF34:AF65" si="21">IF(AB34&lt;=0,"BONUS","")</f>
         <v/>
       </c>
     </row>
@@ -5142,23 +5148,23 @@
         <v>5000</v>
       </c>
       <c r="J35" s="24">
-        <f>(1-$D35)*E35</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K35" s="24">
-        <f>(1-$D35)*F35</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L35" s="24">
-        <f>G35</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M35" s="24">
-        <f>(1-$D35)*H35</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N35" s="24">
-        <f>(1-$D35)*I35</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O35" s="24">
@@ -5195,30 +5201,30 @@
         <v>250</v>
       </c>
       <c r="Z35" s="24">
-        <f>SUM(J35:Y35)</f>
+        <f t="shared" si="16"/>
         <v>72480</v>
       </c>
       <c r="AA35" s="24">
         <v>0</v>
       </c>
       <c r="AB35" s="20">
-        <f>Z35-AA35</f>
+        <f t="shared" si="17"/>
         <v>72480</v>
       </c>
       <c r="AC35" s="24" t="str">
-        <f>IF(AND($T35=6000, ($T35+$W35-$AB35)&gt;=6000),T35,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD35" s="24" t="str">
-        <f>IF(AND($T35=8000, ($T35+$W35-$AB35)&gt;=8000),T35,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE35" s="24" t="str">
-        <f>IF(($T35+$W35-$AB35)&gt;=$T35+8000,W35,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF35" s="25" t="str">
-        <f>IF(AB35&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5251,23 +5257,23 @@
         <v>0</v>
       </c>
       <c r="J36" s="24">
-        <f>(1-$D36)*E36</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K36" s="24">
-        <f>(1-$D36)*F36</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L36" s="24">
-        <f>G36</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M36" s="24">
-        <f>(1-$D36)*H36</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N36" s="24">
-        <f>(1-$D36)*I36</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O36" s="24">
@@ -5304,30 +5310,30 @@
         <v>0</v>
       </c>
       <c r="Z36" s="24">
-        <f>SUM(J36:Y36)</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AA36" s="24">
         <v>0</v>
       </c>
       <c r="AB36" s="20">
-        <f>Z36-AA36</f>
+        <f t="shared" si="17"/>
         <v>43140</v>
       </c>
       <c r="AC36" s="24" t="str">
-        <f>IF(AND($T36=6000, ($T36+$W36-$AB36)&gt;=6000),T36,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD36" s="24" t="str">
-        <f>IF(AND($T36=8000, ($T36+$W36-$AB36)&gt;=8000),T36,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE36" s="24" t="str">
-        <f>IF(($T36+$W36-$AB36)&gt;=$T36+8000,W36,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF36" s="25" t="str">
-        <f>IF(AB36&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5360,23 +5366,23 @@
         <v>0</v>
       </c>
       <c r="J37" s="24">
-        <f>(1-$D37)*E37</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K37" s="24">
-        <f>(1-$D37)*F37</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L37" s="24">
-        <f>G37</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M37" s="24">
-        <f>(1-$D37)*H37</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N37" s="24">
-        <f>(1-$D37)*I37</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O37" s="24">
@@ -5413,30 +5419,30 @@
         <v>0</v>
       </c>
       <c r="Z37" s="24">
-        <f>SUM(J37:Y37)</f>
+        <f t="shared" si="16"/>
         <v>56930</v>
       </c>
       <c r="AA37" s="24">
         <v>0</v>
       </c>
       <c r="AB37" s="20">
-        <f>Z37-AA37</f>
+        <f t="shared" si="17"/>
         <v>56930</v>
       </c>
       <c r="AC37" s="24" t="str">
-        <f>IF(AND($T37=6000, ($T37+$W37-$AB37)&gt;=6000),T37,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD37" s="24" t="str">
-        <f>IF(AND($T37=8000, ($T37+$W37-$AB37)&gt;=8000),T37,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE37" s="24" t="str">
-        <f>IF(($T37+$W37-$AB37)&gt;=$T37+8000,W37,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF37" s="25" t="str">
-        <f>IF(AB37&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5469,23 +5475,23 @@
         <v>0</v>
       </c>
       <c r="J38" s="24">
-        <f>(1-$D38)*E38</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K38" s="24">
-        <f>(1-$D38)*F38</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L38" s="24">
-        <f>G38</f>
+        <f t="shared" si="13"/>
         <v>2000</v>
       </c>
       <c r="M38" s="24">
-        <f>(1-$D38)*H38</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N38" s="24">
-        <f>(1-$D38)*I38</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O38" s="24">
@@ -5522,30 +5528,30 @@
         <v>0</v>
       </c>
       <c r="Z38" s="24">
-        <f>SUM(J38:Y38)</f>
+        <f t="shared" si="16"/>
         <v>31050</v>
       </c>
       <c r="AA38" s="24">
         <v>0</v>
       </c>
       <c r="AB38" s="20">
-        <f>Z38-AA38</f>
+        <f t="shared" si="17"/>
         <v>31050</v>
       </c>
       <c r="AC38" s="24" t="str">
-        <f>IF(AND($T38=6000, ($T38+$W38-$AB38)&gt;=6000),T38,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD38" s="24" t="str">
-        <f>IF(AND($T38=8000, ($T38+$W38-$AB38)&gt;=8000),T38,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE38" s="24" t="str">
-        <f>IF(($T38+$W38-$AB38)&gt;=$T38+8000,W38,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF38" s="25" t="str">
-        <f>IF(AB38&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5578,23 +5584,23 @@
         <v>0</v>
       </c>
       <c r="J39" s="24">
-        <f>(1-$D39)*E39</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K39" s="24">
-        <f>(1-$D39)*F39</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L39" s="24">
-        <f>G39</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M39" s="24">
-        <f>(1-$D39)*H39</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N39" s="24">
-        <f>(1-$D39)*I39</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O39" s="24">
@@ -5631,30 +5637,30 @@
         <v>0</v>
       </c>
       <c r="Z39" s="24">
-        <f>SUM(J39:Y39)</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AA39" s="24">
         <v>0</v>
       </c>
       <c r="AB39" s="20">
-        <f>Z39-AA39</f>
+        <f t="shared" si="17"/>
         <v>43140</v>
       </c>
       <c r="AC39" s="24" t="str">
-        <f>IF(AND($T39=6000, ($T39+$W39-$AB39)&gt;=6000),T39,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD39" s="24" t="str">
-        <f>IF(AND($T39=8000, ($T39+$W39-$AB39)&gt;=8000),T39,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE39" s="24" t="str">
-        <f>IF(($T39+$W39-$AB39)&gt;=$T39+8000,W39,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF39" s="25" t="str">
-        <f>IF(AB39&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5687,23 +5693,23 @@
         <v>6000</v>
       </c>
       <c r="J40" s="24">
-        <f>(1-$D40)*E40</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K40" s="24">
-        <f>(1-$D40)*F40</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L40" s="24">
-        <f>G40</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M40" s="24">
-        <f>(1-$D40)*H40</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N40" s="24">
-        <f>(1-$D40)*I40</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O40" s="24">
@@ -5740,30 +5746,30 @@
         <v>-30</v>
       </c>
       <c r="Z40" s="24">
-        <f>SUM(J40:Y40)</f>
+        <f t="shared" si="16"/>
         <v>70200</v>
       </c>
       <c r="AA40" s="24">
         <v>0</v>
       </c>
       <c r="AB40" s="20">
-        <f>Z40-AA40</f>
+        <f t="shared" si="17"/>
         <v>70200</v>
       </c>
       <c r="AC40" s="24" t="str">
-        <f>IF(AND($T40=6000, ($T40+$W40-$AB40)&gt;=6000),T40,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD40" s="24" t="str">
-        <f>IF(AND($T40=8000, ($T40+$W40-$AB40)&gt;=8000),T40,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE40" s="24" t="str">
-        <f>IF(($T40+$W40-$AB40)&gt;=$T40+8000,W40,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF40" s="25" t="str">
-        <f>IF(AB40&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5796,23 +5802,23 @@
         <v>6000</v>
       </c>
       <c r="J41" s="24">
-        <f>(1-$D41)*E41</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K41" s="24">
-        <f>(1-$D41)*F41</f>
+        <f t="shared" si="12"/>
         <v>33000</v>
       </c>
       <c r="L41" s="24">
-        <f>G41</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M41" s="24">
-        <f>(1-$D41)*H41</f>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N41" s="24">
-        <f>(1-$D41)*I41</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O41" s="24">
@@ -5849,30 +5855,30 @@
         <v>-8970</v>
       </c>
       <c r="Z41" s="24">
-        <f>SUM(J41:Y41)</f>
+        <f t="shared" si="16"/>
         <v>73760</v>
       </c>
       <c r="AA41" s="24">
         <v>0</v>
       </c>
       <c r="AB41" s="20">
-        <f>Z41-AA41</f>
+        <f t="shared" si="17"/>
         <v>73760</v>
       </c>
       <c r="AC41" s="24" t="str">
-        <f>IF(AND($T41=6000, ($T41+$W41-$AB41)&gt;=6000),T41,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD41" s="24" t="str">
-        <f>IF(AND($T41=8000, ($T41+$W41-$AB41)&gt;=8000),T41,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE41" s="24" t="str">
-        <f>IF(($T41+$W41-$AB41)&gt;=$T41+8000,W41,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF41" s="25" t="str">
-        <f>IF(AB41&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -5905,23 +5911,23 @@
         <v>8000</v>
       </c>
       <c r="J42" s="24">
-        <f>(1-$D42)*E42</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K42" s="24">
-        <f>(1-$D42)*F42</f>
+        <f t="shared" si="12"/>
         <v>40000</v>
       </c>
       <c r="L42" s="24">
-        <f>G42</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M42" s="24">
-        <f>(1-$D42)*H42</f>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N42" s="24">
-        <f>(1-$D42)*I42</f>
+        <f t="shared" si="15"/>
         <v>8000</v>
       </c>
       <c r="O42" s="24">
@@ -5958,30 +5964,30 @@
         <v>120</v>
       </c>
       <c r="Z42" s="24">
-        <f>SUM(J42:Y42)</f>
+        <f t="shared" si="16"/>
         <v>81330</v>
       </c>
       <c r="AA42" s="24">
         <v>0</v>
       </c>
       <c r="AB42" s="20">
-        <f>Z42-AA42</f>
+        <f t="shared" si="17"/>
         <v>81330</v>
       </c>
       <c r="AC42" s="24" t="str">
-        <f>IF(AND($T42=6000, ($T42+$W42-$AB42)&gt;=6000),T42,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD42" s="24" t="str">
-        <f>IF(AND($T42=8000, ($T42+$W42-$AB42)&gt;=8000),T42,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE42" s="24" t="str">
-        <f>IF(($T42+$W42-$AB42)&gt;=$T42+8000,W42,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF42" s="25" t="str">
-        <f>IF(AB42&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6014,23 +6020,23 @@
         <v>6000</v>
       </c>
       <c r="J43" s="24">
-        <f>(1-$D43)*E43</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K43" s="24">
-        <f>(1-$D43)*F43</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L43" s="24">
-        <f>G43</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M43" s="24">
-        <f>(1-$D43)*H43</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N43" s="24">
-        <f>(1-$D43)*I43</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O43" s="24">
@@ -6067,30 +6073,30 @@
         <v>480</v>
       </c>
       <c r="Z43" s="24">
-        <f>SUM(J43:Y43)</f>
+        <f t="shared" si="16"/>
         <v>62710</v>
       </c>
       <c r="AA43" s="24">
         <v>0</v>
       </c>
       <c r="AB43" s="20">
-        <f>Z43-AA43</f>
+        <f t="shared" si="17"/>
         <v>62710</v>
       </c>
       <c r="AC43" s="24" t="str">
-        <f>IF(AND($T43=6000, ($T43+$W43-$AB43)&gt;=6000),T43,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD43" s="24" t="str">
-        <f>IF(AND($T43=8000, ($T43+$W43-$AB43)&gt;=8000),T43,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE43" s="24" t="str">
-        <f>IF(($T43+$W43-$AB43)&gt;=$T43+8000,W43,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF43" s="25" t="str">
-        <f>IF(AB43&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6123,23 +6129,23 @@
         <v>6000</v>
       </c>
       <c r="J44" s="24">
-        <f>(1-$D44)*E44</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K44" s="24">
-        <f>(1-$D44)*F44</f>
+        <f t="shared" si="12"/>
         <v>24750</v>
       </c>
       <c r="L44" s="24">
-        <f>G44</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M44" s="24">
-        <f>(1-$D44)*H44</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N44" s="24">
-        <f>(1-$D44)*I44</f>
+        <f t="shared" si="15"/>
         <v>4500</v>
       </c>
       <c r="O44" s="24">
@@ -6176,30 +6182,30 @@
         <v>0</v>
       </c>
       <c r="Z44" s="24">
-        <f>SUM(J44:Y44)</f>
+        <f t="shared" si="16"/>
         <v>72480</v>
       </c>
       <c r="AA44" s="24">
         <v>0</v>
       </c>
       <c r="AB44" s="20">
-        <f>Z44-AA44</f>
+        <f t="shared" si="17"/>
         <v>72480</v>
       </c>
       <c r="AC44" s="24" t="str">
-        <f>IF(AND($T44=6000, ($T44+$W44-$AB44)&gt;=6000),T44,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD44" s="24" t="str">
-        <f>IF(AND($T44=8000, ($T44+$W44-$AB44)&gt;=8000),T44,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE44" s="24" t="str">
-        <f>IF(($T44+$W44-$AB44)&gt;=$T44+8000,W44,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF44" s="25" t="str">
-        <f>IF(AB44&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6232,23 +6238,23 @@
         <v>8000</v>
       </c>
       <c r="J45" s="24">
-        <f>(1-$D45)*E45</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K45" s="24">
-        <f>(1-$D45)*F45</f>
+        <f t="shared" si="12"/>
         <v>30000</v>
       </c>
       <c r="L45" s="24">
-        <f>G45</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M45" s="24">
-        <f>(1-$D45)*H45</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N45" s="24">
-        <f>(1-$D45)*I45</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O45" s="24">
@@ -6285,30 +6291,30 @@
         <v>0</v>
       </c>
       <c r="Z45" s="24">
-        <f>SUM(J45:Y45)</f>
+        <f t="shared" si="16"/>
         <v>68710</v>
       </c>
       <c r="AA45" s="24">
         <v>0</v>
       </c>
       <c r="AB45" s="20">
-        <f>Z45-AA45</f>
+        <f t="shared" si="17"/>
         <v>68710</v>
       </c>
       <c r="AC45" s="24" t="str">
-        <f>IF(AND($T45=6000, ($T45+$W45-$AB45)&gt;=6000),T45,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD45" s="24" t="str">
-        <f>IF(AND($T45=8000, ($T45+$W45-$AB45)&gt;=8000),T45,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE45" s="24" t="str">
-        <f>IF(($T45+$W45-$AB45)&gt;=$T45+8000,W45,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF45" s="25" t="str">
-        <f>IF(AB45&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6341,23 +6347,23 @@
         <v>0</v>
       </c>
       <c r="J46" s="24">
-        <f>(1-$D46)*E46</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K46" s="24">
-        <f>(1-$D46)*F46</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L46" s="24">
-        <f>G46</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M46" s="24">
-        <f>(1-$D46)*H46</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N46" s="24">
-        <f>(1-$D46)*I46</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O46" s="24">
@@ -6394,30 +6400,30 @@
         <v>0</v>
       </c>
       <c r="Z46" s="24">
-        <f>SUM(J46:Y46)</f>
+        <f t="shared" si="16"/>
         <v>43140</v>
       </c>
       <c r="AA46" s="24">
         <v>0</v>
       </c>
       <c r="AB46" s="20">
-        <f>Z46-AA46</f>
+        <f t="shared" si="17"/>
         <v>43140</v>
       </c>
       <c r="AC46" s="24" t="str">
-        <f>IF(AND($T46=6000, ($T46+$W46-$AB46)&gt;=6000),T46,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD46" s="24" t="str">
-        <f>IF(AND($T46=8000, ($T46+$W46-$AB46)&gt;=8000),T46,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE46" s="24" t="str">
-        <f>IF(($T46+$W46-$AB46)&gt;=$T46+8000,W46,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF46" s="25" t="str">
-        <f>IF(AB46&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6450,23 +6456,23 @@
         <v>0</v>
       </c>
       <c r="J47" s="24">
-        <f>(1-$D47)*E47</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K47" s="24">
-        <f>(1-$D47)*F47</f>
+        <f t="shared" si="12"/>
         <v>19500</v>
       </c>
       <c r="L47" s="24">
-        <f>G47</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M47" s="24">
-        <f>(1-$D47)*H47</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N47" s="24">
-        <f>(1-$D47)*I47</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O47" s="24">
@@ -6503,30 +6509,30 @@
         <v>18500</v>
       </c>
       <c r="Z47" s="24">
-        <f>SUM(J47:Y47)</f>
+        <f t="shared" si="16"/>
         <v>83660</v>
       </c>
       <c r="AA47" s="24">
         <v>48000</v>
       </c>
       <c r="AB47" s="20">
-        <f>Z47-AA47</f>
+        <f t="shared" si="17"/>
         <v>35660</v>
       </c>
       <c r="AC47" s="24" t="str">
-        <f>IF(AND($T47=6000, ($T47+$W47-$AB47)&gt;=6000),T47,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD47" s="24" t="str">
-        <f>IF(AND($T47=8000, ($T47+$W47-$AB47)&gt;=8000),T47,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE47" s="24" t="str">
-        <f>IF(($T47+$W47-$AB47)&gt;=$T47+8000,W47,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF47" s="25" t="str">
-        <f>IF(AB47&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6559,23 +6565,23 @@
         <v>5000</v>
       </c>
       <c r="J48" s="24">
-        <f>(1-$D48)*E48</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K48" s="24">
-        <f>(1-$D48)*F48</f>
+        <f t="shared" si="12"/>
         <v>26600</v>
       </c>
       <c r="L48" s="24">
-        <f>G48</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M48" s="24">
-        <f>(1-$D48)*H48</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N48" s="24">
-        <f>(1-$D48)*I48</f>
+        <f t="shared" si="15"/>
         <v>4750</v>
       </c>
       <c r="O48" s="24">
@@ -6612,30 +6618,30 @@
         <v>0</v>
       </c>
       <c r="Z48" s="24">
-        <f>SUM(J48:Y48)</f>
+        <f t="shared" si="16"/>
         <v>77370</v>
       </c>
       <c r="AA48" s="24">
         <v>79020</v>
       </c>
       <c r="AB48" s="20">
-        <f>Z48-AA48</f>
+        <f t="shared" si="17"/>
         <v>-1650</v>
       </c>
       <c r="AC48" s="24" t="str">
-        <f>IF(AND($T48=6000, ($T48+$W48-$AB48)&gt;=6000),T48,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD48" s="24" t="str">
-        <f>IF(AND($T48=8000, ($T48+$W48-$AB48)&gt;=8000),T48,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE48" s="24" t="str">
-        <f>IF(($T48+$W48-$AB48)&gt;=$T48+8000,W48,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF48" s="25" t="str">
-        <f>IF(AB48&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -6668,23 +6674,23 @@
         <v>5000</v>
       </c>
       <c r="J49" s="24">
-        <f>(1-$D49)*E49</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K49" s="24">
-        <f>(1-$D49)*F49</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L49" s="24">
-        <f>G49</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M49" s="24">
-        <f>(1-$D49)*H49</f>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N49" s="24">
-        <f>(1-$D49)*I49</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O49" s="24">
@@ -6721,30 +6727,30 @@
         <v>0</v>
       </c>
       <c r="Z49" s="24">
-        <f>SUM(J49:Y49)</f>
+        <f t="shared" si="16"/>
         <v>82800</v>
       </c>
       <c r="AA49" s="24">
         <v>42350</v>
       </c>
       <c r="AB49" s="20">
-        <f>Z49-AA49</f>
+        <f t="shared" si="17"/>
         <v>40450</v>
       </c>
       <c r="AC49" s="24" t="str">
-        <f>IF(AND($T49=6000, ($T49+$W49-$AB49)&gt;=6000),T49,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD49" s="24" t="str">
-        <f>IF(AND($T49=8000, ($T49+$W49-$AB49)&gt;=8000),T49,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE49" s="24" t="str">
-        <f>IF(($T49+$W49-$AB49)&gt;=$T49+8000,W49,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF49" s="25" t="str">
-        <f>IF(AB49&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6777,23 +6783,23 @@
         <v>6000</v>
       </c>
       <c r="J50" s="24">
-        <f>(1-$D50)*E50</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K50" s="24">
-        <f>(1-$D50)*F50</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L50" s="24">
-        <f>G50</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M50" s="24">
-        <f>(1-$D50)*H50</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N50" s="24">
-        <f>(1-$D50)*I50</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O50" s="24">
@@ -6830,30 +6836,30 @@
         <v>500</v>
       </c>
       <c r="Z50" s="24">
-        <f>SUM(J50:Y50)</f>
+        <f t="shared" si="16"/>
         <v>62730</v>
       </c>
       <c r="AA50" s="24">
         <v>0</v>
       </c>
       <c r="AB50" s="20">
-        <f>Z50-AA50</f>
+        <f t="shared" si="17"/>
         <v>62730</v>
       </c>
       <c r="AC50" s="24" t="str">
-        <f>IF(AND($T50=6000, ($T50+$W50-$AB50)&gt;=6000),T50,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD50" s="24" t="str">
-        <f>IF(AND($T50=8000, ($T50+$W50-$AB50)&gt;=8000),T50,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE50" s="24" t="str">
-        <f>IF(($T50+$W50-$AB50)&gt;=$T50+8000,W50,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF50" s="25" t="str">
-        <f>IF(AB50&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6886,23 +6892,23 @@
         <v>5000</v>
       </c>
       <c r="J51" s="24">
-        <f>(1-$D51)*E51</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K51" s="24">
-        <f>(1-$D51)*F51</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L51" s="24">
-        <f>G51</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M51" s="24">
-        <f>(1-$D51)*H51</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N51" s="24">
-        <f>(1-$D51)*I51</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O51" s="24">
@@ -6939,30 +6945,30 @@
         <v>22105</v>
       </c>
       <c r="Z51" s="24">
-        <f>SUM(J51:Y51)</f>
+        <f t="shared" si="16"/>
         <v>94335</v>
       </c>
       <c r="AA51" s="24">
         <v>0</v>
       </c>
       <c r="AB51" s="20">
-        <f>Z51-AA51</f>
+        <f t="shared" si="17"/>
         <v>94335</v>
       </c>
       <c r="AC51" s="24" t="str">
-        <f>IF(AND($T51=6000, ($T51+$W51-$AB51)&gt;=6000),T51,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD51" s="24" t="str">
-        <f>IF(AND($T51=8000, ($T51+$W51-$AB51)&gt;=8000),T51,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE51" s="24" t="str">
-        <f>IF(($T51+$W51-$AB51)&gt;=$T51+8000,W51,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF51" s="25" t="str">
-        <f>IF(AB51&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6995,23 +7001,23 @@
         <v>5000</v>
       </c>
       <c r="J52" s="24">
-        <f>(1-$D52)*E52</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K52" s="24">
-        <f>(1-$D52)*F52</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L52" s="24">
-        <f>G52</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M52" s="24">
-        <f>(1-$D52)*H52</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N52" s="24">
-        <f>(1-$D52)*I52</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O52" s="24">
@@ -7048,30 +7054,30 @@
         <v>24395</v>
       </c>
       <c r="Z52" s="24">
-        <f>SUM(J52:Y52)</f>
+        <f t="shared" si="16"/>
         <v>101165</v>
       </c>
       <c r="AA52" s="24">
         <v>0</v>
       </c>
       <c r="AB52" s="20">
-        <f>Z52-AA52</f>
+        <f t="shared" si="17"/>
         <v>101165</v>
       </c>
       <c r="AC52" s="24" t="str">
-        <f>IF(AND($T52=6000, ($T52+$W52-$AB52)&gt;=6000),T52,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD52" s="24" t="str">
-        <f>IF(AND($T52=8000, ($T52+$W52-$AB52)&gt;=8000),T52,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE52" s="24" t="str">
-        <f>IF(($T52+$W52-$AB52)&gt;=$T52+8000,W52,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF52" s="25" t="str">
-        <f>IF(AB52&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7104,23 +7110,23 @@
         <v>0</v>
       </c>
       <c r="J53" s="24">
-        <f>(1-$D53)*E53</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K53" s="24">
-        <f>(1-$D53)*F53</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L53" s="24">
-        <f>G53</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M53" s="24">
-        <f>(1-$D53)*H53</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N53" s="24">
-        <f>(1-$D53)*I53</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O53" s="24">
@@ -7157,30 +7163,30 @@
         <v>0</v>
       </c>
       <c r="Z53" s="24">
-        <f>SUM(J53:Y53)</f>
+        <f t="shared" si="16"/>
         <v>51030</v>
       </c>
       <c r="AA53" s="24">
         <v>0</v>
       </c>
       <c r="AB53" s="20">
-        <f>Z53-AA53</f>
+        <f t="shared" si="17"/>
         <v>51030</v>
       </c>
       <c r="AC53" s="24" t="str">
-        <f>IF(AND($T53=6000, ($T53+$W53-$AB53)&gt;=6000),T53,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD53" s="24" t="str">
-        <f>IF(AND($T53=8000, ($T53+$W53-$AB53)&gt;=8000),T53,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE53" s="24" t="str">
-        <f>IF(($T53+$W53-$AB53)&gt;=$T53+8000,W53,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF53" s="25" t="str">
-        <f>IF(AB53&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7213,23 +7219,23 @@
         <v>0</v>
       </c>
       <c r="J54" s="24">
-        <f>(1-$D54)*E54</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K54" s="24">
-        <f>(1-$D54)*F54</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L54" s="24">
-        <f>G54</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M54" s="24">
-        <f>(1-$D54)*H54</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N54" s="24">
-        <f>(1-$D54)*I54</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O54" s="24">
@@ -7266,30 +7272,30 @@
         <v>2000</v>
       </c>
       <c r="Z54" s="24">
-        <f>SUM(J54:Y54)</f>
+        <f t="shared" si="16"/>
         <v>45140</v>
       </c>
       <c r="AA54" s="24">
         <v>39840</v>
       </c>
       <c r="AB54" s="20">
-        <f>Z54-AA54</f>
+        <f t="shared" si="17"/>
         <v>5300</v>
       </c>
       <c r="AC54" s="24" t="str">
-        <f>IF(AND($T54=6000, ($T54+$W54-$AB54)&gt;=6000),T54,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD54" s="24" t="str">
-        <f>IF(AND($T54=8000, ($T54+$W54-$AB54)&gt;=8000),T54,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE54" s="24" t="str">
-        <f>IF(($T54+$W54-$AB54)&gt;=$T54+8000,W54,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF54" s="25" t="str">
-        <f>IF(AB54&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7320,23 +7326,23 @@
         <v>6000</v>
       </c>
       <c r="J55" s="24">
-        <f>(1-$D55)*E55</f>
+        <f t="shared" si="11"/>
         <v>2250</v>
       </c>
       <c r="K55" s="24">
-        <f>(1-$D55)*F55</f>
+        <f t="shared" si="12"/>
         <v>24750</v>
       </c>
       <c r="L55" s="24">
-        <f>G55</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M55" s="24">
-        <f>(1-$D55)*H55</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N55" s="24">
-        <f>(1-$D55)*I55</f>
+        <f t="shared" si="15"/>
         <v>4500</v>
       </c>
       <c r="O55" s="24">
@@ -7373,30 +7379,30 @@
         <v>0</v>
       </c>
       <c r="Z55" s="24">
-        <f>SUM(J55:Y55)</f>
+        <f t="shared" si="16"/>
         <v>102730</v>
       </c>
       <c r="AA55" s="24">
         <v>100000</v>
       </c>
       <c r="AB55" s="20">
-        <f>Z55-AA55</f>
+        <f t="shared" si="17"/>
         <v>2730</v>
       </c>
       <c r="AC55" s="24" t="str">
-        <f>IF(AND($T55=6000, ($T55+$W55-$AB55)&gt;=6000),T55,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD55" s="24" t="str">
-        <f>IF(AND($T55=8000, ($T55+$W55-$AB55)&gt;=8000),T55,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE55" s="24" t="str">
-        <f>IF(($T55+$W55-$AB55)&gt;=$T55+8000,W55,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF55" s="25" t="str">
-        <f>IF(AB55&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7427,23 +7433,23 @@
         <v>8000</v>
       </c>
       <c r="J56" s="24">
-        <f>(1-$D56)*E56</f>
+        <f t="shared" si="11"/>
         <v>2250</v>
       </c>
       <c r="K56" s="24">
-        <f>(1-$D56)*F56</f>
+        <f t="shared" si="12"/>
         <v>30000</v>
       </c>
       <c r="L56" s="24">
-        <f>G56</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M56" s="24">
-        <f>(1-$D56)*H56</f>
+        <f t="shared" si="14"/>
         <v>1500</v>
       </c>
       <c r="N56" s="24">
-        <f>(1-$D56)*I56</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O56" s="24">
@@ -7480,30 +7486,30 @@
         <v>0</v>
       </c>
       <c r="Z56" s="24">
-        <f>SUM(J56:Y56)</f>
+        <f t="shared" si="16"/>
         <v>106960</v>
       </c>
       <c r="AA56" s="24">
         <v>100000</v>
       </c>
       <c r="AB56" s="20">
-        <f>Z56-AA56</f>
+        <f t="shared" si="17"/>
         <v>6960</v>
       </c>
       <c r="AC56" s="24" t="str">
-        <f>IF(AND($T56=6000, ($T56+$W56-$AB56)&gt;=6000),T56,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD56" s="24" t="str">
-        <f>IF(AND($T56=8000, ($T56+$W56-$AB56)&gt;=8000),T56,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE56" s="24" t="str">
-        <f>IF(($T56+$W56-$AB56)&gt;=$T56+8000,W56,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF56" s="25" t="str">
-        <f>IF(AB56&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7536,23 +7542,23 @@
         <v>0</v>
       </c>
       <c r="J57" s="24">
-        <f>(1-$D57)*E57</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K57" s="24">
-        <f>(1-$D57)*F57</f>
+        <f t="shared" si="12"/>
         <v>26000</v>
       </c>
       <c r="L57" s="24">
-        <f>G57</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M57" s="24">
-        <f>(1-$D57)*H57</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N57" s="24">
-        <f>(1-$D57)*I57</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O57" s="24">
@@ -7589,30 +7595,30 @@
         <v>0</v>
       </c>
       <c r="Z57" s="24">
-        <f>SUM(J57:Y57)</f>
+        <f t="shared" si="16"/>
         <v>56930</v>
       </c>
       <c r="AA57" s="24">
         <v>0</v>
       </c>
       <c r="AB57" s="20">
-        <f>Z57-AA57</f>
+        <f t="shared" si="17"/>
         <v>56930</v>
       </c>
       <c r="AC57" s="24" t="str">
-        <f>IF(AND($T57=6000, ($T57+$W57-$AB57)&gt;=6000),T57,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD57" s="24" t="str">
-        <f>IF(AND($T57=8000, ($T57+$W57-$AB57)&gt;=8000),T57,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE57" s="24" t="str">
-        <f>IF(($T57+$W57-$AB57)&gt;=$T57+8000,W57,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF57" s="25" t="str">
-        <f>IF(AB57&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7645,23 +7651,23 @@
         <v>5000</v>
       </c>
       <c r="J58" s="24">
-        <f>(1-$D58)*E58</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K58" s="24">
-        <f>(1-$D58)*F58</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L58" s="24">
-        <f>G58</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M58" s="24">
-        <f>(1-$D58)*H58</f>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N58" s="24">
-        <f>(1-$D58)*I58</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O58" s="24">
@@ -7698,30 +7704,30 @@
         <v>0</v>
       </c>
       <c r="Z58" s="24">
-        <f>SUM(J58:Y58)</f>
+        <f t="shared" si="16"/>
         <v>76800</v>
       </c>
       <c r="AA58" s="24">
         <v>0</v>
       </c>
       <c r="AB58" s="20">
-        <f>Z58-AA58</f>
+        <f t="shared" si="17"/>
         <v>76800</v>
       </c>
       <c r="AC58" s="24" t="str">
-        <f>IF(AND($T58=6000, ($T58+$W58-$AB58)&gt;=6000),T58,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD58" s="24" t="str">
-        <f>IF(AND($T58=8000, ($T58+$W58-$AB58)&gt;=8000),T58,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE58" s="24" t="str">
-        <f>IF(($T58+$W58-$AB58)&gt;=$T58+8000,W58,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF58" s="25" t="str">
-        <f>IF(AB58&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7754,23 +7760,23 @@
         <v>0</v>
       </c>
       <c r="J59" s="24">
-        <f>(1-$D59)*E59</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K59" s="24">
-        <f>(1-$D59)*F59</f>
+        <f t="shared" si="12"/>
         <v>19500</v>
       </c>
       <c r="L59" s="24">
-        <f>G59</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M59" s="24">
-        <f>(1-$D59)*H59</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N59" s="24">
-        <f>(1-$D59)*I59</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O59" s="24">
@@ -7807,30 +7813,30 @@
         <v>0</v>
       </c>
       <c r="Z59" s="24">
-        <f>SUM(J59:Y59)</f>
+        <f t="shared" si="16"/>
         <v>44430</v>
       </c>
       <c r="AA59" s="24">
         <v>0</v>
       </c>
       <c r="AB59" s="20">
-        <f>Z59-AA59</f>
+        <f t="shared" si="17"/>
         <v>44430</v>
       </c>
       <c r="AC59" s="24" t="str">
-        <f>IF(AND($T59=6000, ($T59+$W59-$AB59)&gt;=6000),T59,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD59" s="24" t="str">
-        <f>IF(AND($T59=8000, ($T59+$W59-$AB59)&gt;=8000),T59,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE59" s="24" t="str">
-        <f>IF(($T59+$W59-$AB59)&gt;=$T59+8000,W59,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF59" s="25" t="str">
-        <f>IF(AB59&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -7863,23 +7869,23 @@
         <v>0</v>
       </c>
       <c r="J60" s="24">
-        <f>(1-$D60)*E60</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K60" s="24">
-        <f>(1-$D60)*F60</f>
+        <f t="shared" si="12"/>
         <v>24700</v>
       </c>
       <c r="L60" s="24">
-        <f>G60</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M60" s="24">
-        <f>(1-$D60)*H60</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N60" s="24">
-        <f>(1-$D60)*I60</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="O60" s="24">
@@ -7916,30 +7922,30 @@
         <v>1000</v>
       </c>
       <c r="Z60" s="24">
-        <f>SUM(J60:Y60)</f>
+        <f t="shared" si="16"/>
         <v>50630</v>
       </c>
       <c r="AA60" s="24">
         <v>51930</v>
       </c>
       <c r="AB60" s="20">
-        <f>Z60-AA60</f>
+        <f t="shared" si="17"/>
         <v>-1300</v>
       </c>
       <c r="AC60" s="24" t="str">
-        <f>IF(AND($T60=6000, ($T60+$W60-$AB60)&gt;=6000),T60,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD60" s="24" t="str">
-        <f>IF(AND($T60=8000, ($T60+$W60-$AB60)&gt;=8000),T60,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE60" s="24" t="str">
-        <f>IF(($T60+$W60-$AB60)&gt;=$T60+8000,W60,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF60" s="25" t="str">
-        <f>IF(AB60&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -7972,23 +7978,23 @@
         <v>5000</v>
       </c>
       <c r="J61" s="24">
-        <f>(1-$D61)*E61</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K61" s="24">
-        <f>(1-$D61)*F61</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L61" s="24">
-        <f>G61</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M61" s="24">
-        <f>(1-$D61)*H61</f>
+        <f t="shared" si="14"/>
         <v>2500</v>
       </c>
       <c r="N61" s="24">
-        <f>(1-$D61)*I61</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O61" s="24">
@@ -8025,30 +8031,30 @@
         <v>550</v>
       </c>
       <c r="Z61" s="24">
-        <f>SUM(J61:Y61)</f>
+        <f t="shared" si="16"/>
         <v>77350</v>
       </c>
       <c r="AA61" s="24">
         <v>0</v>
       </c>
       <c r="AB61" s="20">
-        <f>Z61-AA61</f>
+        <f t="shared" si="17"/>
         <v>77350</v>
       </c>
       <c r="AC61" s="24" t="str">
-        <f>IF(AND($T61=6000, ($T61+$W61-$AB61)&gt;=6000),T61,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD61" s="24" t="str">
-        <f>IF(AND($T61=8000, ($T61+$W61-$AB61)&gt;=8000),T61,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE61" s="24" t="str">
-        <f>IF(($T61+$W61-$AB61)&gt;=$T61+8000,W61,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF61" s="25" t="str">
-        <f>IF(AB61&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -8081,23 +8087,23 @@
         <v>5000</v>
       </c>
       <c r="J62" s="24">
-        <f>(1-$D62)*E62</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K62" s="24">
-        <f>(1-$D62)*F62</f>
+        <f t="shared" si="12"/>
         <v>28000</v>
       </c>
       <c r="L62" s="24">
-        <f>G62</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M62" s="24">
-        <f>(1-$D62)*H62</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N62" s="24">
-        <f>(1-$D62)*I62</f>
+        <f t="shared" si="15"/>
         <v>5000</v>
       </c>
       <c r="O62" s="24">
@@ -8134,30 +8140,30 @@
         <v>0</v>
       </c>
       <c r="Z62" s="24">
-        <f>SUM(J62:Y62)</f>
+        <f t="shared" si="16"/>
         <v>77540</v>
       </c>
       <c r="AA62" s="24">
         <v>0</v>
       </c>
       <c r="AB62" s="20">
-        <f>Z62-AA62</f>
+        <f t="shared" si="17"/>
         <v>77540</v>
       </c>
       <c r="AC62" s="24" t="str">
-        <f>IF(AND($T62=6000, ($T62+$W62-$AB62)&gt;=6000),T62,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD62" s="24" t="str">
-        <f>IF(AND($T62=8000, ($T62+$W62-$AB62)&gt;=8000),T62,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE62" s="24" t="str">
-        <f>IF(($T62+$W62-$AB62)&gt;=$T62+8000,W62,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF62" s="25" t="str">
-        <f>IF(AB62&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -8190,23 +8196,23 @@
         <v>6000</v>
       </c>
       <c r="J63" s="24">
-        <f>(1-$D63)*E63</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K63" s="24">
-        <f>(1-$D63)*F63</f>
+        <f t="shared" si="12"/>
         <v>16500</v>
       </c>
       <c r="L63" s="24">
-        <f>G63</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M63" s="24">
-        <f>(1-$D63)*H63</f>
+        <f t="shared" si="14"/>
         <v>1000</v>
       </c>
       <c r="N63" s="24">
-        <f>(1-$D63)*I63</f>
+        <f t="shared" si="15"/>
         <v>3000</v>
       </c>
       <c r="O63" s="24">
@@ -8243,30 +8249,30 @@
         <v>0</v>
       </c>
       <c r="Z63" s="24">
-        <f>SUM(J63:Y63)</f>
+        <f t="shared" si="16"/>
         <v>62230</v>
       </c>
       <c r="AA63" s="24">
         <v>0</v>
       </c>
       <c r="AB63" s="20">
-        <f>Z63-AA63</f>
+        <f t="shared" si="17"/>
         <v>62230</v>
       </c>
       <c r="AC63" s="24" t="str">
-        <f>IF(AND($T63=6000, ($T63+$W63-$AB63)&gt;=6000),T63,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD63" s="24" t="str">
-        <f>IF(AND($T63=8000, ($T63+$W63-$AB63)&gt;=8000),T63,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE63" s="24" t="str">
-        <f>IF(($T63+$W63-$AB63)&gt;=$T63+8000,W63,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF63" s="25" t="str">
-        <f>IF(AB63&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -8299,23 +8305,23 @@
         <v>5000</v>
       </c>
       <c r="J64" s="24">
-        <f>(1-$D64)*E64</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K64" s="24">
-        <f>(1-$D64)*F64</f>
+        <f t="shared" si="12"/>
         <v>21000</v>
       </c>
       <c r="L64" s="24">
-        <f>G64</f>
+        <f t="shared" si="13"/>
         <v>4000</v>
       </c>
       <c r="M64" s="24">
-        <f>(1-$D64)*H64</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N64" s="24">
-        <f>(1-$D64)*I64</f>
+        <f t="shared" si="15"/>
         <v>3750</v>
       </c>
       <c r="O64" s="24">
@@ -8352,30 +8358,30 @@
         <v>0</v>
       </c>
       <c r="Z64" s="24">
-        <f>SUM(J64:Y64)</f>
+        <f t="shared" si="16"/>
         <v>69310</v>
       </c>
       <c r="AA64" s="24">
         <v>0</v>
       </c>
       <c r="AB64" s="20">
-        <f>Z64-AA64</f>
+        <f t="shared" si="17"/>
         <v>69310</v>
       </c>
       <c r="AC64" s="24" t="str">
-        <f>IF(AND($T64=6000, ($T64+$W64-$AB64)&gt;=6000),T64,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD64" s="24" t="str">
-        <f>IF(AND($T64=8000, ($T64+$W64-$AB64)&gt;=8000),T64,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE64" s="24" t="str">
-        <f>IF(($T64+$W64-$AB64)&gt;=$T64+8000,W64,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF64" s="25" t="str">
-        <f>IF(AB64&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -8408,23 +8414,23 @@
         <v>6000</v>
       </c>
       <c r="J65" s="24">
-        <f>(1-$D65)*E65</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K65" s="24">
-        <f>(1-$D65)*F65</f>
+        <f t="shared" si="12"/>
         <v>33000</v>
       </c>
       <c r="L65" s="24">
-        <f>G65</f>
+        <f t="shared" si="13"/>
         <v>5000</v>
       </c>
       <c r="M65" s="24">
-        <f>(1-$D65)*H65</f>
+        <f t="shared" si="14"/>
         <v>2000</v>
       </c>
       <c r="N65" s="24">
-        <f>(1-$D65)*I65</f>
+        <f t="shared" si="15"/>
         <v>6000</v>
       </c>
       <c r="O65" s="24">
@@ -8461,30 +8467,30 @@
         <v>0</v>
       </c>
       <c r="Z65" s="24">
-        <f>SUM(J65:Y65)</f>
+        <f t="shared" si="16"/>
         <v>79830</v>
       </c>
       <c r="AA65" s="24">
         <v>0</v>
       </c>
       <c r="AB65" s="20">
-        <f>Z65-AA65</f>
+        <f t="shared" si="17"/>
         <v>79830</v>
       </c>
       <c r="AC65" s="24" t="str">
-        <f>IF(AND($T65=6000, ($T65+$W65-$AB65)&gt;=6000),T65,"")</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="AD65" s="24" t="str">
-        <f>IF(AND($T65=8000, ($T65+$W65-$AB65)&gt;=8000),T65,"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AE65" s="24" t="str">
-        <f>IF(($T65+$W65-$AB65)&gt;=$T65+8000,W65,"")</f>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="AF65" s="25" t="str">
-        <f>IF(AB65&lt;=0,"BONUS","")</f>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -8517,23 +8523,23 @@
         <v>0</v>
       </c>
       <c r="J66" s="24">
-        <f>(1-$D66)*E66</f>
+        <f t="shared" ref="J66:J97" si="22">(1-$D66)*E66</f>
         <v>0</v>
       </c>
       <c r="K66" s="24">
-        <f>(1-$D66)*F66</f>
+        <f t="shared" ref="K66:K97" si="23">(1-$D66)*F66</f>
         <v>13000</v>
       </c>
       <c r="L66" s="24">
-        <f>G66</f>
+        <f t="shared" ref="L66:L97" si="24">G66</f>
         <v>4000</v>
       </c>
       <c r="M66" s="24">
-        <f>(1-$D66)*H66</f>
+        <f t="shared" ref="M66:M97" si="25">(1-$D66)*H66</f>
         <v>500</v>
       </c>
       <c r="N66" s="24">
-        <f>(1-$D66)*I66</f>
+        <f t="shared" ref="N66:N97" si="26">(1-$D66)*I66</f>
         <v>0</v>
       </c>
       <c r="O66" s="24">
@@ -8570,30 +8576,30 @@
         <v>0</v>
       </c>
       <c r="Z66" s="24">
-        <f>SUM(J66:Y66)</f>
+        <f t="shared" ref="Z66:Z97" si="27">SUM(J66:Y66)</f>
         <v>29640</v>
       </c>
       <c r="AA66" s="24">
         <v>20000</v>
       </c>
       <c r="AB66" s="20">
-        <f>Z66-AA66</f>
+        <f t="shared" ref="AB66:AB97" si="28">Z66-AA66</f>
         <v>9640</v>
       </c>
       <c r="AC66" s="24" t="str">
-        <f>IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
+        <f t="shared" ref="AC66:AC97" si="29">IF(AND($T66=6000, ($T66+$W66-$AB66)&gt;=6000),T66,"")</f>
         <v/>
       </c>
       <c r="AD66" s="24" t="str">
-        <f>IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
+        <f t="shared" ref="AD66:AD97" si="30">IF(AND($T66=8000, ($T66+$W66-$AB66)&gt;=8000),T66,"")</f>
         <v/>
       </c>
       <c r="AE66" s="24" t="str">
-        <f>IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
+        <f t="shared" ref="AE66:AE97" si="31">IF(($T66+$W66-$AB66)&gt;=$T66+8000,W66,"")</f>
         <v/>
       </c>
       <c r="AF66" s="25" t="str">
-        <f>IF(AB66&lt;=0,"BONUS","")</f>
+        <f t="shared" ref="AF66:AF97" si="32">IF(AB66&lt;=0,"BONUS","")</f>
         <v/>
       </c>
     </row>
@@ -8626,23 +8632,23 @@
         <v>0</v>
       </c>
       <c r="J67" s="24">
-        <f>(1-$D67)*E67</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K67" s="24">
-        <f>(1-$D67)*F67</f>
+        <f t="shared" si="23"/>
         <v>13000</v>
       </c>
       <c r="L67" s="24">
-        <f>G67</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M67" s="24">
-        <f>(1-$D67)*H67</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N67" s="24">
-        <f>(1-$D67)*I67</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O67" s="24">
@@ -8679,30 +8685,30 @@
         <v>8000</v>
       </c>
       <c r="Z67" s="24">
-        <f>SUM(J67:Y67)</f>
+        <f t="shared" si="27"/>
         <v>45930</v>
       </c>
       <c r="AA67" s="24">
         <v>0</v>
       </c>
       <c r="AB67" s="20">
-        <f>Z67-AA67</f>
+        <f t="shared" si="28"/>
         <v>45930</v>
       </c>
       <c r="AC67" s="24" t="str">
-        <f>IF(AND($T67=6000, ($T67+$W67-$AB67)&gt;=6000),T67,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD67" s="24" t="str">
-        <f>IF(AND($T67=8000, ($T67+$W67-$AB67)&gt;=8000),T67,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE67" s="24" t="str">
-        <f>IF(($T67+$W67-$AB67)&gt;=$T67+8000,W67,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF67" s="25" t="str">
-        <f>IF(AB67&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -8735,23 +8741,23 @@
         <v>0</v>
       </c>
       <c r="J68" s="24">
-        <f>(1-$D68)*E68</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K68" s="24">
-        <f>(1-$D68)*F68</f>
+        <f t="shared" si="23"/>
         <v>13000</v>
       </c>
       <c r="L68" s="24">
-        <f>G68</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M68" s="24">
-        <f>(1-$D68)*H68</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N68" s="24">
-        <f>(1-$D68)*I68</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O68" s="24">
@@ -8788,30 +8794,30 @@
         <v>8000</v>
       </c>
       <c r="Z68" s="24">
-        <f>SUM(J68:Y68)</f>
+        <f t="shared" si="27"/>
         <v>45930</v>
       </c>
       <c r="AA68" s="24">
         <v>0</v>
       </c>
       <c r="AB68" s="20">
-        <f>Z68-AA68</f>
+        <f t="shared" si="28"/>
         <v>45930</v>
       </c>
       <c r="AC68" s="24" t="str">
-        <f>IF(AND($T68=6000, ($T68+$W68-$AB68)&gt;=6000),T68,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD68" s="24" t="str">
-        <f>IF(AND($T68=8000, ($T68+$W68-$AB68)&gt;=8000),T68,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE68" s="24" t="str">
-        <f>IF(($T68+$W68-$AB68)&gt;=$T68+8000,W68,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF68" s="25" t="str">
-        <f>IF(AB68&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -8844,23 +8850,23 @@
         <v>5000</v>
       </c>
       <c r="J69" s="24">
-        <f>(1-$D69)*E69</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K69" s="24">
-        <f>(1-$D69)*F69</f>
+        <f t="shared" si="23"/>
         <v>14000</v>
       </c>
       <c r="L69" s="24">
-        <f>G69</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M69" s="24">
-        <f>(1-$D69)*H69</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N69" s="24">
-        <f>(1-$D69)*I69</f>
+        <f t="shared" si="26"/>
         <v>2500</v>
       </c>
       <c r="O69" s="24">
@@ -8897,30 +8903,30 @@
         <v>8080</v>
       </c>
       <c r="Z69" s="24">
-        <f>SUM(J69:Y69)</f>
+        <f t="shared" si="27"/>
         <v>69140</v>
       </c>
       <c r="AA69" s="24">
         <v>0</v>
       </c>
       <c r="AB69" s="20">
-        <f>Z69-AA69</f>
+        <f t="shared" si="28"/>
         <v>69140</v>
       </c>
       <c r="AC69" s="24" t="str">
-        <f>IF(AND($T69=6000, ($T69+$W69-$AB69)&gt;=6000),T69,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD69" s="24" t="str">
-        <f>IF(AND($T69=8000, ($T69+$W69-$AB69)&gt;=8000),T69,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE69" s="24" t="str">
-        <f>IF(($T69+$W69-$AB69)&gt;=$T69+8000,W69,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF69" s="25" t="str">
-        <f>IF(AB69&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -8953,23 +8959,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="24">
-        <f>(1-$D70)*E70</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K70" s="24">
-        <f>(1-$D70)*F70</f>
+        <f t="shared" si="23"/>
         <v>26000</v>
       </c>
       <c r="L70" s="24">
-        <f>G70</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M70" s="24">
-        <f>(1-$D70)*H70</f>
+        <f t="shared" si="25"/>
         <v>1000</v>
       </c>
       <c r="N70" s="24">
-        <f>(1-$D70)*I70</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O70" s="24">
@@ -9006,30 +9012,30 @@
         <v>0</v>
       </c>
       <c r="Z70" s="24">
-        <f>SUM(J70:Y70)</f>
+        <f t="shared" si="27"/>
         <v>43140</v>
       </c>
       <c r="AA70" s="24">
         <v>0</v>
       </c>
       <c r="AB70" s="20">
-        <f>Z70-AA70</f>
+        <f t="shared" si="28"/>
         <v>43140</v>
       </c>
       <c r="AC70" s="24" t="str">
-        <f>IF(AND($T70=6000, ($T70+$W70-$AB70)&gt;=6000),T70,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD70" s="24" t="str">
-        <f>IF(AND($T70=8000, ($T70+$W70-$AB70)&gt;=8000),T70,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE70" s="24" t="str">
-        <f>IF(($T70+$W70-$AB70)&gt;=$T70+8000,W70,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF70" s="25" t="str">
-        <f>IF(AB70&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9062,23 +9068,23 @@
         <v>0</v>
       </c>
       <c r="J71" s="24">
-        <f>(1-$D71)*E71</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K71" s="24">
-        <f>(1-$D71)*F71</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L71" s="24">
-        <f>G71</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M71" s="24">
-        <f>(1-$D71)*H71</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N71" s="24">
-        <f>(1-$D71)*I71</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O71" s="24">
@@ -9115,30 +9121,30 @@
         <v>0</v>
       </c>
       <c r="Z71" s="24">
-        <f>SUM(J71:Y71)</f>
+        <f t="shared" si="27"/>
         <v>65160</v>
       </c>
       <c r="AA71" s="24">
         <v>0</v>
       </c>
       <c r="AB71" s="20">
-        <f>Z71-AA71</f>
+        <f t="shared" si="28"/>
         <v>65160</v>
       </c>
       <c r="AC71" s="24" t="str">
-        <f>IF(AND($T71=6000, ($T71+$W71-$AB71)&gt;=6000),T71,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD71" s="24" t="str">
-        <f>IF(AND($T71=8000, ($T71+$W71-$AB71)&gt;=8000),T71,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE71" s="24" t="str">
-        <f>IF(($T71+$W71-$AB71)&gt;=$T71+8000,W71,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF71" s="25" t="str">
-        <f>IF(AB71&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9171,23 +9177,23 @@
         <v>0</v>
       </c>
       <c r="J72" s="24">
-        <f>(1-$D72)*E72</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K72" s="24">
-        <f>(1-$D72)*F72</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L72" s="24">
-        <f>G72</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M72" s="24">
-        <f>(1-$D72)*H72</f>
+        <f t="shared" si="25"/>
         <v>750</v>
       </c>
       <c r="N72" s="24">
-        <f>(1-$D72)*I72</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O72" s="24">
@@ -9224,30 +9230,30 @@
         <v>-500</v>
       </c>
       <c r="Z72" s="24">
-        <f>SUM(J72:Y72)</f>
+        <f t="shared" si="27"/>
         <v>35890</v>
       </c>
       <c r="AA72" s="24">
         <v>0</v>
       </c>
       <c r="AB72" s="20">
-        <f>Z72-AA72</f>
+        <f t="shared" si="28"/>
         <v>35890</v>
       </c>
       <c r="AC72" s="24" t="str">
-        <f>IF(AND($T72=6000, ($T72+$W72-$AB72)&gt;=6000),T72,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD72" s="24" t="str">
-        <f>IF(AND($T72=8000, ($T72+$W72-$AB72)&gt;=8000),T72,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE72" s="24" t="str">
-        <f>IF(($T72+$W72-$AB72)&gt;=$T72+8000,W72,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF72" s="25" t="str">
-        <f>IF(AB72&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9280,23 +9286,23 @@
         <v>0</v>
       </c>
       <c r="J73" s="24">
-        <f>(1-$D73)*E73</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K73" s="24">
-        <f>(1-$D73)*F73</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L73" s="24">
-        <f>G73</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M73" s="24">
-        <f>(1-$D73)*H73</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N73" s="24">
-        <f>(1-$D73)*I73</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O73" s="24">
@@ -9333,30 +9339,30 @@
         <v>0</v>
       </c>
       <c r="Z73" s="24">
-        <f>SUM(J73:Y73)</f>
+        <f t="shared" si="27"/>
         <v>50430</v>
       </c>
       <c r="AA73" s="24">
         <v>0</v>
       </c>
       <c r="AB73" s="20">
-        <f>Z73-AA73</f>
+        <f t="shared" si="28"/>
         <v>50430</v>
       </c>
       <c r="AC73" s="24" t="str">
-        <f>IF(AND($T73=6000, ($T73+$W73-$AB73)&gt;=6000),T73,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD73" s="24" t="str">
-        <f>IF(AND($T73=8000, ($T73+$W73-$AB73)&gt;=8000),T73,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE73" s="24" t="str">
-        <f>IF(($T73+$W73-$AB73)&gt;=$T73+8000,W73,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF73" s="25" t="str">
-        <f>IF(AB73&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9389,23 +9395,23 @@
         <v>0</v>
       </c>
       <c r="J74" s="24">
-        <f>(1-$D74)*E74</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K74" s="24">
-        <f>(1-$D74)*F74</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L74" s="24">
-        <f>G74</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M74" s="24">
-        <f>(1-$D74)*H74</f>
+        <f t="shared" si="25"/>
         <v>750</v>
       </c>
       <c r="N74" s="24">
-        <f>(1-$D74)*I74</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O74" s="24">
@@ -9442,30 +9448,30 @@
         <v>0</v>
       </c>
       <c r="Z74" s="24">
-        <f>SUM(J74:Y74)</f>
+        <f t="shared" si="27"/>
         <v>36390</v>
       </c>
       <c r="AA74" s="24">
         <v>0</v>
       </c>
       <c r="AB74" s="20">
-        <f>Z74-AA74</f>
+        <f t="shared" si="28"/>
         <v>36390</v>
       </c>
       <c r="AC74" s="24" t="str">
-        <f>IF(AND($T74=6000, ($T74+$W74-$AB74)&gt;=6000),T74,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD74" s="24" t="str">
-        <f>IF(AND($T74=8000, ($T74+$W74-$AB74)&gt;=8000),T74,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE74" s="24" t="str">
-        <f>IF(($T74+$W74-$AB74)&gt;=$T74+8000,W74,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF74" s="25" t="str">
-        <f>IF(AB74&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9498,23 +9504,23 @@
         <v>0</v>
       </c>
       <c r="J75" s="24">
-        <f>(1-$D75)*E75</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K75" s="24">
-        <f>(1-$D75)*F75</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L75" s="24">
-        <f>G75</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M75" s="24">
-        <f>(1-$D75)*H75</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N75" s="24">
-        <f>(1-$D75)*I75</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O75" s="24">
@@ -9551,30 +9557,30 @@
         <v>0</v>
       </c>
       <c r="Z75" s="24">
-        <f>SUM(J75:Y75)</f>
+        <f t="shared" si="27"/>
         <v>50430</v>
       </c>
       <c r="AA75" s="24">
         <v>0</v>
       </c>
       <c r="AB75" s="20">
-        <f>Z75-AA75</f>
+        <f t="shared" si="28"/>
         <v>50430</v>
       </c>
       <c r="AC75" s="24" t="str">
-        <f>IF(AND($T75=6000, ($T75+$W75-$AB75)&gt;=6000),T75,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD75" s="24" t="str">
-        <f>IF(AND($T75=8000, ($T75+$W75-$AB75)&gt;=8000),T75,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE75" s="24" t="str">
-        <f>IF(($T75+$W75-$AB75)&gt;=$T75+8000,W75,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF75" s="25" t="str">
-        <f>IF(AB75&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9607,23 +9613,23 @@
         <v>5000</v>
       </c>
       <c r="J76" s="24">
-        <f>(1-$D76)*E76</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K76" s="24">
-        <f>(1-$D76)*F76</f>
+        <f t="shared" si="23"/>
         <v>21000</v>
       </c>
       <c r="L76" s="24">
-        <f>G76</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M76" s="24">
-        <f>(1-$D76)*H76</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N76" s="24">
-        <f>(1-$D76)*I76</f>
+        <f t="shared" si="26"/>
         <v>3750</v>
       </c>
       <c r="O76" s="24">
@@ -9660,30 +9666,30 @@
         <v>-695</v>
       </c>
       <c r="Z76" s="24">
-        <f>SUM(J76:Y76)</f>
+        <f t="shared" si="27"/>
         <v>74595</v>
       </c>
       <c r="AA76" s="24">
         <v>0</v>
       </c>
       <c r="AB76" s="20">
-        <f>Z76-AA76</f>
+        <f t="shared" si="28"/>
         <v>74595</v>
       </c>
       <c r="AC76" s="24" t="str">
-        <f>IF(AND($T76=6000, ($T76+$W76-$AB76)&gt;=6000),T76,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD76" s="24" t="str">
-        <f>IF(AND($T76=8000, ($T76+$W76-$AB76)&gt;=8000),T76,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE76" s="24" t="str">
-        <f>IF(($T76+$W76-$AB76)&gt;=$T76+8000,W76,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF76" s="25" t="str">
-        <f>IF(AB76&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9716,23 +9722,23 @@
         <v>0</v>
       </c>
       <c r="J77" s="24">
-        <f>(1-$D77)*E77</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K77" s="24">
-        <f>(1-$D77)*F77</f>
+        <f t="shared" si="23"/>
         <v>26000</v>
       </c>
       <c r="L77" s="24">
-        <f>G77</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M77" s="24">
-        <f>(1-$D77)*H77</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N77" s="24">
-        <f>(1-$D77)*I77</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O77" s="24">
@@ -9769,30 +9775,30 @@
         <v>14000</v>
       </c>
       <c r="Z77" s="24">
-        <f>SUM(J77:Y77)</f>
+        <f t="shared" si="27"/>
         <v>64930</v>
       </c>
       <c r="AA77" s="24">
         <v>0</v>
       </c>
       <c r="AB77" s="20">
-        <f>Z77-AA77</f>
+        <f t="shared" si="28"/>
         <v>64930</v>
       </c>
       <c r="AC77" s="24" t="str">
-        <f>IF(AND($T77=6000, ($T77+$W77-$AB77)&gt;=6000),T77,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD77" s="24" t="str">
-        <f>IF(AND($T77=8000, ($T77+$W77-$AB77)&gt;=8000),T77,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE77" s="24" t="str">
-        <f>IF(($T77+$W77-$AB77)&gt;=$T77+8000,W77,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF77" s="25" t="str">
-        <f>IF(AB77&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9825,23 +9831,23 @@
         <v>6000</v>
       </c>
       <c r="J78" s="24">
-        <f>(1-$D78)*E78</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K78" s="24">
-        <f>(1-$D78)*F78</f>
+        <f t="shared" si="23"/>
         <v>23100</v>
       </c>
       <c r="L78" s="24">
-        <f>G78</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="M78" s="24">
-        <f>(1-$D78)*H78</f>
+        <f t="shared" si="25"/>
         <v>1400</v>
       </c>
       <c r="N78" s="24">
-        <f>(1-$D78)*I78</f>
+        <f t="shared" si="26"/>
         <v>4200</v>
       </c>
       <c r="O78" s="24">
@@ -9878,30 +9884,30 @@
         <v>0</v>
       </c>
       <c r="Z78" s="24">
-        <f>SUM(J78:Y78)</f>
+        <f t="shared" si="27"/>
         <v>67530</v>
       </c>
       <c r="AA78" s="24">
         <v>0</v>
       </c>
       <c r="AB78" s="20">
-        <f>Z78-AA78</f>
+        <f t="shared" si="28"/>
         <v>67530</v>
       </c>
       <c r="AC78" s="24" t="str">
-        <f>IF(AND($T78=6000, ($T78+$W78-$AB78)&gt;=6000),T78,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD78" s="24" t="str">
-        <f>IF(AND($T78=8000, ($T78+$W78-$AB78)&gt;=8000),T78,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE78" s="24" t="str">
-        <f>IF(($T78+$W78-$AB78)&gt;=$T78+8000,W78,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF78" s="25" t="str">
-        <f>IF(AB78&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -9934,23 +9940,23 @@
         <v>5000</v>
       </c>
       <c r="J79" s="24">
-        <f>(1-$D79)*E79</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K79" s="24">
-        <f>(1-$D79)*F79</f>
+        <f t="shared" si="23"/>
         <v>21000</v>
       </c>
       <c r="L79" s="24">
-        <f>G79</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M79" s="24">
-        <f>(1-$D79)*H79</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N79" s="24">
-        <f>(1-$D79)*I79</f>
+        <f t="shared" si="26"/>
         <v>3750</v>
       </c>
       <c r="O79" s="24">
@@ -9987,30 +9993,30 @@
         <v>450</v>
       </c>
       <c r="Z79" s="24">
-        <f>SUM(J79:Y79)</f>
+        <f t="shared" si="27"/>
         <v>69740</v>
       </c>
       <c r="AA79" s="24">
         <v>0</v>
       </c>
       <c r="AB79" s="20">
-        <f>Z79-AA79</f>
+        <f t="shared" si="28"/>
         <v>69740</v>
       </c>
       <c r="AC79" s="24" t="str">
-        <f>IF(AND($T79=6000, ($T79+$W79-$AB79)&gt;=6000),T79,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD79" s="24" t="str">
-        <f>IF(AND($T79=8000, ($T79+$W79-$AB79)&gt;=8000),T79,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE79" s="24" t="str">
-        <f>IF(($T79+$W79-$AB79)&gt;=$T79+8000,W79,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF79" s="25" t="str">
-        <f>IF(AB79&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10043,23 +10049,23 @@
         <v>8000</v>
       </c>
       <c r="J80" s="24">
-        <f>(1-$D80)*E80</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K80" s="24">
-        <f>(1-$D80)*F80</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L80" s="24">
-        <f>G80</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="M80" s="24">
-        <f>(1-$D80)*H80</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N80" s="24">
-        <f>(1-$D80)*I80</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O80" s="24">
@@ -10096,30 +10102,30 @@
         <v>0</v>
       </c>
       <c r="Z80" s="24">
-        <f>SUM(J80:Y80)</f>
+        <f t="shared" si="27"/>
         <v>31210</v>
       </c>
       <c r="AA80" s="24">
         <v>0</v>
       </c>
       <c r="AB80" s="20">
-        <f>Z80-AA80</f>
+        <f t="shared" si="28"/>
         <v>31210</v>
       </c>
       <c r="AC80" s="24" t="str">
-        <f>IF(AND($T80=6000, ($T80+$W80-$AB80)&gt;=6000),T80,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD80" s="24" t="str">
-        <f>IF(AND($T80=8000, ($T80+$W80-$AB80)&gt;=8000),T80,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE80" s="24" t="str">
-        <f>IF(($T80+$W80-$AB80)&gt;=$T80+8000,W80,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF80" s="25" t="str">
-        <f>IF(AB80&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10152,23 +10158,23 @@
         <v>0</v>
       </c>
       <c r="J81" s="24">
-        <f>(1-$D81)*E81</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K81" s="24">
-        <f>(1-$D81)*F81</f>
+        <f t="shared" si="23"/>
         <v>26000</v>
       </c>
       <c r="L81" s="24">
-        <f>G81</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M81" s="24">
-        <f>(1-$D81)*H81</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N81" s="24">
-        <f>(1-$D81)*I81</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O81" s="24">
@@ -10205,30 +10211,30 @@
         <v>7000</v>
       </c>
       <c r="Z81" s="24">
-        <f>SUM(J81:Y81)</f>
+        <f t="shared" si="27"/>
         <v>65930</v>
       </c>
       <c r="AA81" s="24">
         <v>0</v>
       </c>
       <c r="AB81" s="20">
-        <f>Z81-AA81</f>
+        <f t="shared" si="28"/>
         <v>65930</v>
       </c>
       <c r="AC81" s="24" t="str">
-        <f>IF(AND($T81=6000, ($T81+$W81-$AB81)&gt;=6000),T81,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD81" s="24" t="str">
-        <f>IF(AND($T81=8000, ($T81+$W81-$AB81)&gt;=8000),T81,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE81" s="24" t="str">
-        <f>IF(($T81+$W81-$AB81)&gt;=$T81+8000,W81,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF81" s="25" t="str">
-        <f>IF(AB81&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10261,23 +10267,23 @@
         <v>0</v>
       </c>
       <c r="J82" s="24">
-        <f>(1-$D82)*E82</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K82" s="24">
-        <f>(1-$D82)*F82</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L82" s="24">
-        <f>G82</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M82" s="24">
-        <f>(1-$D82)*H82</f>
+        <f t="shared" si="25"/>
         <v>750</v>
       </c>
       <c r="N82" s="24">
-        <f>(1-$D82)*I82</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O82" s="24">
@@ -10314,30 +10320,30 @@
         <v>19200</v>
       </c>
       <c r="Z82" s="24">
-        <f>SUM(J82:Y82)</f>
+        <f t="shared" si="27"/>
         <v>55590</v>
       </c>
       <c r="AA82" s="24">
         <v>0</v>
       </c>
       <c r="AB82" s="20">
-        <f>Z82-AA82</f>
+        <f t="shared" si="28"/>
         <v>55590</v>
       </c>
       <c r="AC82" s="24" t="str">
-        <f>IF(AND($T82=6000, ($T82+$W82-$AB82)&gt;=6000),T82,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD82" s="24" t="str">
-        <f>IF(AND($T82=8000, ($T82+$W82-$AB82)&gt;=8000),T82,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE82" s="24" t="str">
-        <f>IF(($T82+$W82-$AB82)&gt;=$T82+8000,W82,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF82" s="25" t="str">
-        <f>IF(AB82&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10370,23 +10376,23 @@
         <v>0</v>
       </c>
       <c r="J83" s="24">
-        <f>(1-$D83)*E83</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K83" s="24">
-        <f>(1-$D83)*F83</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L83" s="24">
-        <f>G83</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M83" s="24">
-        <f>(1-$D83)*H83</f>
+        <f t="shared" si="25"/>
         <v>750</v>
       </c>
       <c r="N83" s="24">
-        <f>(1-$D83)*I83</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O83" s="24">
@@ -10423,30 +10429,30 @@
         <v>19200</v>
       </c>
       <c r="Z83" s="24">
-        <f>SUM(J83:Y83)</f>
+        <f t="shared" si="27"/>
         <v>55590</v>
       </c>
       <c r="AA83" s="24">
         <v>0</v>
       </c>
       <c r="AB83" s="20">
-        <f>Z83-AA83</f>
+        <f t="shared" si="28"/>
         <v>55590</v>
       </c>
       <c r="AC83" s="24" t="str">
-        <f>IF(AND($T83=6000, ($T83+$W83-$AB83)&gt;=6000),T83,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD83" s="24" t="str">
-        <f>IF(AND($T83=8000, ($T83+$W83-$AB83)&gt;=8000),T83,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE83" s="24" t="str">
-        <f>IF(($T83+$W83-$AB83)&gt;=$T83+8000,W83,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF83" s="25" t="str">
-        <f>IF(AB83&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10479,23 +10485,23 @@
         <v>8000</v>
       </c>
       <c r="J84" s="24">
-        <f>(1-$D84)*E84</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K84" s="24">
-        <f>(1-$D84)*F84</f>
+        <f t="shared" si="23"/>
         <v>40000</v>
       </c>
       <c r="L84" s="24">
-        <f>G84</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="M84" s="24">
-        <f>(1-$D84)*H84</f>
+        <f t="shared" si="25"/>
         <v>2000</v>
       </c>
       <c r="N84" s="24">
-        <f>(1-$D84)*I84</f>
+        <f t="shared" si="26"/>
         <v>8000</v>
       </c>
       <c r="O84" s="24">
@@ -10532,30 +10538,30 @@
         <v>5830</v>
       </c>
       <c r="Z84" s="24">
-        <f>SUM(J84:Y84)</f>
+        <f t="shared" si="27"/>
         <v>87040</v>
       </c>
       <c r="AA84" s="24">
         <v>0</v>
       </c>
       <c r="AB84" s="20">
-        <f>Z84-AA84</f>
+        <f t="shared" si="28"/>
         <v>87040</v>
       </c>
       <c r="AC84" s="24" t="str">
-        <f>IF(AND($T84=6000, ($T84+$W84-$AB84)&gt;=6000),T84,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD84" s="24" t="str">
-        <f>IF(AND($T84=8000, ($T84+$W84-$AB84)&gt;=8000),T84,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE84" s="24" t="str">
-        <f>IF(($T84+$W84-$AB84)&gt;=$T84+8000,W84,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF84" s="25" t="str">
-        <f>IF(AB84&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10588,23 +10594,23 @@
         <v>0</v>
       </c>
       <c r="J85" s="24">
-        <f>(1-$D85)*E85</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K85" s="24">
-        <f>(1-$D85)*F85</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L85" s="24">
-        <f>G85</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M85" s="24">
-        <f>(1-$D85)*H85</f>
+        <f t="shared" si="25"/>
         <v>750</v>
       </c>
       <c r="N85" s="24">
-        <f>(1-$D85)*I85</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O85" s="24">
@@ -10641,30 +10647,30 @@
         <v>0</v>
       </c>
       <c r="Z85" s="24">
-        <f>SUM(J85:Y85)</f>
+        <f t="shared" si="27"/>
         <v>60390</v>
       </c>
       <c r="AA85" s="24">
         <v>0</v>
       </c>
       <c r="AB85" s="20">
-        <f>Z85-AA85</f>
+        <f t="shared" si="28"/>
         <v>60390</v>
       </c>
       <c r="AC85" s="24" t="str">
-        <f>IF(AND($T85=6000, ($T85+$W85-$AB85)&gt;=6000),T85,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD85" s="24" t="str">
-        <f>IF(AND($T85=8000, ($T85+$W85-$AB85)&gt;=8000),T85,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE85" s="24" t="str">
-        <f>IF(($T85+$W85-$AB85)&gt;=$T85+8000,W85,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF85" s="25" t="str">
-        <f>IF(AB85&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10697,23 +10703,23 @@
         <v>5000</v>
       </c>
       <c r="J86" s="24">
-        <f>(1-$D86)*E86</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K86" s="24">
-        <f>(1-$D86)*F86</f>
+        <f t="shared" si="23"/>
         <v>21000</v>
       </c>
       <c r="L86" s="24">
-        <f>G86</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M86" s="24">
-        <f>(1-$D86)*H86</f>
+        <f t="shared" si="25"/>
         <v>1875</v>
       </c>
       <c r="N86" s="24">
-        <f>(1-$D86)*I86</f>
+        <f t="shared" si="26"/>
         <v>3750</v>
       </c>
       <c r="O86" s="24">
@@ -10750,30 +10756,30 @@
         <v>0</v>
       </c>
       <c r="Z86" s="24">
-        <f>SUM(J86:Y86)</f>
+        <f t="shared" si="27"/>
         <v>83925</v>
       </c>
       <c r="AA86" s="24">
         <v>0</v>
       </c>
       <c r="AB86" s="20">
-        <f>Z86-AA86</f>
+        <f t="shared" si="28"/>
         <v>83925</v>
       </c>
       <c r="AC86" s="24" t="str">
-        <f>IF(AND($T86=6000, ($T86+$W86-$AB86)&gt;=6000),T86,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD86" s="24" t="str">
-        <f>IF(AND($T86=8000, ($T86+$W86-$AB86)&gt;=8000),T86,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE86" s="24" t="str">
-        <f>IF(($T86+$W86-$AB86)&gt;=$T86+8000,W86,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF86" s="25" t="str">
-        <f>IF(AB86&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10806,23 +10812,23 @@
         <v>0</v>
       </c>
       <c r="J87" s="24">
-        <f>(1-$D87)*E87</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K87" s="24">
-        <f>(1-$D87)*F87</f>
+        <f t="shared" si="23"/>
         <v>26000</v>
       </c>
       <c r="L87" s="24">
-        <f>G87</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M87" s="24">
-        <f>(1-$D87)*H87</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N87" s="24">
-        <f>(1-$D87)*I87</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O87" s="24">
@@ -10859,30 +10865,30 @@
         <v>-3030</v>
       </c>
       <c r="Z87" s="24">
-        <f>SUM(J87:Y87)</f>
+        <f t="shared" si="27"/>
         <v>47900</v>
       </c>
       <c r="AA87" s="24">
         <v>0</v>
       </c>
       <c r="AB87" s="20">
-        <f>Z87-AA87</f>
+        <f t="shared" si="28"/>
         <v>47900</v>
       </c>
       <c r="AC87" s="24" t="str">
-        <f>IF(AND($T87=6000, ($T87+$W87-$AB87)&gt;=6000),T87,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD87" s="24" t="str">
-        <f>IF(AND($T87=8000, ($T87+$W87-$AB87)&gt;=8000),T87,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE87" s="24" t="str">
-        <f>IF(($T87+$W87-$AB87)&gt;=$T87+8000,W87,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF87" s="25" t="str">
-        <f>IF(AB87&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -10915,23 +10921,23 @@
         <v>0</v>
       </c>
       <c r="J88" s="24">
-        <f>(1-$D88)*E88</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K88" s="24">
-        <f>(1-$D88)*F88</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L88" s="24">
-        <f>G88</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M88" s="24">
-        <f>(1-$D88)*H88</f>
+        <f t="shared" si="25"/>
         <v>750</v>
       </c>
       <c r="N88" s="24">
-        <f>(1-$D88)*I88</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O88" s="24">
@@ -10968,30 +10974,30 @@
         <v>3500</v>
       </c>
       <c r="Z88" s="24">
-        <f>SUM(J88:Y88)</f>
+        <f t="shared" si="27"/>
         <v>39890</v>
       </c>
       <c r="AA88" s="24">
         <v>0</v>
       </c>
       <c r="AB88" s="20">
-        <f>Z88-AA88</f>
+        <f t="shared" si="28"/>
         <v>39890</v>
       </c>
       <c r="AC88" s="24" t="str">
-        <f>IF(AND($T88=6000, ($T88+$W88-$AB88)&gt;=6000),T88,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD88" s="24" t="str">
-        <f>IF(AND($T88=8000, ($T88+$W88-$AB88)&gt;=8000),T88,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE88" s="24" t="str">
-        <f>IF(($T88+$W88-$AB88)&gt;=$T88+8000,W88,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF88" s="25" t="str">
-        <f>IF(AB88&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11024,23 +11030,23 @@
         <v>0</v>
       </c>
       <c r="J89" s="24">
-        <f>(1-$D89)*E89</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K89" s="24">
-        <f>(1-$D89)*F89</f>
+        <f t="shared" si="23"/>
         <v>26000</v>
       </c>
       <c r="L89" s="24">
-        <f>G89</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M89" s="24">
-        <f>(1-$D89)*H89</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N89" s="24">
-        <f>(1-$D89)*I89</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O89" s="24">
@@ -11077,30 +11083,30 @@
         <v>0</v>
       </c>
       <c r="Z89" s="24">
-        <f>SUM(J89:Y89)</f>
+        <f t="shared" si="27"/>
         <v>56930</v>
       </c>
       <c r="AA89" s="24">
         <v>0</v>
       </c>
       <c r="AB89" s="20">
-        <f>Z89-AA89</f>
+        <f t="shared" si="28"/>
         <v>56930</v>
       </c>
       <c r="AC89" s="24" t="str">
-        <f>IF(AND($T89=6000, ($T89+$W89-$AB89)&gt;=6000),T89,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD89" s="24" t="str">
-        <f>IF(AND($T89=8000, ($T89+$W89-$AB89)&gt;=8000),T89,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE89" s="24" t="str">
-        <f>IF(($T89+$W89-$AB89)&gt;=$T89+8000,W89,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF89" s="25" t="str">
-        <f>IF(AB89&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11133,23 +11139,23 @@
         <v>0</v>
       </c>
       <c r="J90" s="24">
-        <f>(1-$D90)*E90</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K90" s="24">
-        <f>(1-$D90)*F90</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L90" s="24">
-        <f>G90</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M90" s="24">
-        <f>(1-$D90)*H90</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N90" s="24">
-        <f>(1-$D90)*I90</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O90" s="24">
@@ -11186,30 +11192,30 @@
         <v>0</v>
       </c>
       <c r="Z90" s="24">
-        <f>SUM(J90:Y90)</f>
+        <f t="shared" si="27"/>
         <v>50430</v>
       </c>
       <c r="AA90" s="24">
         <v>0</v>
       </c>
       <c r="AB90" s="20">
-        <f>Z90-AA90</f>
+        <f t="shared" si="28"/>
         <v>50430</v>
       </c>
       <c r="AC90" s="24" t="str">
-        <f>IF(AND($T90=6000, ($T90+$W90-$AB90)&gt;=6000),T90,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD90" s="24" t="str">
-        <f>IF(AND($T90=8000, ($T90+$W90-$AB90)&gt;=8000),T90,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE90" s="24" t="str">
-        <f>IF(($T90+$W90-$AB90)&gt;=$T90+8000,W90,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF90" s="25" t="str">
-        <f>IF(AB90&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11242,23 +11248,23 @@
         <v>5000</v>
       </c>
       <c r="J91" s="24">
-        <f>(1-$D91)*E91</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K91" s="24">
-        <f>(1-$D91)*F91</f>
+        <f t="shared" si="23"/>
         <v>21000</v>
       </c>
       <c r="L91" s="24">
-        <f>G91</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M91" s="24">
-        <f>(1-$D91)*H91</f>
+        <f t="shared" si="25"/>
         <v>1875</v>
       </c>
       <c r="N91" s="24">
-        <f>(1-$D91)*I91</f>
+        <f t="shared" si="26"/>
         <v>3750</v>
       </c>
       <c r="O91" s="24">
@@ -11295,30 +11301,30 @@
         <v>0</v>
       </c>
       <c r="Z91" s="24">
-        <f>SUM(J91:Y91)</f>
+        <f t="shared" si="27"/>
         <v>73925</v>
       </c>
       <c r="AA91" s="24">
         <v>0</v>
       </c>
       <c r="AB91" s="20">
-        <f>Z91-AA91</f>
+        <f t="shared" si="28"/>
         <v>73925</v>
       </c>
       <c r="AC91" s="24" t="str">
-        <f>IF(AND($T91=6000, ($T91+$W91-$AB91)&gt;=6000),T91,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD91" s="24" t="str">
-        <f>IF(AND($T91=8000, ($T91+$W91-$AB91)&gt;=8000),T91,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE91" s="24" t="str">
-        <f>IF(($T91+$W91-$AB91)&gt;=$T91+8000,W91,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF91" s="25" t="str">
-        <f>IF(AB91&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11351,23 +11357,23 @@
         <v>5000</v>
       </c>
       <c r="J92" s="24">
-        <f>(1-$D92)*E92</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K92" s="24">
-        <f>(1-$D92)*F92</f>
+        <f t="shared" si="23"/>
         <v>21000</v>
       </c>
       <c r="L92" s="24">
-        <f>G92</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M92" s="24">
-        <f>(1-$D92)*H92</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N92" s="24">
-        <f>(1-$D92)*I92</f>
+        <f t="shared" si="26"/>
         <v>3750</v>
       </c>
       <c r="O92" s="24">
@@ -11404,30 +11410,30 @@
         <v>0</v>
       </c>
       <c r="Z92" s="24">
-        <f>SUM(J92:Y92)</f>
+        <f t="shared" si="27"/>
         <v>75290</v>
       </c>
       <c r="AA92" s="24">
         <v>0</v>
       </c>
       <c r="AB92" s="20">
-        <f>Z92-AA92</f>
+        <f t="shared" si="28"/>
         <v>75290</v>
       </c>
       <c r="AC92" s="24" t="str">
-        <f>IF(AND($T92=6000, ($T92+$W92-$AB92)&gt;=6000),T92,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD92" s="24" t="str">
-        <f>IF(AND($T92=8000, ($T92+$W92-$AB92)&gt;=8000),T92,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE92" s="24" t="str">
-        <f>IF(($T92+$W92-$AB92)&gt;=$T92+8000,W92,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF92" s="25" t="str">
-        <f>IF(AB92&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11460,23 +11466,23 @@
         <v>5000</v>
       </c>
       <c r="J93" s="24">
-        <f>(1-$D93)*E93</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K93" s="24">
-        <f>(1-$D93)*F93</f>
+        <f t="shared" si="23"/>
         <v>28000</v>
       </c>
       <c r="L93" s="24">
-        <f>G93</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M93" s="24">
-        <f>(1-$D93)*H93</f>
+        <f t="shared" si="25"/>
         <v>2500</v>
       </c>
       <c r="N93" s="24">
-        <f>(1-$D93)*I93</f>
+        <f t="shared" si="26"/>
         <v>5000</v>
       </c>
       <c r="O93" s="24">
@@ -11513,30 +11519,30 @@
         <v>0</v>
       </c>
       <c r="Z93" s="24">
-        <f>SUM(J93:Y93)</f>
+        <f t="shared" si="27"/>
         <v>76800</v>
       </c>
       <c r="AA93" s="24">
         <v>0</v>
       </c>
       <c r="AB93" s="20">
-        <f>Z93-AA93</f>
+        <f t="shared" si="28"/>
         <v>76800</v>
       </c>
       <c r="AC93" s="24" t="str">
-        <f>IF(AND($T93=6000, ($T93+$W93-$AB93)&gt;=6000),T93,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD93" s="24" t="str">
-        <f>IF(AND($T93=8000, ($T93+$W93-$AB93)&gt;=8000),T93,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE93" s="24" t="str">
-        <f>IF(($T93+$W93-$AB93)&gt;=$T93+8000,W93,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF93" s="25" t="str">
-        <f>IF(AB93&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11569,23 +11575,23 @@
         <v>5000</v>
       </c>
       <c r="J94" s="24">
-        <f>(1-$D94)*E94</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K94" s="24">
-        <f>(1-$D94)*F94</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="L94" s="24">
-        <f>G94</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M94" s="24">
-        <f>(1-$D94)*H94</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N94" s="24">
-        <f>(1-$D94)*I94</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O94" s="24">
@@ -11622,30 +11628,30 @@
         <v>0</v>
       </c>
       <c r="Z94" s="24">
-        <f>SUM(J94:Y94)</f>
+        <f t="shared" si="27"/>
         <v>50560</v>
       </c>
       <c r="AA94" s="24">
         <v>0</v>
       </c>
       <c r="AB94" s="20">
-        <f>Z94-AA94</f>
+        <f t="shared" si="28"/>
         <v>50560</v>
       </c>
       <c r="AC94" s="24" t="str">
-        <f>IF(AND($T94=6000, ($T94+$W94-$AB94)&gt;=6000),T94,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD94" s="24" t="str">
-        <f>IF(AND($T94=8000, ($T94+$W94-$AB94)&gt;=8000),T94,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE94" s="24" t="str">
-        <f>IF(($T94+$W94-$AB94)&gt;=$T94+8000,W94,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF94" s="25" t="str">
-        <f>IF(AB94&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11678,23 +11684,23 @@
         <v>0</v>
       </c>
       <c r="J95" s="24">
-        <f>(1-$D95)*E95</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K95" s="24">
-        <f>(1-$D95)*F95</f>
+        <f t="shared" si="23"/>
         <v>19500</v>
       </c>
       <c r="L95" s="24">
-        <f>G95</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M95" s="24">
-        <f>(1-$D95)*H95</f>
+        <f t="shared" si="25"/>
         <v>750</v>
       </c>
       <c r="N95" s="24">
-        <f>(1-$D95)*I95</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O95" s="24">
@@ -11731,30 +11737,30 @@
         <v>65</v>
       </c>
       <c r="Z95" s="24">
-        <f>SUM(J95:Y95)</f>
+        <f t="shared" si="27"/>
         <v>50345</v>
       </c>
       <c r="AA95" s="24">
         <v>0</v>
       </c>
       <c r="AB95" s="20">
-        <f>Z95-AA95</f>
+        <f t="shared" si="28"/>
         <v>50345</v>
       </c>
       <c r="AC95" s="24" t="str">
-        <f>IF(AND($T95=6000, ($T95+$W95-$AB95)&gt;=6000),T95,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD95" s="24" t="str">
-        <f>IF(AND($T95=8000, ($T95+$W95-$AB95)&gt;=8000),T95,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE95" s="24" t="str">
-        <f>IF(($T95+$W95-$AB95)&gt;=$T95+8000,W95,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF95" s="25" t="str">
-        <f>IF(AB95&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11787,23 +11793,23 @@
         <v>5000</v>
       </c>
       <c r="J96" s="24">
-        <f>(1-$D96)*E96</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K96" s="24">
-        <f>(1-$D96)*F96</f>
+        <f t="shared" si="23"/>
         <v>21000</v>
       </c>
       <c r="L96" s="24">
-        <f>G96</f>
+        <f t="shared" si="24"/>
         <v>4000</v>
       </c>
       <c r="M96" s="24">
-        <f>(1-$D96)*H96</f>
+        <f t="shared" si="25"/>
         <v>1875</v>
       </c>
       <c r="N96" s="24">
-        <f>(1-$D96)*I96</f>
+        <f t="shared" si="26"/>
         <v>3750</v>
       </c>
       <c r="O96" s="24">
@@ -11840,30 +11846,30 @@
         <v>0</v>
       </c>
       <c r="Z96" s="24">
-        <f>SUM(J96:Y96)</f>
+        <f t="shared" si="27"/>
         <v>73925</v>
       </c>
       <c r="AA96" s="24">
         <v>0</v>
       </c>
       <c r="AB96" s="20">
-        <f>Z96-AA96</f>
+        <f t="shared" si="28"/>
         <v>73925</v>
       </c>
       <c r="AC96" s="24" t="str">
-        <f>IF(AND($T96=6000, ($T96+$W96-$AB96)&gt;=6000),T96,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD96" s="24" t="str">
-        <f>IF(AND($T96=8000, ($T96+$W96-$AB96)&gt;=8000),T96,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE96" s="24" t="str">
-        <f>IF(($T96+$W96-$AB96)&gt;=$T96+8000,W96,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF96" s="25" t="str">
-        <f>IF(AB96&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11896,23 +11902,23 @@
         <v>6000</v>
       </c>
       <c r="J97" s="24">
-        <f>(1-$D97)*E97</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K97" s="24">
-        <f>(1-$D97)*F97</f>
+        <f t="shared" si="23"/>
         <v>23100</v>
       </c>
       <c r="L97" s="24">
-        <f>G97</f>
+        <f t="shared" si="24"/>
         <v>5000</v>
       </c>
       <c r="M97" s="24">
-        <f>(1-$D97)*H97</f>
+        <f t="shared" si="25"/>
         <v>1400</v>
       </c>
       <c r="N97" s="24">
-        <f>(1-$D97)*I97</f>
+        <f t="shared" si="26"/>
         <v>4200</v>
       </c>
       <c r="O97" s="24">
@@ -11949,30 +11955,30 @@
         <v>0</v>
       </c>
       <c r="Z97" s="24">
-        <f>SUM(J97:Y97)</f>
+        <f t="shared" si="27"/>
         <v>70430</v>
       </c>
       <c r="AA97" s="24">
         <v>0</v>
       </c>
       <c r="AB97" s="20">
-        <f>Z97-AA97</f>
+        <f t="shared" si="28"/>
         <v>70430</v>
       </c>
       <c r="AC97" s="24" t="str">
-        <f>IF(AND($T97=6000, ($T97+$W97-$AB97)&gt;=6000),T97,"")</f>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="AD97" s="24" t="str">
-        <f>IF(AND($T97=8000, ($T97+$W97-$AB97)&gt;=8000),T97,"")</f>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AE97" s="24" t="str">
-        <f>IF(($T97+$W97-$AB97)&gt;=$T97+8000,W97,"")</f>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AF97" s="25" t="str">
-        <f>IF(AB97&lt;=0,"BONUS","")</f>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11987,7 +11993,7 @@
         <v>49</v>
       </c>
       <c r="D98" s="23">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E98" s="24">
         <v>0</v>
@@ -12005,23 +12011,23 @@
         <v>0</v>
       </c>
       <c r="J98" s="24">
-        <f>(1-$D98)*E98</f>
+        <f t="shared" ref="J98:J122" si="33">(1-$D98)*E98</f>
         <v>0</v>
       </c>
       <c r="K98" s="24">
-        <f>(1-$D98)*F98</f>
-        <v>26000</v>
+        <f t="shared" ref="K98:K122" si="34">(1-$D98)*F98</f>
+        <v>24700</v>
       </c>
       <c r="L98" s="24">
-        <f>G98</f>
+        <f t="shared" ref="L98:L122" si="35">G98</f>
         <v>4000</v>
       </c>
       <c r="M98" s="24">
-        <f>(1-$D98)*H98</f>
-        <v>1000</v>
+        <f t="shared" ref="M98:M122" si="36">(1-$D98)*H98</f>
+        <v>950</v>
       </c>
       <c r="N98" s="24">
-        <f>(1-$D98)*I98</f>
+        <f t="shared" ref="N98:N122" si="37">(1-$D98)*I98</f>
         <v>0</v>
       </c>
       <c r="O98" s="24">
@@ -12058,31 +12064,31 @@
         <v>-10000</v>
       </c>
       <c r="Z98" s="24">
-        <f>SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z129" si="38">SUM(J98:Y98)</f>
+        <v>31790</v>
+      </c>
+      <c r="AA98" s="24">
         <v>33140</v>
       </c>
-      <c r="AA98" s="24">
-        <v>0</v>
-      </c>
       <c r="AB98" s="20">
-        <f>Z98-AA98</f>
-        <v>33140</v>
+        <f t="shared" ref="AB98:AB129" si="39">Z98-AA98</f>
+        <v>-1350</v>
       </c>
       <c r="AC98" s="24" t="str">
-        <f>IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
+        <f t="shared" ref="AC98:AC122" si="40">IF(AND($T98=6000, ($T98+$W98-$AB98)&gt;=6000),T98,"")</f>
         <v/>
       </c>
       <c r="AD98" s="24" t="str">
-        <f>IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
+        <f t="shared" ref="AD98:AD122" si="41">IF(AND($T98=8000, ($T98+$W98-$AB98)&gt;=8000),T98,"")</f>
         <v/>
       </c>
       <c r="AE98" s="24" t="str">
-        <f>IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
+        <f t="shared" ref="AE98:AE122" si="42">IF(($T98+$W98-$AB98)&gt;=$T98+8000,W98,"")</f>
         <v/>
       </c>
       <c r="AF98" s="25" t="str">
-        <f>IF(AB98&lt;=0,"BONUS","")</f>
-        <v/>
+        <f t="shared" ref="AF98:AF122" si="43">IF(AB98&lt;=0,"BONUS","")</f>
+        <v>BONUS</v>
       </c>
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.25">
@@ -12114,23 +12120,23 @@
         <v>0</v>
       </c>
       <c r="J99" s="24">
-        <f>(1-$D99)*E99</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K99" s="24">
-        <f>(1-$D99)*F99</f>
+        <f t="shared" si="34"/>
         <v>13000</v>
       </c>
       <c r="L99" s="24">
-        <f>G99</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M99" s="24">
-        <f>(1-$D99)*H99</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N99" s="24">
-        <f>(1-$D99)*I99</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O99" s="24">
@@ -12167,30 +12173,30 @@
         <v>8000</v>
       </c>
       <c r="Z99" s="24">
-        <f>SUM(J99:Y99)</f>
+        <f t="shared" si="38"/>
         <v>45930</v>
       </c>
       <c r="AA99" s="24">
         <v>0</v>
       </c>
       <c r="AB99" s="20">
-        <f>Z99-AA99</f>
+        <f t="shared" si="39"/>
         <v>45930</v>
       </c>
       <c r="AC99" s="24" t="str">
-        <f>IF(AND($T99=6000, ($T99+$W99-$AB99)&gt;=6000),T99,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD99" s="24" t="str">
-        <f>IF(AND($T99=8000, ($T99+$W99-$AB99)&gt;=8000),T99,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE99" s="24" t="str">
-        <f>IF(($T99+$W99-$AB99)&gt;=$T99+8000,W99,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF99" s="25" t="str">
-        <f>IF(AB99&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12223,23 +12229,23 @@
         <v>5000</v>
       </c>
       <c r="J100" s="24">
-        <f>(1-$D100)*E100</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K100" s="24">
-        <f>(1-$D100)*F100</f>
+        <f t="shared" si="34"/>
         <v>14000</v>
       </c>
       <c r="L100" s="24">
-        <f>G100</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M100" s="24">
-        <f>(1-$D100)*H100</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N100" s="24">
-        <f>(1-$D100)*I100</f>
+        <f t="shared" si="37"/>
         <v>2500</v>
       </c>
       <c r="O100" s="24">
@@ -12276,30 +12282,30 @@
         <v>0</v>
       </c>
       <c r="Z100" s="24">
-        <f>SUM(J100:Y100)</f>
+        <f t="shared" si="38"/>
         <v>57980</v>
       </c>
       <c r="AA100" s="24">
         <v>0</v>
       </c>
       <c r="AB100" s="20">
-        <f>Z100-AA100</f>
+        <f t="shared" si="39"/>
         <v>57980</v>
       </c>
       <c r="AC100" s="24" t="str">
-        <f>IF(AND($T100=6000, ($T100+$W100-$AB100)&gt;=6000),T100,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD100" s="24" t="str">
-        <f>IF(AND($T100=8000, ($T100+$W100-$AB100)&gt;=8000),T100,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE100" s="24" t="str">
-        <f>IF(($T100+$W100-$AB100)&gt;=$T100+8000,W100,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF100" s="25" t="str">
-        <f>IF(AB100&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12332,23 +12338,23 @@
         <v>6000</v>
       </c>
       <c r="J101" s="24">
-        <f>(1-$D101)*E101</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K101" s="24">
-        <f>(1-$D101)*F101</f>
+        <f t="shared" si="34"/>
         <v>16500</v>
       </c>
       <c r="L101" s="24">
-        <f>G101</f>
+        <f t="shared" si="35"/>
         <v>5000</v>
       </c>
       <c r="M101" s="24">
-        <f>(1-$D101)*H101</f>
+        <f t="shared" si="36"/>
         <v>1000</v>
       </c>
       <c r="N101" s="24">
-        <f>(1-$D101)*I101</f>
+        <f t="shared" si="37"/>
         <v>3000</v>
       </c>
       <c r="O101" s="24">
@@ -12385,30 +12391,30 @@
         <v>-3145</v>
       </c>
       <c r="Z101" s="24">
-        <f>SUM(J101:Y101)</f>
+        <f t="shared" si="38"/>
         <v>67085</v>
       </c>
       <c r="AA101" s="24">
         <v>0</v>
       </c>
       <c r="AB101" s="20">
-        <f>Z101-AA101</f>
+        <f t="shared" si="39"/>
         <v>67085</v>
       </c>
       <c r="AC101" s="24" t="str">
-        <f>IF(AND($T101=6000, ($T101+$W101-$AB101)&gt;=6000),T101,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD101" s="24" t="str">
-        <f>IF(AND($T101=8000, ($T101+$W101-$AB101)&gt;=8000),T101,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE101" s="24" t="str">
-        <f>IF(($T101+$W101-$AB101)&gt;=$T101+8000,W101,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF101" s="25" t="str">
-        <f>IF(AB101&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12441,23 +12447,23 @@
         <v>0</v>
       </c>
       <c r="J102" s="24">
-        <f>(1-$D102)*E102</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K102" s="24">
-        <f>(1-$D102)*F102</f>
+        <f t="shared" si="34"/>
         <v>19500</v>
       </c>
       <c r="L102" s="24">
-        <f>G102</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M102" s="24">
-        <f>(1-$D102)*H102</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N102" s="24">
-        <f>(1-$D102)*I102</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O102" s="24">
@@ -12494,30 +12500,30 @@
         <v>0</v>
       </c>
       <c r="Z102" s="24">
-        <f>SUM(J102:Y102)</f>
+        <f t="shared" si="38"/>
         <v>52430</v>
       </c>
       <c r="AA102" s="24">
         <v>0</v>
       </c>
       <c r="AB102" s="20">
-        <f>Z102-AA102</f>
+        <f t="shared" si="39"/>
         <v>52430</v>
       </c>
       <c r="AC102" s="24" t="str">
-        <f>IF(AND($T102=6000, ($T102+$W102-$AB102)&gt;=6000),T102,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD102" s="24" t="str">
-        <f>IF(AND($T102=8000, ($T102+$W102-$AB102)&gt;=8000),T102,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE102" s="24" t="str">
-        <f>IF(($T102+$W102-$AB102)&gt;=$T102+8000,W102,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF102" s="25" t="str">
-        <f>IF(AB102&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12550,23 +12556,23 @@
         <v>5000</v>
       </c>
       <c r="J103" s="24">
-        <f>(1-$D103)*E103</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K103" s="24">
-        <f>(1-$D103)*F103</f>
+        <f t="shared" si="34"/>
         <v>21000</v>
       </c>
       <c r="L103" s="24">
-        <f>G103</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M103" s="24">
-        <f>(1-$D103)*H103</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N103" s="24">
-        <f>(1-$D103)*I103</f>
+        <f t="shared" si="37"/>
         <v>3750</v>
       </c>
       <c r="O103" s="24">
@@ -12603,30 +12609,30 @@
         <v>0</v>
       </c>
       <c r="Z103" s="24">
-        <f>SUM(J103:Y103)</f>
+        <f t="shared" si="38"/>
         <v>77290</v>
       </c>
       <c r="AA103" s="24">
         <v>0</v>
       </c>
       <c r="AB103" s="20">
-        <f>Z103-AA103</f>
+        <f t="shared" si="39"/>
         <v>77290</v>
       </c>
       <c r="AC103" s="24" t="str">
-        <f>IF(AND($T103=6000, ($T103+$W103-$AB103)&gt;=6000),T103,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD103" s="24" t="str">
-        <f>IF(AND($T103=8000, ($T103+$W103-$AB103)&gt;=8000),T103,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE103" s="24" t="str">
-        <f>IF(($T103+$W103-$AB103)&gt;=$T103+8000,W103,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF103" s="25" t="str">
-        <f>IF(AB103&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12659,23 +12665,23 @@
         <v>0</v>
       </c>
       <c r="J104" s="24">
-        <f>(1-$D104)*E104</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K104" s="24">
-        <f>(1-$D104)*F104</f>
+        <f t="shared" si="34"/>
         <v>19500</v>
       </c>
       <c r="L104" s="24">
-        <f>G104</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M104" s="24">
-        <f>(1-$D104)*H104</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N104" s="24">
-        <f>(1-$D104)*I104</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O104" s="24">
@@ -12712,30 +12718,30 @@
         <v>0</v>
       </c>
       <c r="Z104" s="24">
-        <f>SUM(J104:Y104)</f>
+        <f t="shared" si="38"/>
         <v>65160</v>
       </c>
       <c r="AA104" s="24">
         <v>0</v>
       </c>
       <c r="AB104" s="20">
-        <f>Z104-AA104</f>
+        <f t="shared" si="39"/>
         <v>65160</v>
       </c>
       <c r="AC104" s="24" t="str">
-        <f>IF(AND($T104=6000, ($T104+$W104-$AB104)&gt;=6000),T104,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD104" s="24" t="str">
-        <f>IF(AND($T104=8000, ($T104+$W104-$AB104)&gt;=8000),T104,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE104" s="24" t="str">
-        <f>IF(($T104+$W104-$AB104)&gt;=$T104+8000,W104,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF104" s="25" t="str">
-        <f>IF(AB104&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12768,23 +12774,23 @@
         <v>5000</v>
       </c>
       <c r="J105" s="24">
-        <f>(1-$D105)*E105</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K105" s="24">
-        <f>(1-$D105)*F105</f>
+        <f t="shared" si="34"/>
         <v>21000</v>
       </c>
       <c r="L105" s="24">
-        <f>G105</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M105" s="24">
-        <f>(1-$D105)*H105</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N105" s="24">
-        <f>(1-$D105)*I105</f>
+        <f t="shared" si="37"/>
         <v>3750</v>
       </c>
       <c r="O105" s="24">
@@ -12821,30 +12827,30 @@
         <v>0</v>
       </c>
       <c r="Z105" s="24">
-        <f>SUM(J105:Y105)</f>
+        <f t="shared" si="38"/>
         <v>75290</v>
       </c>
       <c r="AA105" s="24">
         <v>0</v>
       </c>
       <c r="AB105" s="20">
-        <f>Z105-AA105</f>
+        <f t="shared" si="39"/>
         <v>75290</v>
       </c>
       <c r="AC105" s="24" t="str">
-        <f>IF(AND($T105=6000, ($T105+$W105-$AB105)&gt;=6000),T105,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD105" s="24" t="str">
-        <f>IF(AND($T105=8000, ($T105+$W105-$AB105)&gt;=8000),T105,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE105" s="24" t="str">
-        <f>IF(($T105+$W105-$AB105)&gt;=$T105+8000,W105,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF105" s="25" t="str">
-        <f>IF(AB105&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12877,23 +12883,23 @@
         <v>0</v>
       </c>
       <c r="J106" s="24">
-        <f>(1-$D106)*E106</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K106" s="24">
-        <f>(1-$D106)*F106</f>
+        <f t="shared" si="34"/>
         <v>19500</v>
       </c>
       <c r="L106" s="24">
-        <f>G106</f>
+        <f t="shared" si="35"/>
         <v>2000</v>
       </c>
       <c r="M106" s="24">
-        <f>(1-$D106)*H106</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N106" s="24">
-        <f>(1-$D106)*I106</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O106" s="24">
@@ -12930,30 +12936,30 @@
         <v>0</v>
       </c>
       <c r="Z106" s="24">
-        <f>SUM(J106:Y106)</f>
+        <f t="shared" si="38"/>
         <v>24550</v>
       </c>
       <c r="AA106" s="24">
         <v>0</v>
       </c>
       <c r="AB106" s="20">
-        <f>Z106-AA106</f>
+        <f t="shared" si="39"/>
         <v>24550</v>
       </c>
       <c r="AC106" s="24" t="str">
-        <f>IF(AND($T106=6000, ($T106+$W106-$AB106)&gt;=6000),T106,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD106" s="24" t="str">
-        <f>IF(AND($T106=8000, ($T106+$W106-$AB106)&gt;=8000),T106,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE106" s="24" t="str">
-        <f>IF(($T106+$W106-$AB106)&gt;=$T106+8000,W106,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF106" s="25" t="str">
-        <f>IF(AB106&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12986,23 +12992,23 @@
         <v>0</v>
       </c>
       <c r="J107" s="24">
-        <f>(1-$D107)*E107</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K107" s="24">
-        <f>(1-$D107)*F107</f>
+        <f t="shared" si="34"/>
         <v>19500</v>
       </c>
       <c r="L107" s="24">
-        <f>G107</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M107" s="24">
-        <f>(1-$D107)*H107</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N107" s="24">
-        <f>(1-$D107)*I107</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O107" s="24">
@@ -13039,30 +13045,30 @@
         <v>0</v>
       </c>
       <c r="Z107" s="24">
-        <f>SUM(J107:Y107)</f>
+        <f t="shared" si="38"/>
         <v>65160</v>
       </c>
       <c r="AA107" s="24">
         <v>0</v>
       </c>
       <c r="AB107" s="20">
-        <f>Z107-AA107</f>
+        <f t="shared" si="39"/>
         <v>65160</v>
       </c>
       <c r="AC107" s="24" t="str">
-        <f>IF(AND($T107=6000, ($T107+$W107-$AB107)&gt;=6000),T107,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD107" s="24" t="str">
-        <f>IF(AND($T107=8000, ($T107+$W107-$AB107)&gt;=8000),T107,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE107" s="24" t="str">
-        <f>IF(($T107+$W107-$AB107)&gt;=$T107+8000,W107,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF107" s="25" t="str">
-        <f>IF(AB107&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13095,23 +13101,23 @@
         <v>0</v>
       </c>
       <c r="J108" s="24">
-        <f>(1-$D108)*E108</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K108" s="24">
-        <f>(1-$D108)*F108</f>
+        <f t="shared" si="34"/>
         <v>26000</v>
       </c>
       <c r="L108" s="24">
-        <f>G108</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M108" s="24">
-        <f>(1-$D108)*H108</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N108" s="24">
-        <f>(1-$D108)*I108</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O108" s="24">
@@ -13148,30 +13154,30 @@
         <v>14240</v>
       </c>
       <c r="Z108" s="24">
-        <f>SUM(J108:Y108)</f>
+        <f t="shared" si="38"/>
         <v>85900</v>
       </c>
       <c r="AA108" s="24">
         <v>50000</v>
       </c>
       <c r="AB108" s="20">
-        <f>Z108-AA108</f>
+        <f t="shared" si="39"/>
         <v>35900</v>
       </c>
       <c r="AC108" s="24" t="str">
-        <f>IF(AND($T108=6000, ($T108+$W108-$AB108)&gt;=6000),T108,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD108" s="24" t="str">
-        <f>IF(AND($T108=8000, ($T108+$W108-$AB108)&gt;=8000),T108,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE108" s="24" t="str">
-        <f>IF(($T108+$W108-$AB108)&gt;=$T108+8000,W108,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF108" s="25" t="str">
-        <f>IF(AB108&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13204,23 +13210,23 @@
         <v>0</v>
       </c>
       <c r="J109" s="24">
-        <f>(1-$D109)*E109</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K109" s="24">
-        <f>(1-$D109)*F109</f>
+        <f t="shared" si="34"/>
         <v>19500</v>
       </c>
       <c r="L109" s="24">
-        <f>G109</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M109" s="24">
-        <f>(1-$D109)*H109</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N109" s="24">
-        <f>(1-$D109)*I109</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O109" s="24">
@@ -13257,30 +13263,30 @@
         <v>0</v>
       </c>
       <c r="Z109" s="24">
-        <f>SUM(J109:Y109)</f>
+        <f t="shared" si="38"/>
         <v>44430</v>
       </c>
       <c r="AA109" s="24">
         <v>0</v>
       </c>
       <c r="AB109" s="20">
-        <f>Z109-AA109</f>
+        <f t="shared" si="39"/>
         <v>44430</v>
       </c>
       <c r="AC109" s="24" t="str">
-        <f>IF(AND($T109=6000, ($T109+$W109-$AB109)&gt;=6000),T109,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD109" s="24" t="str">
-        <f>IF(AND($T109=8000, ($T109+$W109-$AB109)&gt;=8000),T109,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE109" s="24" t="str">
-        <f>IF(($T109+$W109-$AB109)&gt;=$T109+8000,W109,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF109" s="25" t="str">
-        <f>IF(AB109&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13313,23 +13319,23 @@
         <v>5000</v>
       </c>
       <c r="J110" s="24">
-        <f>(1-$D110)*E110</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K110" s="24">
-        <f>(1-$D110)*F110</f>
+        <f t="shared" si="34"/>
         <v>21000</v>
       </c>
       <c r="L110" s="24">
-        <f>G110</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M110" s="24">
-        <f>(1-$D110)*H110</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N110" s="24">
-        <f>(1-$D110)*I110</f>
+        <f t="shared" si="37"/>
         <v>3750</v>
       </c>
       <c r="O110" s="24">
@@ -13366,30 +13372,30 @@
         <v>0</v>
       </c>
       <c r="Z110" s="24">
-        <f>SUM(J110:Y110)</f>
+        <f t="shared" si="38"/>
         <v>66230</v>
       </c>
       <c r="AA110" s="24">
         <v>0</v>
       </c>
       <c r="AB110" s="20">
-        <f>Z110-AA110</f>
+        <f t="shared" si="39"/>
         <v>66230</v>
       </c>
       <c r="AC110" s="24" t="str">
-        <f>IF(AND($T110=6000, ($T110+$W110-$AB110)&gt;=6000),T110,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD110" s="24" t="str">
-        <f>IF(AND($T110=8000, ($T110+$W110-$AB110)&gt;=8000),T110,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE110" s="24" t="str">
-        <f>IF(($T110+$W110-$AB110)&gt;=$T110+8000,W110,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF110" s="25" t="str">
-        <f>IF(AB110&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13422,23 +13428,23 @@
         <v>5000</v>
       </c>
       <c r="J111" s="24">
-        <f>(1-$D111)*E111</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K111" s="24">
-        <f>(1-$D111)*F111</f>
+        <f t="shared" si="34"/>
         <v>21000</v>
       </c>
       <c r="L111" s="24">
-        <f>G111</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M111" s="24">
-        <f>(1-$D111)*H111</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N111" s="24">
-        <f>(1-$D111)*I111</f>
+        <f t="shared" si="37"/>
         <v>3750</v>
       </c>
       <c r="O111" s="24">
@@ -13475,30 +13481,30 @@
         <v>0</v>
       </c>
       <c r="Z111" s="24">
-        <f>SUM(J111:Y111)</f>
+        <f t="shared" si="38"/>
         <v>76770</v>
       </c>
       <c r="AA111" s="24">
         <v>0</v>
       </c>
       <c r="AB111" s="20">
-        <f>Z111-AA111</f>
+        <f t="shared" si="39"/>
         <v>76770</v>
       </c>
       <c r="AC111" s="24" t="str">
-        <f>IF(AND($T111=6000, ($T111+$W111-$AB111)&gt;=6000),T111,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD111" s="24" t="str">
-        <f>IF(AND($T111=8000, ($T111+$W111-$AB111)&gt;=8000),T111,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE111" s="24" t="str">
-        <f>IF(($T111+$W111-$AB111)&gt;=$T111+8000,W111,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF111" s="25" t="str">
-        <f>IF(AB111&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13531,23 +13537,23 @@
         <v>8000</v>
       </c>
       <c r="J112" s="24">
-        <f>(1-$D112)*E112</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K112" s="24">
-        <f>(1-$D112)*F112</f>
+        <f t="shared" si="34"/>
         <v>30000</v>
       </c>
       <c r="L112" s="24">
-        <f>G112</f>
+        <f t="shared" si="35"/>
         <v>5000</v>
       </c>
       <c r="M112" s="24">
-        <f>(1-$D112)*H112</f>
+        <f t="shared" si="36"/>
         <v>1500</v>
       </c>
       <c r="N112" s="24">
-        <f>(1-$D112)*I112</f>
+        <f t="shared" si="37"/>
         <v>6000</v>
       </c>
       <c r="O112" s="24">
@@ -13584,30 +13590,30 @@
         <v>2660</v>
       </c>
       <c r="Z112" s="24">
-        <f>SUM(J112:Y112)</f>
+        <f t="shared" si="38"/>
         <v>79370</v>
       </c>
       <c r="AA112" s="24">
         <v>0</v>
       </c>
       <c r="AB112" s="20">
-        <f>Z112-AA112</f>
+        <f t="shared" si="39"/>
         <v>79370</v>
       </c>
       <c r="AC112" s="24" t="str">
-        <f>IF(AND($T112=6000, ($T112+$W112-$AB112)&gt;=6000),T112,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD112" s="24" t="str">
-        <f>IF(AND($T112=8000, ($T112+$W112-$AB112)&gt;=8000),T112,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE112" s="24" t="str">
-        <f>IF(($T112+$W112-$AB112)&gt;=$T112+8000,W112,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF112" s="25" t="str">
-        <f>IF(AB112&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13640,23 +13646,23 @@
         <v>0</v>
       </c>
       <c r="J113" s="24">
-        <f>(1-$D113)*E113</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K113" s="24">
-        <f>(1-$D113)*F113</f>
+        <f t="shared" si="34"/>
         <v>19500</v>
       </c>
       <c r="L113" s="24">
-        <f>G113</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M113" s="24">
-        <f>(1-$D113)*H113</f>
+        <f t="shared" si="36"/>
         <v>750</v>
       </c>
       <c r="N113" s="24">
-        <f>(1-$D113)*I113</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O113" s="24">
@@ -13693,30 +13699,30 @@
         <v>1250</v>
       </c>
       <c r="Z113" s="24">
-        <f>SUM(J113:Y113)</f>
+        <f t="shared" si="38"/>
         <v>51530</v>
       </c>
       <c r="AA113" s="24">
         <v>0</v>
       </c>
       <c r="AB113" s="20">
-        <f>Z113-AA113</f>
+        <f t="shared" si="39"/>
         <v>51530</v>
       </c>
       <c r="AC113" s="24" t="str">
-        <f>IF(AND($T113=6000, ($T113+$W113-$AB113)&gt;=6000),T113,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD113" s="24" t="str">
-        <f>IF(AND($T113=8000, ($T113+$W113-$AB113)&gt;=8000),T113,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE113" s="24" t="str">
-        <f>IF(($T113+$W113-$AB113)&gt;=$T113+8000,W113,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF113" s="25" t="str">
-        <f>IF(AB113&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13749,23 +13755,23 @@
         <v>5000</v>
       </c>
       <c r="J114" s="24">
-        <f>(1-$D114)*E114</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K114" s="24">
-        <f>(1-$D114)*F114</f>
+        <f t="shared" si="34"/>
         <v>21000</v>
       </c>
       <c r="L114" s="24">
-        <f>G114</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M114" s="24">
-        <f>(1-$D114)*H114</f>
+        <f t="shared" si="36"/>
         <v>1875</v>
       </c>
       <c r="N114" s="24">
-        <f>(1-$D114)*I114</f>
+        <f t="shared" si="37"/>
         <v>3750</v>
       </c>
       <c r="O114" s="24">
@@ -13802,30 +13808,30 @@
         <v>9500</v>
       </c>
       <c r="Z114" s="24">
-        <f>SUM(J114:Y114)</f>
+        <f t="shared" si="38"/>
         <v>83425</v>
       </c>
       <c r="AA114" s="24">
         <v>0</v>
       </c>
       <c r="AB114" s="20">
-        <f>Z114-AA114</f>
+        <f t="shared" si="39"/>
         <v>83425</v>
       </c>
       <c r="AC114" s="24" t="str">
-        <f>IF(AND($T114=6000, ($T114+$W114-$AB114)&gt;=6000),T114,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD114" s="24" t="str">
-        <f>IF(AND($T114=8000, ($T114+$W114-$AB114)&gt;=8000),T114,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE114" s="24" t="str">
-        <f>IF(($T114+$W114-$AB114)&gt;=$T114+8000,W114,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF114" s="25" t="str">
-        <f>IF(AB114&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13858,23 +13864,23 @@
         <v>5000</v>
       </c>
       <c r="J115" s="24">
-        <f>(1-$D115)*E115</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K115" s="24">
-        <f>(1-$D115)*F115</f>
+        <f t="shared" si="34"/>
         <v>21000</v>
       </c>
       <c r="L115" s="24">
-        <f>G115</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M115" s="24">
-        <f>(1-$D115)*H115</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N115" s="24">
-        <f>(1-$D115)*I115</f>
+        <f t="shared" si="37"/>
         <v>3750</v>
       </c>
       <c r="O115" s="24">
@@ -13911,30 +13917,30 @@
         <v>0</v>
       </c>
       <c r="Z115" s="24">
-        <f>SUM(J115:Y115)</f>
+        <f t="shared" si="38"/>
         <v>75310</v>
       </c>
       <c r="AA115" s="24">
         <v>0</v>
       </c>
       <c r="AB115" s="20">
-        <f>Z115-AA115</f>
+        <f t="shared" si="39"/>
         <v>75310</v>
       </c>
       <c r="AC115" s="24" t="str">
-        <f>IF(AND($T115=6000, ($T115+$W115-$AB115)&gt;=6000),T115,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD115" s="24" t="str">
-        <f>IF(AND($T115=8000, ($T115+$W115-$AB115)&gt;=8000),T115,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE115" s="24" t="str">
-        <f>IF(($T115+$W115-$AB115)&gt;=$T115+8000,W115,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF115" s="25" t="str">
-        <f>IF(AB115&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -13967,23 +13973,23 @@
         <v>0</v>
       </c>
       <c r="J116" s="24">
-        <f>(1-$D116)*E116</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K116" s="24">
-        <f>(1-$D116)*F116</f>
+        <f t="shared" si="34"/>
         <v>26000</v>
       </c>
       <c r="L116" s="24">
-        <f>G116</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M116" s="24">
-        <f>(1-$D116)*H116</f>
+        <f t="shared" si="36"/>
         <v>1000</v>
       </c>
       <c r="N116" s="24">
-        <f>(1-$D116)*I116</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O116" s="24">
@@ -14020,30 +14026,30 @@
         <v>1000</v>
       </c>
       <c r="Z116" s="24">
-        <f>SUM(J116:Y116)</f>
+        <f t="shared" si="38"/>
         <v>44140</v>
       </c>
       <c r="AA116" s="24">
         <v>0</v>
       </c>
       <c r="AB116" s="20">
-        <f>Z116-AA116</f>
+        <f t="shared" si="39"/>
         <v>44140</v>
       </c>
       <c r="AC116" s="24" t="str">
-        <f>IF(AND($T116=6000, ($T116+$W116-$AB116)&gt;=6000),T116,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD116" s="24" t="str">
-        <f>IF(AND($T116=8000, ($T116+$W116-$AB116)&gt;=8000),T116,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE116" s="24" t="str">
-        <f>IF(($T116+$W116-$AB116)&gt;=$T116+8000,W116,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF116" s="25" t="str">
-        <f>IF(AB116&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -14076,23 +14082,23 @@
         <v>6000</v>
       </c>
       <c r="J117" s="24">
-        <f>(1-$D117)*E117</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K117" s="24">
-        <f>(1-$D117)*F117</f>
+        <f t="shared" si="34"/>
         <v>23100</v>
       </c>
       <c r="L117" s="24">
-        <f>G117</f>
+        <f t="shared" si="35"/>
         <v>5000</v>
       </c>
       <c r="M117" s="24">
-        <f>(1-$D117)*H117</f>
+        <f t="shared" si="36"/>
         <v>1400</v>
       </c>
       <c r="N117" s="24">
-        <f>(1-$D117)*I117</f>
+        <f t="shared" si="37"/>
         <v>4200</v>
       </c>
       <c r="O117" s="24">
@@ -14129,30 +14135,30 @@
         <v>0</v>
       </c>
       <c r="Z117" s="24">
-        <f>SUM(J117:Y117)</f>
+        <f t="shared" si="38"/>
         <v>78430</v>
       </c>
       <c r="AA117" s="24">
         <v>0</v>
       </c>
       <c r="AB117" s="20">
-        <f>Z117-AA117</f>
+        <f t="shared" si="39"/>
         <v>78430</v>
       </c>
       <c r="AC117" s="24" t="str">
-        <f>IF(AND($T117=6000, ($T117+$W117-$AB117)&gt;=6000),T117,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD117" s="24" t="str">
-        <f>IF(AND($T117=8000, ($T117+$W117-$AB117)&gt;=8000),T117,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE117" s="24" t="str">
-        <f>IF(($T117+$W117-$AB117)&gt;=$T117+8000,W117,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF117" s="25" t="str">
-        <f>IF(AB117&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -14185,23 +14191,23 @@
         <v>8000</v>
       </c>
       <c r="J118" s="24">
-        <f>(1-$D118)*E118</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K118" s="24">
-        <f>(1-$D118)*F118</f>
+        <f t="shared" si="34"/>
         <v>30000</v>
       </c>
       <c r="L118" s="24">
-        <f>G118</f>
+        <f t="shared" si="35"/>
         <v>5000</v>
       </c>
       <c r="M118" s="24">
-        <f>(1-$D118)*H118</f>
+        <f t="shared" si="36"/>
         <v>1500</v>
       </c>
       <c r="N118" s="24">
-        <f>(1-$D118)*I118</f>
+        <f t="shared" si="37"/>
         <v>6000</v>
       </c>
       <c r="O118" s="24">
@@ -14238,30 +14244,30 @@
         <v>0</v>
       </c>
       <c r="Z118" s="24">
-        <f>SUM(J118:Y118)</f>
+        <f t="shared" si="38"/>
         <v>68710</v>
       </c>
       <c r="AA118" s="24">
         <v>0</v>
       </c>
       <c r="AB118" s="20">
-        <f>Z118-AA118</f>
+        <f t="shared" si="39"/>
         <v>68710</v>
       </c>
       <c r="AC118" s="24" t="str">
-        <f>IF(AND($T118=6000, ($T118+$W118-$AB118)&gt;=6000),T118,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD118" s="24" t="str">
-        <f>IF(AND($T118=8000, ($T118+$W118-$AB118)&gt;=8000),T118,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE118" s="24" t="str">
-        <f>IF(($T118+$W118-$AB118)&gt;=$T118+8000,W118,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF118" s="25" t="str">
-        <f>IF(AB118&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -14294,23 +14300,23 @@
         <v>5000</v>
       </c>
       <c r="J119" s="24">
-        <f>(1-$D119)*E119</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K119" s="24">
-        <f>(1-$D119)*F119</f>
+        <f t="shared" si="34"/>
         <v>28000</v>
       </c>
       <c r="L119" s="24">
-        <f>G119</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M119" s="24">
-        <f>(1-$D119)*H119</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N119" s="24">
-        <f>(1-$D119)*I119</f>
+        <f t="shared" si="37"/>
         <v>5000</v>
       </c>
       <c r="O119" s="24">
@@ -14347,30 +14353,30 @@
         <v>4020</v>
       </c>
       <c r="Z119" s="24">
-        <f>SUM(J119:Y119)</f>
+        <f t="shared" si="38"/>
         <v>78500</v>
       </c>
       <c r="AA119" s="24">
         <v>0</v>
       </c>
       <c r="AB119" s="20">
-        <f>Z119-AA119</f>
+        <f t="shared" si="39"/>
         <v>78500</v>
       </c>
       <c r="AC119" s="24" t="str">
-        <f>IF(AND($T119=6000, ($T119+$W119-$AB119)&gt;=6000),T119,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD119" s="24" t="str">
-        <f>IF(AND($T119=8000, ($T119+$W119-$AB119)&gt;=8000),T119,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE119" s="24" t="str">
-        <f>IF(($T119+$W119-$AB119)&gt;=$T119+8000,W119,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF119" s="25" t="str">
-        <f>IF(AB119&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -14403,23 +14409,23 @@
         <v>0</v>
       </c>
       <c r="J120" s="24">
-        <f>(1-$D120)*E120</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K120" s="24">
-        <f>(1-$D120)*F120</f>
+        <f t="shared" si="34"/>
         <v>19500</v>
       </c>
       <c r="L120" s="24">
-        <f>G120</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M120" s="24">
-        <f>(1-$D120)*H120</f>
+        <f t="shared" si="36"/>
         <v>750</v>
       </c>
       <c r="N120" s="24">
-        <f>(1-$D120)*I120</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O120" s="24">
@@ -14456,30 +14462,30 @@
         <v>0</v>
       </c>
       <c r="Z120" s="24">
-        <f>SUM(J120:Y120)</f>
+        <f t="shared" si="38"/>
         <v>36390</v>
       </c>
       <c r="AA120" s="24">
         <v>7070</v>
       </c>
       <c r="AB120" s="20">
-        <f>Z120-AA120</f>
+        <f t="shared" si="39"/>
         <v>29320</v>
       </c>
       <c r="AC120" s="24" t="str">
-        <f>IF(AND($T120=6000, ($T120+$W120-$AB120)&gt;=6000),T120,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD120" s="24" t="str">
-        <f>IF(AND($T120=8000, ($T120+$W120-$AB120)&gt;=8000),T120,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE120" s="24" t="str">
-        <f>IF(($T120+$W120-$AB120)&gt;=$T120+8000,W120,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF120" s="25" t="str">
-        <f>IF(AB120&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -14512,23 +14518,23 @@
         <v>0</v>
       </c>
       <c r="J121" s="24">
-        <f>(1-$D121)*E121</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K121" s="24">
-        <f>(1-$D121)*F121</f>
+        <f t="shared" si="34"/>
         <v>18200</v>
       </c>
       <c r="L121" s="24">
-        <f>G121</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M121" s="24">
-        <f>(1-$D121)*H121</f>
+        <f t="shared" si="36"/>
         <v>700</v>
       </c>
       <c r="N121" s="24">
-        <f>(1-$D121)*I121</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O121" s="24">
@@ -14565,30 +14571,30 @@
         <v>0</v>
       </c>
       <c r="Z121" s="24">
-        <f>SUM(J121:Y121)</f>
+        <f t="shared" si="38"/>
         <v>42930</v>
       </c>
       <c r="AA121" s="24">
         <v>42930</v>
       </c>
       <c r="AB121" s="20">
-        <f>Z121-AA121</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AC121" s="24" t="str">
-        <f>IF(AND($T121=6000, ($T121+$W121-$AB121)&gt;=6000),T121,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD121" s="24" t="str">
-        <f>IF(AND($T121=8000, ($T121+$W121-$AB121)&gt;=8000),T121,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE121" s="24" t="str">
-        <f>IF(($T121+$W121-$AB121)&gt;=$T121+8000,W121,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF121" s="25" t="str">
-        <f>IF(AB121&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v>BONUS</v>
       </c>
     </row>
@@ -14621,23 +14627,23 @@
         <v>0</v>
       </c>
       <c r="J122" s="24">
-        <f>(1-$D122)*E122</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K122" s="24">
-        <f>(1-$D122)*F122</f>
+        <f t="shared" si="34"/>
         <v>26000</v>
       </c>
       <c r="L122" s="24">
-        <f>G122</f>
+        <f t="shared" si="35"/>
         <v>4000</v>
       </c>
       <c r="M122" s="24">
-        <f>(1-$D122)*H122</f>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N122" s="24">
-        <f>(1-$D122)*I122</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="O122" s="24">
@@ -14674,30 +14680,30 @@
         <v>0</v>
       </c>
       <c r="Z122" s="24">
-        <f>SUM(J122:Y122)</f>
+        <f t="shared" si="38"/>
         <v>50930</v>
       </c>
       <c r="AA122" s="24">
         <v>0</v>
       </c>
       <c r="AB122" s="20">
-        <f>Z122-AA122</f>
+        <f t="shared" si="39"/>
         <v>50930</v>
       </c>
       <c r="AC122" s="24" t="str">
-        <f>IF(AND($T122=6000, ($T122+$W122-$AB122)&gt;=6000),T122,"")</f>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="AD122" s="24" t="str">
-        <f>IF(AND($T122=8000, ($T122+$W122-$AB122)&gt;=8000),T122,"")</f>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="AE122" s="24" t="str">
-        <f>IF(($T122+$W122-$AB122)&gt;=$T122+8000,W122,"")</f>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="AF122" s="25" t="str">
-        <f>IF(AB122&lt;=0,"BONUS","")</f>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -14716,79 +14722,79 @@
       <c r="L123" s="28"/>
       <c r="M123" s="28"/>
       <c r="N123" s="28">
-        <f t="shared" ref="N123:AA123" si="0">SUM(N2:N122)</f>
+        <f t="shared" ref="N123:AA123" si="44">SUM(N2:N122)</f>
         <v>259800</v>
       </c>
       <c r="O123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>2138190</v>
       </c>
       <c r="P123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>1232050</v>
       </c>
       <c r="Q123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>108000</v>
       </c>
       <c r="R123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>24000</v>
       </c>
       <c r="S123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>16000</v>
       </c>
       <c r="T123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>252000</v>
       </c>
       <c r="U123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="V123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="W123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="X123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Y123" s="28">
-        <f t="shared" si="0"/>
+        <f t="shared" si="44"/>
         <v>188670</v>
       </c>
       <c r="Z123" s="28">
-        <f t="shared" si="0"/>
-        <v>7499985</v>
+        <f t="shared" si="44"/>
+        <v>7498635</v>
       </c>
       <c r="AA123" s="28">
-        <f t="shared" si="0"/>
-        <v>888325</v>
+        <f t="shared" si="44"/>
+        <v>921465</v>
       </c>
       <c r="AB123" s="28">
         <f>SUM(AB2:AB122)</f>
-        <v>6611660</v>
+        <v>6577170</v>
       </c>
       <c r="AC123" s="28">
-        <f t="shared" ref="AC123:AF123" si="1">SUM(AC2:AC122)</f>
+        <f t="shared" ref="AC123:AF123" si="45">SUM(AC2:AC122)</f>
         <v>6000</v>
       </c>
       <c r="AD123" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AE123" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="AF123" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
     </row>
@@ -22974,7 +22980,7 @@
     <sortCondition ref="A2:A123"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="AC1:AF1 AB124:AB980 AB1:AB122 E123:AF123">
+  <conditionalFormatting sqref="AC1:AF1 AB1:AB122 E123:AF123 AB124:AB980">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -23001,7 +23007,7 @@
   <cols>
     <col min="1" max="1" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" style="7" customWidth="1"/>
@@ -23487,11 +23493,21 @@
       <c r="X19" s="7"/>
     </row>
     <row r="20" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="11"/>
+      <c r="A20" s="10">
+        <v>46275</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D20" s="12">
+        <v>33140</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>285</v>
+      </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>

--- a/2026 - 2027 FEE.xlsx
+++ b/2026 - 2027 FEE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B291D2-5646-4D7E-A0FC-35ACFAE817AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C1F0EF-02A9-49BB-BEC6-09CCEF8DA40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1ST TERM ACCOUNT" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="288">
   <si>
     <t>LAST NAME</t>
   </si>
@@ -891,10 +891,16 @@
     <t>JAMIU FAIZAH</t>
   </si>
   <si>
-    <t>IP:KAYODE MATHEW OLUWASEUN-ISRAEL 1ST TERM</t>
+    <t>OLUWASEUN ISRAEL</t>
   </si>
   <si>
-    <t>OLUWASEUN ISRAEL</t>
+    <t>NIP:KAYODE MATHEW OLUWASEUN-ISRAEL 1ST TERM</t>
+  </si>
+  <si>
+    <t>NIP:OLATUNDE BUKOLA ALICE</t>
+  </si>
+  <si>
+    <t>OLATUNDE FAITHFULNESS</t>
   </si>
 </sst>
 </file>
@@ -11087,11 +11093,11 @@
         <v>56930</v>
       </c>
       <c r="AA89" s="24">
-        <v>0</v>
+        <v>24700</v>
       </c>
       <c r="AB89" s="20">
         <f t="shared" si="28"/>
-        <v>56930</v>
+        <v>32230</v>
       </c>
       <c r="AC89" s="24" t="str">
         <f t="shared" si="29"/>
@@ -12064,14 +12070,14 @@
         <v>-10000</v>
       </c>
       <c r="Z98" s="24">
-        <f t="shared" ref="Z98:Z129" si="38">SUM(J98:Y98)</f>
+        <f t="shared" ref="Z98:Z122" si="38">SUM(J98:Y98)</f>
         <v>31790</v>
       </c>
       <c r="AA98" s="24">
         <v>33140</v>
       </c>
       <c r="AB98" s="20">
-        <f t="shared" ref="AB98:AB129" si="39">Z98-AA98</f>
+        <f t="shared" ref="AB98:AB122" si="39">Z98-AA98</f>
         <v>-1350</v>
       </c>
       <c r="AC98" s="24" t="str">
@@ -14775,11 +14781,11 @@
       </c>
       <c r="AA123" s="28">
         <f t="shared" si="44"/>
-        <v>921465</v>
+        <v>946165</v>
       </c>
       <c r="AB123" s="28">
         <f>SUM(AB2:AB122)</f>
-        <v>6577170</v>
+        <v>6552470</v>
       </c>
       <c r="AC123" s="28">
         <f t="shared" ref="AC123:AF123" si="45">SUM(AC2:AC122)</f>
@@ -23007,7 +23013,7 @@
   <cols>
     <col min="1" max="1" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="68.85546875" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.7109375" style="7" customWidth="1"/>
@@ -23500,13 +23506,13 @@
         <v>250</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D20" s="12">
         <v>33140</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -23529,10 +23535,21 @@
       <c r="X20" s="7"/>
     </row>
     <row r="21" spans="1:24" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="7"/>
+      <c r="A21" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D21" s="9">
+        <v>24700</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>287</v>
+      </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
